--- a/code/data/phones_clean.xlsx
+++ b/code/data/phones_clean.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>苹果iPhone iPhone的8G版为黑色、银色外壳，支持UMTS/HSDPA (850, 1900, 2100 MHz)三频网络，在原有GSM/EDGE网络的基础上有了质的提升，这样一来iPhone内置的Safari浏览器将真正的发挥出它应有的性能。此外，其还内置了GPS模块，支持AGPS辅助导航功能，能够通过Wi-Fi、通信基站以及卫星三方面进行定位，并且误差仅为3米，这一数字甚至可以与专业</t>
+          <t>苹果iPhone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>苹果iPhone（16GB） 外观设计:直板 手机制式:GSM 支持频段:GSM850/900/1800/1900MHz 屏幕色彩:1600万色 主屏参数:320×480像素 手机类型:智能手机，音乐手机 摄像头像素:200万像素 理论待机时间:250小时</t>
+          <t>苹果iPhone（16GB）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>苹果iPhone 3G（8G） 苹果公司2008年推出的第二款手机，3.5英寸的大屏幕支持多点触摸，加之2.0时代新引入的App store使得这款手机的整体性能更上层楼。而目前这款手机是iPhone三款手机中销售量最大的一款，也是iPhone真正打开全世界市场的一款手机。</t>
+          <t>苹果iPhone 3G（8G）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -692,8 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>苹果iPhone 3G（16GB） 外观设计:直板 网络模式:GSM，WCDMA 支持频段:2G：GSM 850/900/1800/1900
-3G：WCDMA 850/1800/1900MHz 主屏色彩:1600万色 主屏分辨率:320×480像素 手机类型:3G手机，智能手机 摄像头像素:200万像素 理论待机时间:300小时</t>
+          <t>苹果iPhone 3G（16GB）</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -754,7 +753,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>苹果iPhone 3GS（8GB） 上市日期:2010年07月 手机类型:3G手机，智能手机，音乐手机 外观设计:直板 主屏尺寸:3.5英寸 触摸屏:支持 主屏分辨率:320×480像素 网络模式:GSM，WCDMA</t>
+          <t>苹果iPhone 3GS（8GB）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -815,7 +814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>苹果iPhone 3GS（32GB） 上市日期:2009年06月 手机类型:3G手机，智能手机，音乐手机 外观设计:直板 主屏尺寸:3.5英寸 触摸屏:支持 主屏分辨率:320×480像素 网络模式:GSM，WCDMA</t>
+          <t>苹果iPhone 3GS（32GB）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>苹果iPhone 3GS（16GB/联通版） 主屏尺寸:3.5英寸 主屏材质:TFT 主屏分辨率:480x320像素 网络类型:单卡双模 网络模式:GSM，WCDMA 操作系统:iOS 3.0 CPU型号:ARM Cortex-A8</t>
+          <t>苹果iPhone 3GS（16GB/联通版）</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -939,7 +938,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>苹果iPhone 3G（8G/联通版） 主屏尺寸:3.5英寸 主屏材质:TFT 主屏分辨率:320×480像素 网络模式:GSM，WCDMA 操作系统:iOS 3.0 CPU型号:ARM11 CPU频率:620MHz</t>
+          <t>苹果iPhone 3G（8G/联通版）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1002,7 +1001,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>苹果iPhone 3GS（32GB/联通版） 主屏尺寸:3.5英寸 主屏材质:TFT 主屏分辨率:480x320像素 网络类型:单卡双模 网络模式:GSM，WCDMA 操作系统:iOS 3.0 CPU型号:ARM Cortex-A8</t>
+          <t>苹果iPhone 3GS（32GB/联通版）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1065,7 +1064,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（16GB） 最新的iPhone 4相比于前三代产品无论是在硬件配置和软件上都有了较大的升级,采用了1GHz的苹果A4处理器，搭载3.5英寸960x640分辨率的屏幕。正面副摄像头具备视频通话功能同时背部500万摄像头支持720P高清摄像。软件方面iPhone 4将会成为首款搭载iOS（原iPhone OS4）平台的手机。这款手机毫无疑问成为年度最重磅的明星产品。</t>
+          <t>苹果iPhone 4（16GB）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1126,7 +1125,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（32GB） 最新的iPhone 4相比于前三代产品无论是在硬件配置和软件上都有了较大的升级,采用了1GHz的苹果A4处理器，搭载3.5英寸960x640分辨率的屏幕。正面副摄像头具备视频通话功能同时背部500万摄像头支持720P高清摄像。软件方面iPhone 4将会成为首款搭载iOS（原iPhone OS4）平台的手机。这款手机毫无疑问成为年度最重磅的明星产品。</t>
+          <t>苹果iPhone 4（32GB）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1187,7 +1186,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（16GB/C网） 上市日期:2011年02月 手机类型:3G手机，智能手机，音乐手机，拍照手机 主屏尺寸:3.5英寸 外观设计:直板 触摸屏:电容屏，多点触控 主屏分辨率:960x640像素 网络模式:CDMA2000</t>
+          <t>苹果iPhone 4（16GB/C网）</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1248,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（16GB/联通版） 联通定制版iPhone 4，16GB ROM容量版本</t>
+          <t>苹果iPhone 4（16GB/联通版）</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1309,7 +1308,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（32GB/联通版） 联通定制版iPhone 4，32GB ROM容量版本</t>
+          <t>苹果iPhone 4（32GB/联通版）</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1370,7 +1369,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（16GB/白色） 白色iPhone4的信号问题依然存在，也会丢失3G信号。无论是白色还是黑色iPhone4，机器两端和中间的厚度是不同的，因此我们的比较也分为两部分。结果表明白色iPhone4与黑色iPhone4的机身两端厚度基本一致，但机身中间则不同。白色iPhone4为9.56毫米，确实要比黑色版略厚0.19毫米。白色iPhone4的屏幕面板的确比黑色iPhone4的颜色</t>
+          <t>苹果iPhone 4（16GB/白色）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1433,7 +1432,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（16GB） 非定制版，包含GSM和WCDMA网络版本，黑色比白色略便宜，港版可在大陆专营店保修，比其他版本稍贵</t>
+          <t>苹果iPhone 5（16GB）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1504,7 +1503,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（32GB/C网） 主屏尺寸:3.5英寸 主屏材质:IPS 主屏分辨率:960x640像素 网络模式:CDMA2000 操作系统:iOS 4.0 CPU型号:苹果 A4 CPU频率:1024MHz</t>
+          <t>苹果iPhone 4（32GB/C网）</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1567,7 +1566,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（32GB/施华洛世奇粉色） 主屏尺寸:3.5英寸 主屏材质:IPS 主屏分辨率:960x640像素 网络类型:单卡双模 网络模式:GSM，WCDMA 操作系统:iOS 4.0 CPU型号:苹果 A4</t>
+          <t>苹果iPhone 4（32GB/施华洛世奇粉色）</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1630,7 +1629,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>苹果iPhone 6（全网通） 圆弧形边缘，视网膜Retina技术，指纹识别，Siri语音</t>
+          <t>苹果iPhone 6（全网通）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1701,7 +1700,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（16GB） 价格稳定，现在买较合适，但是翻新机很多，购买时需谨慎，操作系统很稳定，不存在掉漆现象</t>
+          <t>苹果iPhone 4S（16GB）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1754,7 +1753,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（32GB） 市场上货源少于16GB，siri语音功能支持中文，iOS操作系统很稳定，个别用户反映有掉漆现象</t>
+          <t>苹果iPhone 5（32GB）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1825,7 +1824,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（64GB） 64GB超大容量，但是货源不多，价格较贵，续航能力一般，有必要配备移动电源，只能用Nano SIM卡</t>
+          <t>苹果iPhone 5（64GB）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1896,7 +1895,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（32GB/白色） 主屏尺寸:3.5英寸 主屏材质:IPS 主屏分辨率:960x640像素 网络类型:单卡双模 网络模式:GSM，WCDMA 操作系统:iOS 4.0 CPU型号:苹果 A4</t>
+          <t>苹果iPhone 4（32GB/白色）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1959,7 +1958,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>苹果iPhone 5C（双3G） 视网膜Retina技术，iSight摄像头，照片地理标记</t>
+          <t>苹果iPhone 5C（双3G）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2101,7 +2100,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（8GB） 市场上只有行货，价格便宜，很容易买到翻新机，支持的软件大部分都是要付费的，内存较小</t>
+          <t>苹果iPhone 4（8GB）</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2221,7 +2220,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（32GB） 普通非定制版4S，分为WCDMA网络和CDMA200网络，32GB容量版本</t>
+          <t>苹果iPhone 4S（32GB）</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2274,7 +2273,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（64GB） 普通非定制版4S，分为WCDMA网络和CDMA200网络，64GB容量版本</t>
+          <t>苹果iPhone 4S（64GB）</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2327,7 +2326,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>苹果iPhone 4（8GB/联通版） 联通定制版，市场上有少量货源，越狱前输入法不好用，下载东西不方便，个别用户反映信号一般</t>
+          <t>苹果iPhone 4（8GB/联通版）</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2589,7 +2588,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>苹果iPhone 5S（双4G） 指纹识别，视网膜Retina技术，背照式镜头，Siri语音</t>
+          <t>苹果iPhone 5S（双4G）</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2731,7 +2730,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>苹果iPhone 5C（移动4G） 移动4G网络，5种机身颜色可选择，IOS7操作系统运行流畅，塑料外壳</t>
+          <t>苹果iPhone 5C（移动4G）</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2802,7 +2801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>苹果iPhone 5C（电信3G） 电信合约定制版5C，包含16GB/32GB容量版本</t>
+          <t>苹果iPhone 5C（电信3G）</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2873,7 +2872,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>苹果iPhone 5S（电信3G） 指纹识别，视网膜Retina技术，背照式镜头，Siri语音</t>
+          <t>苹果iPhone 5S（电信3G）</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2944,7 +2943,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>苹果iPhone 5S（移动4G） 指纹识别，视网膜Retina技术，背照式镜头，Siri语音</t>
+          <t>苹果iPhone 5S（移动4G）</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3015,7 +3014,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（8GB） Siri语音，IOS7系统，1080P视频录制</t>
+          <t>苹果iPhone 4S（8GB）</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3084,7 +3083,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>苹果iPhone 5S（联通3G） 指纹识别，视网膜Retina技术，背照式镜头，Siri语音</t>
+          <t>苹果iPhone 5S（联通3G）</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3155,7 +3154,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S（全网通） 压力感应触控，True Tone闪光灯，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 6S（全网通）</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3226,7 +3225,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>苹果iPhone 5C（联通3G） 联通定制机，5种机身颜色可选择，IOS7操作系统运行流畅，塑料外壳</t>
+          <t>苹果iPhone 5C（联通3G）</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3283,7 +3282,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>苹果iPhone 6 Plus（移动4G） 光线图像防抖，水平显示功能，iSight传感器，Siri语音</t>
+          <t>苹果iPhone 6 Plus（移动4G）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3354,7 +3353,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>苹果iPhone 7（全网通） 防水防尘，True Tone闪光灯，4K视频摄录，非按压式指纹识别</t>
+          <t>苹果iPhone 7（全网通）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3429,7 +3428,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>苹果iPhone 6（移动4G） 圆弧形边缘，视网膜Retina技术，指纹识别，Siri语音</t>
+          <t>苹果iPhone 6（移动4G）</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3500,7 +3499,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>苹果iPhone 6 Plus（全网通） 光线图像防抖，水平显示功能，iSight传感器，Siri语音</t>
+          <t>苹果iPhone 6 Plus（全网通）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3571,7 +3570,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>苹果iPhone 6（国际版/双4G） 圆弧形边缘，视网膜Retina技术，指纹识别，Siri语音</t>
+          <t>苹果iPhone 6（国际版/双4G）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3628,7 +3627,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>苹果iPhone 6 Plus（国际版/双4G） 光线图像防抖，水平显示功能，iSight传感器，Siri语音</t>
+          <t>苹果iPhone 6 Plus（国际版/双4G）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3685,7 +3684,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>苹果iPhone 8（全网通） 双面玻璃，无线充电，AR游戏，指纹识别</t>
+          <t>苹果iPhone 8（全网通）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3760,7 +3759,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>苹果iPhone SE（全网通） 指纹识别，NFC无线通讯，Apple Pay移动支付，Siri语音</t>
+          <t>苹果iPhone SE（全网通）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3831,7 +3830,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S Plus（全网通） 3D Touch，航空铝镁合金材料，支持NFC，Siri语音</t>
+          <t>苹果iPhone 6S Plus（全网通）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3902,7 +3901,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S（国际版/双4G） 压力感应触控，True Tone闪光灯，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 6S（国际版/双4G）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3959,7 +3958,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S Plus（国际版/双4G） 3D Touch，航空铝镁合金材料，玫瑰金色，Siri语音</t>
+          <t>苹果iPhone 6S Plus（国际版/双4G）</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4016,7 +4015,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>苹果iPhone 7 Plus（全网通） 后置双摄像头，多语言文字同时显示，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 7 Plus（全网通）</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4091,7 +4090,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S（移动4G） 压力感应触控，True Tone闪光灯，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 6S（移动4G）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4162,7 +4161,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>苹果iPhone 6S Plus（移动4G） 3D Touch，航空铝镁合金材料，玫瑰金色，Siri语音</t>
+          <t>苹果iPhone 6S Plus（移动4G）</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4233,7 +4232,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>苹果iPhone SE（国际版） 指纹识别，NFC无线通讯，Apple Pay移动支付，Siri语音</t>
+          <t>苹果iPhone SE（国际版）</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4290,7 +4289,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>苹果iPhone 7（国际版/全网通） 防水防尘，True Tone闪光灯，4K视频摄录，非按压式指纹识别</t>
+          <t>苹果iPhone 7（国际版/全网通）</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4347,7 +4346,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>苹果iPhone 7 Plus（国际版/全网通） 后置双摄像头，多语言文字同时显示，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 7 Plus（国际版/全网通）</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4404,7 +4403,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>苹果iPhone 7（双4G） 防水防尘，True Tone闪光灯，4K视频摄录，非按压式指纹识别</t>
+          <t>苹果iPhone 7（双4G）</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4475,7 +4474,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 2（3GB/64GB/全网通） 小屏手机，A13仿生芯片，触控ID</t>
+          <t>苹果iPhone SE 2（3GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4550,7 +4549,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>苹果iPhone 7（特别版/全网通） 防水防尘，True Tone闪光灯，4K视频摄录，非按压式指纹识别</t>
+          <t>苹果iPhone 7（特别版/全网通）</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4621,7 +4620,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>苹果iPhone 7 Plus（特别版/全网通） 后置双摄像头，多语言文字同时显示，4K视频摄录，Siri语音</t>
+          <t>苹果iPhone 7 Plus（特别版/全网通）</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4692,7 +4691,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>苹果iPhone 7 Plus（双4G） 双4G</t>
+          <t>苹果iPhone 7 Plus（双4G）</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4763,7 +4762,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>苹果iPhone 8 Plus（全网通） 双面玻璃，无线充电，Portrait Lighting，后置双摄</t>
+          <t>苹果iPhone 8 Plus（全网通）</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4838,7 +4837,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>苹果iPhone X（全网通） 无线充电，面容ID，后置双摄，超大全面屏</t>
+          <t>苹果iPhone X（全网通）</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4909,7 +4908,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>苹果iPhone 8（国际版/全网通） 双面玻璃，无线充电，AR游戏</t>
+          <t>苹果iPhone 8（国际版/全网通）</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4966,7 +4965,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>苹果iPhone 8 Plus（国际版/全网通） 双面玻璃，无线充电，Portrait Lighting，后置双摄</t>
+          <t>苹果iPhone 8 Plus（国际版/全网通）</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>苹果iPhone X（国际版/全网通） 无线充电，面容ID，后置双摄，全面屏</t>
+          <t>苹果iPhone X（国际版/全网通）</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5076,7 +5075,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>苹果iPhone XR（全网通） 全面屏，快速充电，双卡双待，超视网膜高清显示屏</t>
+          <t>苹果iPhone XR（全网通）</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5151,7 +5150,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>苹果iPhone 11（4GB/64GB/全网通） A13处理器，GPU抗锯齿效果，夜间模式</t>
+          <t>苹果iPhone 11（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5226,7 +5225,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>华为Mate30（8GB/128GB/全网通/5G版/玻璃版） IP53防水防尘，磁悬浮发声技术，4000万超感光徕卡影像，OLED全面屏</t>
+          <t>华为Mate30（8GB/128GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5302,7 +5301,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>苹果iPhone XS（国际版/全网通） 国际版</t>
+          <t>苹果iPhone XS（国际版/全网通）</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5359,7 +5358,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>苹果iPhone XS（国际版/双4G） 双4G</t>
+          <t>苹果iPhone XS（国际版/双4G）</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5416,7 +5415,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>苹果iPhone XS Max（国际版/全网通） 超视网膜显示屏，双卡双待，后置双摄，苹果 A12处理器</t>
+          <t>苹果iPhone XS Max（国际版/全网通）</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5473,7 +5472,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>苹果iPhone XS Max（国际版/双4G） 双4G</t>
+          <t>苹果iPhone XS Max（国际版/双4G）</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5530,7 +5529,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>苹果iPhone XR（国际版/双4G） 全面屏，快速充电，双卡双待，超视网膜高清显示屏</t>
+          <t>苹果iPhone XR（国际版/双4G）</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5587,7 +5586,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>华为Mate30 Pro（8GB/256GB/全网通/5G版/玻璃版） 双4000万徕卡电影四摄，超曲面OLED环幕屏</t>
+          <t>华为Mate30 Pro（8GB/256GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5663,7 +5662,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip（8GB/256GB/全网通） 折叠手机，自适应模式，灵动外屏</t>
+          <t>三星Galaxy Z Flip（8GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5738,7 +5737,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>荣耀20青春版（4GB/64GB/全网通） 4800万后置三摄，OLED 屏幕，屏幕指纹解锁，AOD息屏显示</t>
+          <t>荣耀20青春版（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5813,7 +5812,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro（4GB/64GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5884,7 +5883,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro（6GB/128GB/全网通/5G版） 5G加身，A14仿生速度超快，Pro级摄像头系统</t>
+          <t>苹果iPhone 12 Pro（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5955,7 +5954,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>三星Galaxy A50s（6GB/128GB/全网通） 4800万后置三摄，多功能NFC，游戏助推器</t>
+          <t>三星Galaxy A50s（6GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6030,7 +6029,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>vivo Y7s（6GB/128GB/全网通） superAmoled全面屏，光电屏幕指纹，超广角AI三摄，前置1600万高清像素，超级逆光</t>
+          <t>vivo Y7s（6GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6105,7 +6104,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>华为畅享10e（4GB/64GB/全网通） 1300万后置双摄，5000mAh大电池，6.3英寸珍珠屏</t>
+          <t>华为畅享10e（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6180,7 +6179,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro Max（4GB/64GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro Max（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6251,7 +6250,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>荣耀Play3（4GB/64GB/全网通） 全场景加速引擎，暗光人脸解锁，麒麟710F自研芯片</t>
+          <t>荣耀Play3（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6326,7 +6325,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华为畅享10 Plus（4GB/128GB/全网通） 6.59英寸全视屏，前置悬浮式镜头，4800万超广角AI三摄</t>
+          <t>华为畅享10 Plus（4GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6401,7 +6400,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>华为P40（6GB/128GB/全网通/5G版） 徕卡三摄，麒麟990 5G，WiFi 6</t>
+          <t>华为P40（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6476,7 +6475,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>苹果iPhone 11（4GB/128GB/全网通） A13处理器，GPU抗锯齿效果，夜间模式</t>
+          <t>苹果iPhone 11（4GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6551,7 +6550,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>苹果iPhone 11（4GB/256GB/全网通） A13处理器，GPU抗锯齿效果，夜间模式</t>
+          <t>苹果iPhone 11（4GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6626,7 +6625,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro（4GB/256GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro（4GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6697,7 +6696,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro（4GB/512GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro（4GB/512GB/全网通）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6768,7 +6767,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro Max（4GB/256GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro Max（4GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6839,7 +6838,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>苹果iPhone 11 Pro Max（4GB/512GB/全网通） HDR10，后置三摄，神经网络引擎，独立取景器</t>
+          <t>苹果iPhone 11 Pro Max（4GB/512GB/全网通）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6910,7 +6909,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>三星W20（12GB/512GB/全网通/5G版） 5G超高速，全方位摄像头组，折叠屏</t>
+          <t>三星W20（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6977,7 +6976,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>华为Mate30 RS保时捷版（12GB/512GB/全网通/5G版） 海思麒麟990 5G，双4000万徕卡电影四摄，后背带设计</t>
+          <t>华为Mate30 RS保时捷版（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7053,7 +7052,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>华为Mate30（8GB/128GB/全网通） IP53防水防尘，磁悬浮发声技术，4000万超感光徕卡影像，OLED全面屏</t>
+          <t>华为Mate30（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7114,7 +7113,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>华为Mate30 Pro（8GB/128GB/全网通/5G版/玻璃版） 双4000万徕卡电影四摄，超曲面OLED环幕屏</t>
+          <t>华为Mate30 Pro（8GB/128GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7190,7 +7189,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华为畅享10（4GB/64GB/全网通） 极点全面屏，4800万超清夜景，4000mAh大电池</t>
+          <t>华为畅享10（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7265,7 +7264,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>三星Galaxy S20（12GB/128GB/全网通） 6400万后置主摄，LPDDR5内存，AI一键多拍</t>
+          <t>三星Galaxy S20（12GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7340,7 +7339,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>华为畅享10S（6GB/64GB/全网通） 超广角AI三摄，AI逆光美拍，光感屏幕指纹</t>
+          <t>华为畅享10S（6GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7415,7 +7414,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 mini（4GB/64GB/全网通/5G版） 超瓷晶面板，A14仿生，超视网膜XDR，超快的双模5G</t>
+          <t>苹果iPhone 12 mini（4GB/64GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7486,7 +7485,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>vivo Y5s（6GB/128GB/全网通） AI智慧三摄，18W双引擎闪充，游戏魔盒</t>
+          <t>vivo Y5s（6GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7561,7 +7560,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>三星Galaxy A51（8GB/128GB/全网通/5G版） 后置4800万四摄，4500mAh大电池，Super AMOLED星点屏</t>
+          <t>三星Galaxy A51（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7636,7 +7635,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>三星GALAXY A71（8GB/128GB/全网通/5G版） Exynos 980，双模5G，1TB扩展存储</t>
+          <t>三星GALAXY A71（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7711,7 +7710,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>华为nova 6 SE（8GB/128GB/全网通） 全场景AI四摄，人像超级夜景2.0，GPU Turbo，40W超级快充</t>
+          <t>华为nova 6 SE（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7786,7 +7785,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>华为Mate Xs（8GB/512GB/全网通/5G版） 超感光徕卡四摄，可折叠全面屏，4500mAh电池</t>
+          <t>华为Mate Xs（8GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7861,7 +7860,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OPPO A8（4GB/128GB/全网通） 千元三摄，阳光护眼屏</t>
+          <t>OPPO A8（4GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7936,7 +7935,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>三星Galaxy S20+（12GB/128GB/全网通） 120Hz超感屏，30倍超视觉空间变焦，8K投屏</t>
+          <t>三星Galaxy S20+（12GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8011,7 +8010,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>三星Galaxy S20 Ultra（12GB/256GB/全网通） 1.08亿像素后置主摄，8k视频录制，100倍变焦</t>
+          <t>三星Galaxy S20 Ultra（12GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8086,7 +8085,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>vivo Z6（6GB/128GB/全网通/5G版） 44W超快闪充，高通骁龙765G，5000mAh超大电池</t>
+          <t>vivo Z6（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8161,7 +8160,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>荣耀30S（8GB/128GB/全网通/5G版） 5G双模，麒麟820，40W快充</t>
+          <t>荣耀30S（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8236,7 +8235,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>三星Galaxy Note 20（8GB/256GB/全网通/5G版） 骁龙865+，S Pen，专业视频拍摄</t>
+          <t>三星Galaxy Note 20（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8311,7 +8310,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>华为nova 7（8GB/128GB/5G版/全网通） OLED极点全面屏，全网通5G，麒麟985</t>
+          <t>华为nova 7（8GB/128GB/5G版/全网通）</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8386,7 +8385,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>华为P40 Pro（8GB/128GB/全网通/5G版） 徕卡四摄，麒麟990 5G，40W快充</t>
+          <t>华为P40 Pro（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8461,7 +8460,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>华为P40 Pro+（8GB/512GB/全网通/5G版） 徕卡五摄，双长焦镜头，麒麟990 5G</t>
+          <t>华为P40 Pro+（8GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8536,7 +8535,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>华为P40 Pro（8GB/256GB/全网通/5G版） 徕卡四摄，麒麟990 5G，40W快充</t>
+          <t>华为P40 Pro（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8611,7 +8610,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>荣耀畅玩9A（4GB/64GB/全网通） 巨肺小霸王，超长续航，双卡双待</t>
+          <t>荣耀畅玩9A（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8686,7 +8685,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>荣耀30（6GB/128GB/全网通/5G版） 麒麟 985，40W快充，50倍超稳远摄</t>
+          <t>荣耀30（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8761,7 +8760,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>荣耀30 Pro（8GB/128GB/全网通/5G版） 50倍超稳远摄，双模5G，麒麟990，4000万超感光摄影</t>
+          <t>荣耀30 Pro（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8836,7 +8835,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>荣耀30 Pro+（8GB/256GB/全网通/5G版） 双模5G，无线反向充电，90Hz刷新率</t>
+          <t>荣耀30 Pro+（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8911,7 +8910,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 2（3GB/128GB/全网通） 小屏手机，A13仿生芯片，触控ID</t>
+          <t>苹果iPhone SE 2（3GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8986,7 +8985,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 2（3GB/256GB/全网通） 小屏手机，A13仿生芯片，触控ID</t>
+          <t>苹果iPhone SE 2（3GB/256GB/全网通）</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9061,7 +9060,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>华为nova 7 Pro（8GB/128GB/5G版/全网通） 前置3200万追焦双摄 ，50倍潜望式变焦四摄，麒麟985</t>
+          <t>华为nova 7 Pro（8GB/128GB/5G版/全网通）</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9136,7 +9135,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>华为nova 7 SE（8GB/128GB/5G版/全网通） 麒麟820，6400万高清AI四摄，40W超级快充</t>
+          <t>华为nova 7 SE（8GB/128GB/5G版/全网通）</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9211,7 +9210,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OPPO A72（8GB/128GB/全网通/5G版） 超薄拍照游戏手机，双模5G，90Hz全面屏，7.9mm超薄</t>
+          <t>OPPO A72（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9286,7 +9285,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>华为nova 7（8GB/256GB/5G版/全网通） OLED极点全面屏，全网通5G，麒麟985</t>
+          <t>华为nova 7（8GB/256GB/5G版/全网通）</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9361,7 +9360,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>荣耀X10（6GB/128GB/全网通/5G版） 5G双模，麒麟820，4300mAh续航，4000万高感光影像</t>
+          <t>荣耀X10（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9436,7 +9435,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold2（12GB/512GB/全网通/5G版） 自适应分屏模式，双芯智能电池，双重预览</t>
+          <t>三星Galaxy Z Fold2（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9511,7 +9510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>vivo X50（8GB/128GB/全网通/5G版） 超感光夜摄，超稳运动拍摄，定制IMX598传感器，90Hz高刷新率，180Hz高采样率屏幕，超薄柔性屏</t>
+          <t>vivo X50（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9586,7 +9585,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>华为畅享Z（6GB/64GB/全网通/5G版） 超级夜景，4K视频录像，5G</t>
+          <t>华为畅享Z（6GB/64GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9661,7 +9660,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>荣耀X10（8GB/128GB/全网通/5G版） 5G双模，麒麟820，4300mAh续航，4000万高感光影像</t>
+          <t>荣耀X10（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9736,7 +9735,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>vivo Y70s（8GB/128GB/全网通/5G版） 三星 Exynos 880，4500毫安电池，侧边指纹，双模5G</t>
+          <t>vivo Y70s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9811,7 +9810,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>vivo X50 Pro（8GB/128GB/全网通/5G版） 微云台超感光主摄，超感光夜摄，超稳运动拍摄，90Hz高刷新率，轻薄曲面屏</t>
+          <t>vivo X50 Pro（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9886,7 +9885,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>华为Mate40（8GB/128GB/全网通/5G版/玻璃版） 90Hz刷新率，240Hz触控采样率，68°曲面屏，麒麟9000E</t>
+          <t>华为Mate40（8GB/128GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9961,7 +9960,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>三星Galaxy S21（8GB/256GB/全网通/5G版） 骁龙888，超高清专业摄像，120Hz护目屏</t>
+          <t>三星Galaxy S21（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10037,7 +10036,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>华为P50（8GB/128GB/全网通） 高通骁龙888处理器，90Hz OLED显示屏，IP68防尘防水，鸿蒙2.0系统</t>
+          <t>华为P50（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10108,7 +10107,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>华为畅享20 Pro（6GB/128GB/全网通/5G版） 全网通 5G SoC芯片，4800万高感光夜拍，90Hz畅滑屏，22.5W华为超级快充，4000mAh大电池</t>
+          <t>华为畅享20 Pro（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10183,7 +10182,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>vivo Y30（8GB/128GB/全网通） 18W双引擎闪充，AI智慧三摄，5000mAh大电池</t>
+          <t>vivo Y30（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10258,7 +10257,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>荣耀30青春版（6GB/64GB/全网通/5G版） 90Hz刷新率，4000mAh大电池，AI极速抓拍</t>
+          <t>荣耀30青春版（6GB/64GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10333,7 +10332,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>三星Galaxy Note 20 Ultra（12GB/256GB/全网通/5G版） S Pen，三星笔记，120Hz自适应屏幕，专业视频拍摄</t>
+          <t>三星Galaxy Note 20 Ultra（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10408,7 +10407,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip（8GB/256GB/全网通/5G版） 双模5G，骁龙865+，超薄柔性玻璃，折叠手机</t>
+          <t>三星Galaxy Z Flip（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10483,7 +10482,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>华为P50 Pocket（8GB/256GB） 宝盒形态设计，晶钻立体微雕工艺，智慧外屏，120Hz高刷新率内屏</t>
+          <t>华为P50 Pocket（8GB/256GB）</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10554,7 +10553,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>华为麦芒9（6GB/128GB/全网通/5G版） 22.5W超级快充，6400w高清摄影，极速5G新体验</t>
+          <t>华为麦芒9（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10629,7 +10628,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>苹果iPhone 12（4GB/64GB/全网通/5G版） A14仿生芯片，超视网膜XDR显示屏，超瓷晶面板，双模5G</t>
+          <t>苹果iPhone 12（4GB/64GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10700,7 +10699,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>vivo Y51s（6GB/128GB/全网通） 双模5G，4500mAh电池，双引擎闪充</t>
+          <t>vivo Y51s（6GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10775,7 +10774,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>vivo S7（8GB/128GB/全网通/5G版） 前置4400万AF双摄自拍，双模5G，后置6400万超感光夜摄，超级夜景4.0</t>
+          <t>vivo S7（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10850,7 +10849,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>三星Galaxy Note 20 Ultra（12GB/512GB/全网通/5G版） S Pen，疾速游戏体验，三星笔记，120Hz自适应屏幕</t>
+          <t>三星Galaxy Note 20 Ultra（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10925,7 +10924,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>华为畅享20 Plus（6GB/128GB/全网通/5G版） 40W超级快充，90Hz高刷屏，4800万AI三摄</t>
+          <t>华为畅享20 Plus（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11000,7 +10999,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>华为Mate X2（8GB/256GB/全网通/5G版） 麒麟9000旗舰芯片，无缝鹰翼折叠，超感知徕卡四摄</t>
+          <t>华为Mate X2（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11075,7 +11074,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro Max（6GB/128GB/全网通/5G版） 超瓷晶面板，5G网络，Pro级摄像头系统，LiDAR激光雷达</t>
+          <t>苹果iPhone 12 Pro Max（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11150,7 +11149,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OPPO Reno5（12GB/256GB/全网通/5G版） AI焕采视频美颜，星钻工艺，6400万水光人像四摄</t>
+          <t>OPPO Reno5（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11225,7 +11224,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OPPO Reno5 Pro（8GB/128GB/全网通/5G版） 闪电启动，星钻光芒设计，6400万水光人像四摄</t>
+          <t>OPPO Reno5 Pro（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11300,7 +11299,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>华为Mate40 Pro（8GB/256GB/全网通/5G版/玻璃版） 麒麟9000，88°超曲环幕屏，66W快充，50W无线快充，IP68级防水防尘，3D人脸识别</t>
+          <t>华为Mate40 Pro（8GB/256GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11375,7 +11374,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>华为Mate40 Pro+（12GB/256GB/全网通/5G版） 麒麟9000，88°超曲环幕屏，66W快充，50W无线快充，超感知徕卡电影五摄，3D人脸识别</t>
+          <t>华为Mate40 Pro+（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11450,7 +11449,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>华为Mate40 RS保时捷版（12GB/512GB/全网通/5G版） 麒麟9000，88°超曲环幕屏，超感知徕卡电影五摄，星星钻设计镜头，66W快充，50W无线快充</t>
+          <t>华为Mate40 RS保时捷版（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11525,7 +11524,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>华为Mate30E Pro（8GB/128GB/全网通/5G版/玻璃版） 麒麟990E，88°超曲面环幕屏，双4000万徕卡电影影像</t>
+          <t>华为Mate30E Pro（8GB/128GB/全网通/5G版/玻璃版）</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11600,7 +11599,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>华为畅享20（4GB/128GB/全网通/5G版） 6.6英寸影音大屏，5000mAh大电池，AI三摄闪拍</t>
+          <t>华为畅享20（4GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11675,7 +11674,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>三星Galaxy S20 FE（8GB/128GB/全网通/5G版） 3倍光学变焦，AI一键多拍，高通骁龙 865</t>
+          <t>三星Galaxy S20 FE（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11750,7 +11749,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>华为nova 8 SE（8GB/128GB/全网通/5G版/标配版） 66W超级快充，6400万像素超清四摄，四重护眼</t>
+          <t>华为nova 8 SE（8GB/128GB/全网通/5G版/标配版）</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11825,7 +11824,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>华为nova 8（8GB/128GB/全网通/5G版） 66W超级快充，麒麟985，6400万魅力四摄，7.64mm纤薄机身，3D石墨烯散热</t>
+          <t>华为nova 8（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11900,7 +11899,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>华为nova 8 Pro（8GB/128GB/全网通/5G版） 麒麟985，通信5G四网协同，Wi-Fi 6+，6400万魅力四摄，66W超级快充，120Hz刷新率</t>
+          <t>华为nova 8 Pro（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11975,7 +11974,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OPPO A32（8GB/128GB/全网通） 5000mAh大电池，18W快充，90Hz刷新率，89.2%屏占比</t>
+          <t>OPPO A32（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -12050,7 +12049,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OPPO Reno4 SE（8GB/128GB/全网通/5G版） 65W超级闪充，小光芒设计，3200万前置自拍，双模5G</t>
+          <t>OPPO Reno4 SE（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -12125,7 +12124,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 3（128GB） A15仿生芯片，IP67防尘防水，前置触控ID，后置1200万像素</t>
+          <t>苹果iPhone SE 3（128GB）</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12196,7 +12195,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>苹果iPhone 13（128GB/全网通/5G版） 解锁超能力，超先进双摄系统，A15仿生芯片</t>
+          <t>苹果iPhone 13（128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12267,7 +12266,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro（128GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro（128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -12338,7 +12337,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro Max（128GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro Max（128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -12407,7 +12406,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>vivo X60（8GB/128GB/全网通/5G版） 蔡司光学镜头，微云台黑光夜视2.0，三星5nm旗舰芯片，双模5G</t>
+          <t>vivo X60（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12482,7 +12481,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>vivo Y73s（8GB/128GB/全网通/5G版） AMOLED高清护眼屏，双引擎闪充，4800万后置影像系统</t>
+          <t>vivo Y73s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -12557,7 +12556,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>三星W21（12GB/512GB/全网通/5G版） 折叠屏，双卡双待，骁龙865+</t>
+          <t>三星W21（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12632,7 +12631,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>vivo X60 Pro（12GB/256GB/全网通/5G版） 蔡司光学镜头，超稳微云台四摄，三星5nm旗舰芯片，双模5G</t>
+          <t>vivo X60 Pro（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -12707,7 +12706,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>华为nova 7 SE（8GB/128GB/5G版/全网通/活力版） 6400万高清AI四摄，6.5英寸极点全面屏，40W华为超级快充，4000mAh大电池</t>
+          <t>华为nova 7 SE（8GB/128GB/5G版/全网通/活力版）</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12782,7 +12781,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>苹果iPhone 12（4GB/128GB/全网通/5G版） A14仿生芯片，超视网膜XDR显示屏，超瓷晶面板，双模5G</t>
+          <t>苹果iPhone 12（4GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12853,7 +12852,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>苹果iPhone 12（4GB/256GB/全网通/5G版） A14仿生芯片，超视网膜XDR显示屏，超瓷晶面板，双模5G</t>
+          <t>苹果iPhone 12（4GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12924,7 +12923,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 mini（4GB/256GB/全网通/5G版） 超瓷晶面板，A14仿生，双模5G</t>
+          <t>苹果iPhone 12 mini（4GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12995,7 +12994,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 mini（4GB/128GB/全网通/5G版） 超瓷晶面板，A14仿生，双模5G</t>
+          <t>苹果iPhone 12 mini（4GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -13066,7 +13065,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro（6GB/256GB/全网通/5G版） 5G加身，超视网膜XDR显示屏，A14仿生速度超快</t>
+          <t>苹果iPhone 12 Pro（6GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13137,7 +13136,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro（6GB/512GB/全网通/5G版） 5G网络，Pro级摄像头系统，超瓷晶面板，IP68级抗水</t>
+          <t>苹果iPhone 12 Pro（6GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13208,7 +13207,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro Max（6GB/256GB/全网通/5G版） A14仿生，激光雷达扫描仪，Pro级摄像头系统</t>
+          <t>苹果iPhone 12 Pro Max（6GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -13283,7 +13282,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>苹果iPhone 12 Pro Max（6GB/512GB/全网通/5G版） Pro级摄像头系统，杜比视界，5G加身，超瓷晶面板</t>
+          <t>苹果iPhone 12 Pro Max（6GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -13358,7 +13357,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vivo Y3s（4GB/128GB/全网通） 5000mAh大电池，AI智慧双摄，面部识别</t>
+          <t>vivo Y3s（4GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -13433,7 +13432,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HUAWEI Mate50（8GB+128GB） 超光变XMAGE影像，6.7英寸，鸿蒙操作系统3.0</t>
+          <t>HUAWEI Mate50（8GB+128GB）</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -13508,7 +13507,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>华为Mate40 RS保时捷版（12GB/256GB/全网通/5G版） 麒麟9000，88°超曲环幕屏，超感知徕卡电影五摄，星星钻设计镜头，66W快充，50W无线快充</t>
+          <t>华为Mate40 RS保时捷版（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13583,7 +13582,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>荣耀V40（8GB/128GB/全网通/5G版） 120Hz刷新率，立体声双扬声器，66W超级闪充，线性马达</t>
+          <t>荣耀V40（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13658,7 +13657,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HUAWEI Mate50 Pro（8GB+256GB） 鸿蒙系统3.0，IP68等级防尘防水，XMAGE影像</t>
+          <t>HUAWEI Mate50 Pro（8GB+256GB）</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -13733,7 +13732,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>三星Galaxy S21 Ultra（12GB/256GB/全网通/5G版） 骁龙888，1.08亿像素，120Hz护目屏，支持Spen</t>
+          <t>三星Galaxy S21 Ultra（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -13809,7 +13808,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>vivo X60 Pro+（8GB/128GB/全网通/5G版） 微云台双主摄，骁龙888，蔡司联合影像系统</t>
+          <t>vivo X60 Pro+（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13884,7 +13883,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>vivo S7e（8GB/128GB/全网通/5G版） 6400万超高清主摄，33W闪充，双模5G</t>
+          <t>vivo S7e（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13959,7 +13958,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold3（12GB/512GB/全网通/5G版） CPU型号:高通 骁龙888 RAM容量:12GB CPU频率:2.84GHz X1*1+2.4GHz A78*3+1.8GHz A55*4 ROM容量:512GB 核心数:八核 主屏尺寸:7.6英寸 屏幕类型:全面屏（屏下式），折叠屏</t>
+          <t>三星Galaxy Z Fold3（12GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -14034,7 +14033,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>三星Galaxy S21+（8GB/256GB/全网通/5G版） 骁龙888，超高清专业摄像，120Hz护目屏</t>
+          <t>三星Galaxy S21+（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14110,7 +14109,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>三星Galaxy A52（8GB/128GB/全网通/5G版） 120Hz全视屏，IP67级防尘防水，多功能NFC</t>
+          <t>三星Galaxy A52（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -14185,7 +14184,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>华为P50 Pro（8GB/256GB/全网通/麒麟9000） 万象双环设计，120Hz OLED显示屏，IP68防尘防水，鸿蒙2.0系统</t>
+          <t>华为P50 Pro（8GB/256GB/全网通/麒麟9000）</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -14256,7 +14255,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 50E（128GB） 500万像素，鸿蒙系统3.0，超光变XMAGE影像</t>
+          <t>HUAWEI Mate 50E（128GB）</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -14331,7 +14330,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 50 RS 保时捷版（12GB/512GB） 5000万像素超光变镜头，鸿蒙操作系统3.0，50w无线充电</t>
+          <t>HUAWEI Mate 50 RS 保时捷版（12GB/512GB）</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14406,7 +14405,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>OPPO A53（4GB/128GB/全网通/5G版） AI智能三摄，双模5G，天玑720</t>
+          <t>OPPO A53（4GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -14481,7 +14480,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>vivo X Note（12GB/256GB） 7英寸2K E5超感宽幕，5000mAh大电池，3D大面积指纹，旗舰骁龙8 Gen1</t>
+          <t>vivo X Note（12GB/256GB）</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -14556,7 +14555,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip3（8GB/256GB/全网通/5G版） CPU型号:高通 骁龙888 RAM容量:8GB CPU频率:2.84GHz X1*1+2.4GHz A78*3+1.8GHz A55*4 ROM容量:256GB 核心数:八核 主屏尺寸:6.7英寸 屏幕类型:全面屏（极点屏），折叠屏</t>
+          <t>三星Galaxy Z Flip3（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -14631,7 +14630,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>vivo Y52s（8GB/128GB/全网通/5G版） 后置4800万双摄，5000mAh电池，90Hz高刷</t>
+          <t>vivo Y52s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -14706,7 +14705,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>华为畅享20 SE（4GB/128GB/全网通） 90.3%屏占比，22.5W超级快充，5000mAh大电池，1300万后置三摄</t>
+          <t>华为畅享20 SE（4GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -14781,7 +14780,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>华为Mate40E（8GB/128GB/全网通/5G版） 麒麟990E，68°曲面屏，超感知徕卡影像</t>
+          <t>华为Mate40E（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14856,7 +14855,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>vivo Y31s（6GB/128GB/全网通/5G版） 双模5G，5000mAh电池，2.5D超质感机身，90Hz高刷护眼屏</t>
+          <t>vivo Y31s（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -14931,7 +14930,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HUAWEI P60（8GB+256GB） 超聚光XMAGE影像，双向北斗卫星消息，鸿蒙系统3.1</t>
+          <t>HUAWEI P60（8GB+256GB）</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -15006,7 +15005,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HUAWEI P60 Pro（8GB+256GB） 超聚光夜视长焦，昆仑玻璃，双向北斗卫星消息</t>
+          <t>HUAWEI P60 Pro（8GB+256GB）</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -15081,7 +15080,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>vivo X70（8GB/256GB/全网通/5G版） 联发科天玑1200vivo定制处理器，4000万像素微云台主摄，蔡司专业影像，萤石AG工艺</t>
+          <t>vivo X70（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -15156,7 +15155,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>vivo X70 Pro（12GB/256GB/全网通/5G版） 三星Exynos1080处理器，5000万像素微云台主摄，专业影像芯片 V1，全新萤石AG工艺</t>
+          <t>vivo X70 Pro（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15231,7 +15230,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OPPO A93（8GB/256GB/全网通/5G版） 90Hz刷新率，5000mAh大电池，后置4800W四摄</t>
+          <t>OPPO A93（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15306,7 +15305,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>vivo S7t（8GB/128GB/全网通/5G版） 天玑820，后置三摄，双模5G</t>
+          <t>vivo S7t（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -15381,7 +15380,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OPPO A55（6GB/128GB/全网通/5G版） 5000mAh电池，后置AI三摄，天玑700，亿级像素超清画质</t>
+          <t>OPPO A55（6GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -15456,7 +15455,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 mini（128GB/全网通/5G版） 解锁超能力，超先进双摄系统，A15仿生芯片</t>
+          <t>苹果iPhone 13 mini（128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -15527,7 +15526,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>华为P40（8GB/128GB/全网通/4G版） 麒麟990，徕卡三摄，30倍数字变焦</t>
+          <t>华为P40（8GB/128GB/全网通/4G版）</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -15602,7 +15601,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>vivo S9（8GB/128GB/全网通/5G版） 约7.35mm纤薄机身，全球首发天玑1100，双极夜柔光灯</t>
+          <t>vivo S9（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -15677,7 +15676,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>三星Galaxy S21 FE（8GB/128GB/5G版） 高通骁龙888处理器，第二代动态AMOLED屏幕，30倍空间变焦，AI一键多拍</t>
+          <t>三星Galaxy S21 FE（8GB/128GB/5G版）</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -15752,7 +15751,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>华为Mate X2（8GB/512GB/全网通/5G版） 麒麟9000旗舰芯片，无缝鹰翼折叠，超感知徕卡四摄</t>
+          <t>华为Mate X2（8GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -15827,7 +15826,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>荣耀X20（8GB/128GB/全网通/5G版） 联发科天玑900处理器，6400万超清影像，66W超级快充，120Hz高刷屏</t>
+          <t>荣耀X20（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -15902,7 +15901,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>vivo S9（12GB/256GB/全网通/5G版） 约7.35mm纤薄机身，全球首发天玑1100，双极夜柔光灯</t>
+          <t>vivo S9（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -15977,7 +15976,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>vivo S9e（8GB/128GB/全网通/5G版） 潮流设计，3200万极夜自拍，6400万超清后置</t>
+          <t>vivo S9e（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -16052,7 +16051,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>vivo Y31s（6GB/128GB/全网通/5G版/标准版） 天玑700，5G+5G双卡双待，5000mAh大电池，18W双引擎闪充，AI智慧影像</t>
+          <t>vivo Y31s（6GB/128GB/全网通/5G版/标准版）</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -16127,7 +16126,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>荣耀V40轻奢版（8GB/128GB/全网通/5G版） 轻薄超曲屏，10亿色显示，66W超级快充，3200W美颜自拍</t>
+          <t>荣耀V40轻奢版（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -16202,7 +16201,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OPPO Reno6（12GB/256GB/全网通/5G版） 6400万像素水光镜头，65w超级快充，90Hz高感屏，36个月流畅护航</t>
+          <t>OPPO Reno6（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -16277,7 +16276,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OPPO Reno6 Pro（12GB/256GB/全网通/5G版） 联发科天玑1200处理器，6400万像素四摄，90Hz曲面屏，，65w超级快充</t>
+          <t>OPPO Reno6 Pro（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -16352,7 +16351,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>华为nova 9（8GB/128GB/全网通） 骁龙778G处理器，HarmonyOS 2操作系统，3200万前置Vlog镜头，66W超级快充</t>
+          <t>华为nova 9（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -16423,7 +16422,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>三星Galaxy S22 Ultra（12GB/256GB/5G版） 超凡卓越影像系统，大屏S Pen书写，全新一代骁龙8移动平台</t>
+          <t>三星Galaxy S22 Ultra（12GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -16499,7 +16498,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>荣耀50（8GB/256GB/全网通/5G版） 高通骁龙778G处理器，亿级像素高清影像，66W超级闪充，120Hz高刷超曲屏</t>
+          <t>荣耀50（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -16574,7 +16573,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>荣耀畅玩20（6GB/128GB/全网通） 5000mAh大电池，128GB大容量存储，6.5英寸高清护眼屏</t>
+          <t>荣耀畅玩20（6GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -16649,7 +16648,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>荣耀Magic3（8GB/128GB/全网通/5G版） 高通骁龙888处理器，6.76英寸超曲屏，多主摄计算摄影，66W超级快充</t>
+          <t>荣耀Magic3（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -16724,7 +16723,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>荣耀Play5（8GB/128GB/全网通/5G版） 66W超级快充，7.46mm超薄设计，6400万超清四摄，OLED真彩屏</t>
+          <t>荣耀Play5（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -16799,7 +16798,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>华为nova 9 Pro（8GB/128GB/全网通） 骁龙778G处理器，HarmonyOS 2操作系统，双3200万前置Vlog镜头，100W超级快充</t>
+          <t>华为nova 9 Pro（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -16870,7 +16869,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>荣耀50 Pro（8GB/256GB/全网通/5G版） 高通骁龙778G处理器，亿级像素高清影像，100W超级闪充，120Hz高刷超曲屏</t>
+          <t>荣耀50 Pro（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -16945,7 +16944,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>三星Galaxy F52（8GB/128GB/全网通/5G版） 高通骁龙750G移动平台，120Hz高刷新率全面屏，6400万像素四摄，玻璃机身</t>
+          <t>三星Galaxy F52（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -17020,7 +17019,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>vivo Y70t（8GB/128GB/全网通/5G版） Exynos 880处理器，4800万AI三摄，零感水冷散热，侧面指纹识别</t>
+          <t>vivo Y70t（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -17095,7 +17094,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>vivo X70 Pro+（12GB/256GB/全网通/5G版） 高通骁龙888Plus处理器，120Hz三星E5 LTPO屏，专业影像芯片 V1，微云台双主摄</t>
+          <t>vivo X70 Pro+（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -17170,7 +17169,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>荣耀Play5T（8GB/128GB/全网通） 虎贲T610处理器，5000毫安大容量电池，22.5w超级闪充</t>
+          <t>荣耀Play5T（8GB/128GB/全网通）</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -17245,7 +17244,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>荣耀50 SE（8GB/128GB/全网通/5G版） 天玑900处理器，亿级像素高清影像，66W超级闪充，120Hz高刷屏</t>
+          <t>荣耀50 SE（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -17320,7 +17319,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>vivo S10（8GB/256GB/全网通/5G版） 联发科天玑1100处理器，前置4400万自然柔光人像，4G内存融合技术，44w闪充</t>
+          <t>vivo S10（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -17395,7 +17394,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>vivo Y53s（8GB/128GB/全网通/5G版） 高通骁龙480处理器，5000mAh大电池，6400万超清主摄， 90Hz高刷屏，双模5G全网通</t>
+          <t>vivo Y53s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -17470,7 +17469,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>OPPO A93s（8GB/256GB/全网通/5G版） 联发科天玑700处理器，18W双芯快充，90Hz高刷屏，全面屏</t>
+          <t>OPPO A93s（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -17545,7 +17544,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>vivo X Fold（12GB/256GB） 2K+120Hz E5折叠巨幕，航天级浮翼式铰链，双屏幕指纹，旗舰骁龙8 Gen1</t>
+          <t>vivo X Fold（12GB/256GB）</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -17620,7 +17619,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>vivo S10 Pro（12GB/256GB/全网通/5G版） 联发科天玑1100处理器，前置4400万自然柔光人像，4G内存融合技术，44w闪充</t>
+          <t>vivo S10 Pro（12GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -17695,7 +17694,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>荣耀Magic3 Pro（8GB/256GB/全网通/5G版） 高通骁龙888Plus处理器，6.76英寸超曲屏，多主摄计算摄影，有线无线双超级快充</t>
+          <t>荣耀Magic3 Pro（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -17770,7 +17769,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>三星Galaxy S22+（8GB/256GB/5G版） 超凡卓越影像系统，超亮顺滑全视屏，全新一代骁龙8移动平台</t>
+          <t>三星Galaxy S22+（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -17846,7 +17845,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>华为Mate Xs 2（8GB/256GB/4G版） 新一代鹰翼折叠，SD Optics计算光学，高硅负极电池，四网并发</t>
+          <t>华为Mate Xs 2（8GB/256GB/4G版）</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -17918,7 +17917,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>苹果iPhone 14（128GB） 超先进双摄系统，A15仿生芯片，6.1英寸屏幕</t>
+          <t>苹果iPhone 14（128GB）</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -17993,7 +17992,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OPPO Find X5（8GB/256GB/5G版） 屏幕尺寸:6.55英寸 屏幕材质:OLED 屏幕类型:全面屏（左上挖孔屏），曲面屏 HDR技术:HDR 10+ CPU型号:高通 骁龙888 CPU核心数:八核 RAM容量:8GB</t>
+          <t>OPPO Find X5（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -18064,7 +18063,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OPPO Find X5 Pro（12GB/256GB/5G版） 全新骁龙8，自研影像芯片，哈苏影像，5000万双主摄，120Hz，80W超级闪充</t>
+          <t>OPPO Find X5 Pro（12GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -18139,7 +18138,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OPPO Reno7（8GB/128GB/全网通/5G版） 高通骁龙778G处理器，超感光猫眼镜头，航天级星雨光刻工艺,6400万大师人像三摄</t>
+          <t>OPPO Reno7（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -18214,7 +18213,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Plus（128GB） 卫星通讯，60Hz屏幕，A15处理器</t>
+          <t>苹果iPhone 14 Plus（128GB）</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -18289,7 +18288,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>荣耀X30 Max（8GB/128GB/全网通/5G版） 联发科天玑900处理器，7.09英寸护眼阳光屏，5000mAh大电池，立体声双扬声器</t>
+          <t>荣耀X30 Max（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -18364,7 +18363,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>vivo S10e（8GB/256GB/全网通/5G版） 联发科天玑900处理器，6400万超清影像，66W超级快充，7.49mm轻薄机身</t>
+          <t>vivo S10e（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -18439,7 +18438,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>苹果iPhone 13（256GB/全网通/5G版） 解锁超能力，超先进双摄系统，A15仿生芯片</t>
+          <t>苹果iPhone 13（256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -18510,7 +18509,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>苹果iPhone 13（512GB/全网通/5G版） 解锁超能力，超先进双摄系统，A15仿生芯片</t>
+          <t>苹果iPhone 13（512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -18581,7 +18580,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 mini（256GB/全网通/5G版） A15仿生芯片，超瓷晶面板，超视网膜XDR显示屏</t>
+          <t>苹果iPhone 13 mini（256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -18652,7 +18651,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 mini（512GB/全网通/5G版） A15仿生芯片，超瓷晶面板，超视网膜XDR显示屏</t>
+          <t>苹果iPhone 13 mini（512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -18723,7 +18722,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro（256GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro（256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -18794,7 +18793,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro（512GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro（512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -18865,7 +18864,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro（1TB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro（1TB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -18936,7 +18935,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro Max（256GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro Max（256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -19005,7 +19004,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro Max（512GB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro Max（512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -19074,7 +19073,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>苹果iPhone 13 Pro Max（1TB/全网通/5G版） A15仿生芯片，超视网膜XDR显示屏，Pro级摄像头系统，ProMotion自适应刷新率技术</t>
+          <t>苹果iPhone 13 Pro Max（1TB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -19143,7 +19142,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro（128GB） 超瓷晶面板，视网膜XDR显示屏，Pro级摄像头系统</t>
+          <t>苹果iPhone 14 Pro（128GB）</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19218,7 +19217,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro Max（128GB） A16处理器，4800万像素，120Hz刷新率</t>
+          <t>苹果iPhone 14 Pro Max（128GB）</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19293,7 +19292,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>vivo S12（8GB/256GB/5G版） 一亿像素，4400万前置，全功能NFC</t>
+          <t>vivo S12（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19368,7 +19367,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>三星W22（16GB/512GB/全网通/5G版） 主屏尺寸:7.6英寸 屏幕类型:全面屏（屏下式），折叠屏 主屏材质:Dynamic AMOLED 2X 出厂系统内核:Android 12 主屏分辨率:2208x1768像素 屏幕像素密度:374ppi HDR技术:HDR 10+</t>
+          <t>三星W22（16GB/512GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -19443,7 +19442,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>vivo Y55s（8GB/128GB/全网通/5G版） 6000mAh金标巨能量电池，5000万像素超清影像，200%大音量超级扬声器</t>
+          <t>vivo Y55s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -19518,7 +19517,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>vivo T1（8GB/256GB/全网通/5G版） 高通骁龙778G处理器，120Hz高刷原色屏，环绕立体声双扬</t>
+          <t>vivo T1（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -19593,7 +19592,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>荣耀X30i（8GB/128GB/全网通/5G版） 联发科天玑810处理器，4800万超清三摄，7.45mm厚度，22.5w快充</t>
+          <t>荣耀X30i（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -19668,7 +19667,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>vivo Y76s（8GB/128GB/全网通/5G版） 联发科天玑810处理器，44w有线充电，后置5000万像素双摄</t>
+          <t>vivo Y76s（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -19743,7 +19742,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>华为畅享20e（4GB/64GB/全网通） 屏幕尺寸:6.3英寸 屏幕材质:LCD 分辨率:1600x800像素 像素密度:278ppi 屏幕类型:全面屏（水滴屏） CPU型号:联发科 Helio P35（MT6765） CPU核心数:八核</t>
+          <t>华为畅享20e（4GB/64GB/全网通）</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -19818,7 +19817,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>vivo X80（12GB/256GB） 蔡司T*光学镜头，自研影像芯片V1+，4nm旗舰芯片</t>
+          <t>vivo X80（12GB/256GB）</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -19893,7 +19892,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>vivo X80 Pro（12GB/256GB） 蔡司影像，自研芯片V1+，双电芯80W闪充</t>
+          <t>vivo X80 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -19968,7 +19967,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>vivo S12 Pro（8GB/256GB/5G版） 联发科天玑1200处理器，前置5000万像素双摄，7.36mm超薄曲面屏，微米级焕肤塑颜算法</t>
+          <t>vivo S12 Pro（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -20043,7 +20042,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>荣耀60（8GB/128GB/全网通/5G版） 骁龙778G 5G处理器，1亿像素超清影像，AI手势识别，66W智慧超级闪充</t>
+          <t>荣耀60（8GB/128GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -20118,7 +20117,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>荣耀60 Pro（8GB/256GB/全网通/5G版） 骁龙778G 5G处理器，1亿像素超清影像，AI手势识别，66W智慧超级闪充</t>
+          <t>荣耀60 Pro（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -20193,7 +20192,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>荣耀Magic4（8GB/256GB） 骁龙8 Gen1处理器，1920Hz高频PWM调光，高规格7P广角主摄</t>
+          <t>荣耀Magic4（8GB/256GB）</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -20269,7 +20268,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>vivo Y76s（8GB/256GB/全网通/5G版） 联发科天玑810处理器，44w有线充电，后置5000万像素双摄</t>
+          <t>vivo Y76s（8GB/256GB/全网通/5G版）</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -20344,7 +20343,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>OPPO Find N（8GB/256GB/5G版） 骁龙888，黄金折叠比例，多角度自由悬停，120Hz镜面折叠屏</t>
+          <t>OPPO Find N（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -20419,7 +20418,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>荣耀X30（8GB/128GB/5G版） 骁龙695处理器，66w超级快充，120Hz全视屏，4800万像素后置三摄</t>
+          <t>荣耀X30（8GB/128GB/5G版）</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -20494,7 +20493,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>荣耀畅玩30 Plus（6GB/128GB/5G版） 联发科天玑700处理器，22.5w超级快充，5000mAh长续航，6.74英寸高刷护眼大屏</t>
+          <t>荣耀畅玩30 Plus（6GB/128GB/5G版）</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -20569,7 +20568,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>三星Galaxy A53（8GB/128GB） 三星猎户座1280处理器，120Hz超流畅滚屏，后置四摄，IP67级防尘防水</t>
+          <t>三星Galaxy A53（8GB/128GB）</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -20644,7 +20643,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>vivo Y32（8GB/128GB） 屏幕尺寸:6.51英寸 屏幕材质:LCD 分辨率:1600x720像素 像素密度:269ppi 屏幕类型:全面屏（水滴屏） CPU型号:高通 骁龙680 4G 核心数:八核</t>
+          <t>vivo Y32（8GB/128GB）</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -20719,7 +20718,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>vivo S12（12GB/256GB/5G版） 一亿像素，4400万前置，全功能NFC</t>
+          <t>vivo S12（12GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -20794,7 +20793,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>OPPO A96（8GB/256GB/5G版） 高通骁龙695处理器，双子星环呼吸灯，OLED超清护眼屏</t>
+          <t>OPPO A96（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -20869,7 +20868,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>vivo Y10 t1版（4GB/128GB） 屏幕尺寸:6.5英寸 屏幕材质:LCD 分辨率:1600x720像素 像素密度:270ppi CPU型号:联发科 Helio P70 CPU核心数:八核 RAM容量:4GB</t>
+          <t>vivo Y10 t1版（4GB/128GB）</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -20944,7 +20943,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>OPPO Reno8（8GB/256GB） 天玑1300，流云双镜设计，36个月流畅双引擎</t>
+          <t>OPPO Reno8（8GB/256GB）</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -21019,7 +21018,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>荣耀Magic4 Pro（12GB/256GB） 骁龙8 Gen1处理器，IP68级防尘抗水，1920Hz高频PWM调光，全时HDR技术</t>
+          <t>荣耀Magic4 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -21095,7 +21094,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>华为Mate40E Pro（8GB/256GB/5G版） 屏幕尺寸:6.76英寸 屏幕材质:OLED 分辨率:2772x1344像素 屏幕类型:全面屏（左上挖孔屏），曲面屏 HDR技术:支持 CPU型号:海思 麒麟 9000L CPU核心数:六核</t>
+          <t>华为Mate40E Pro（8GB/256GB/5G版）</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -21166,7 +21165,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>华为P50E（8GB/256GB） 骁龙778G处理器，万象双环设计，66W有线超级快充，原色双影像单元</t>
+          <t>华为P50E（8GB/256GB）</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -21237,7 +21236,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>OPPO K10（8GB/256GB） 天玑8000-MAX，金刚石VC液冷散热，120Hz高帧变速屏</t>
+          <t>OPPO K10（8GB/256GB）</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21312,7 +21311,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>华为nova 9 SE（8GB/128GB） 一亿像素超清摄影，创新Vlog体验，66W超级快充，1.05mm超窄边框</t>
+          <t>华为nova 9 SE（8GB/128GB）</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -21383,7 +21382,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 3（64GB） A15仿生芯片，IP67防尘防水，前置触控ID，后置1200万像素</t>
+          <t>苹果iPhone SE 3（64GB）</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -21454,7 +21453,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>苹果iPhone SE 3（256GB） A15仿生芯片，IP67防尘防水，前置触控ID，后置1200万像素</t>
+          <t>苹果iPhone SE 3（256GB）</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -21525,7 +21524,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>vivo Y33s（8GB/128GB） 18W闪充，5000mAh大电池，后置1300万清晰影像</t>
+          <t>vivo Y33s（8GB/128GB）</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -21600,7 +21599,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>vivo S15e（12GB/256GB） 纳米丝绒内镀工艺，70万跑分5nm芯片，66W闪充，5000万超质感人像</t>
+          <t>vivo S15e（12GB/256GB）</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -21675,7 +21674,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>vivo S15（8GB/128GB） 高通骁龙870，超感光影像系统，电影感人像大片</t>
+          <t>vivo S15（8GB/128GB）</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -21750,7 +21749,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>vivo S15 Pro（8GB/256GB） 天玑8100，独立显示芯片Pro，索尼定制大底主摄</t>
+          <t>vivo S15 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -21825,7 +21824,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>三星Galaxy S23（8GB/128GB） 超视觉夜拍，第二代骁龙8，超亮全视护眼屏</t>
+          <t>三星Galaxy S23（8GB/128GB）</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -21900,7 +21899,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>三星Galaxy S23 Ultra（8GB/256GB） 超视觉夜拍，第二代骁龙8，S Pen书写</t>
+          <t>三星Galaxy S23 Ultra（8GB/256GB）</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -21975,7 +21974,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>三星Galaxy S23+（8GB/256GB） 超视觉夜拍，超亮全视护眼屏，第二代骁龙8</t>
+          <t>三星Galaxy S23+（8GB/256GB）</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -22050,7 +22049,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>华为nova 10（8GB/128GB） 前置6000万超广角镜头，66W超级快充</t>
+          <t>华为nova 10（8GB/128GB）</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -22121,7 +22120,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HUAWEI nova 10 SE（128GB） 一亿像素，质感人像，超级门禁卡</t>
+          <t>HUAWEI nova 10 SE（128GB）</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -22196,7 +22195,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>华为nova 10 Pro（8GB/128GB） 前置6000万追焦双摄，100W超级快充</t>
+          <t>华为nova 10 Pro（8GB/128GB）</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22267,7 +22266,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>荣耀70（8GB/256GB） IMX800三主摄，双曲屏设计，高通骁龙778G Plus</t>
+          <t>荣耀70（8GB/256GB）</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -22342,7 +22341,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>荣耀70 Pro（8GB/256GB） IMX800三主摄，天玑8000处理器，100w超级快充</t>
+          <t>荣耀70 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -22417,7 +22416,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X3（12GB+256GB） 双向北斗卫星消息，超感知XMAGE影像，昆仑玻璃</t>
+          <t>HUAWEI Mate X3（12GB+256GB）</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -22492,7 +22491,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>vivo X80（8GB/256GB） 蔡司T*光学镜头，自研影像芯片V1+，4nm旗舰芯片</t>
+          <t>vivo X80（8GB/256GB）</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -22567,7 +22566,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>vivo S15e（8GB/128GB） 纳米丝绒内镀工艺，70万跑分5nm芯片，66W闪充，5000万超质感人像</t>
+          <t>vivo S15e（8GB/128GB）</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -22642,7 +22641,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold4（12GB/512GB） 旗舰影像，沉浸大屏，超强生产力</t>
+          <t>三星Galaxy Z Fold4（12GB/512GB）</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -22717,7 +22716,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip4（8GB/256GB） 小屏大用，免手持，掌心折叠</t>
+          <t>三星Galaxy Z Flip4（8GB/256GB）</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -22788,7 +22787,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>荣耀畅玩30（4GB/128GB） 5000mAh大电池，128GB大储存，高通骁龙5G芯</t>
+          <t>荣耀畅玩30（4GB/128GB）</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -22863,7 +22862,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>vivo S15（12GB/256GB） 高通骁龙870，超感光影像系统，电影感人像大片</t>
+          <t>vivo S15（12GB/256GB）</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -22938,7 +22937,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>vivo T2x（8GB/256GB） 天玑1300，6000mAh巨能量电池，144Hz高刷屏</t>
+          <t>vivo T2x（8GB/256GB）</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -23013,7 +23012,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>华为畅享 50（6GB/128GB） 6000mAh大电池，22.5W超能续航 ，6.75英寸影音大屏</t>
+          <t>华为畅享 50（6GB/128GB）</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -23080,7 +23079,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>华为畅享 50 Pro（8GB/128GB） 40W快充，6.7英寸屏幕，5000万像素后置</t>
+          <t>华为畅享 50 Pro（8GB/128GB）</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -23151,7 +23150,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>华为nova 10 Pro（8GB/256GB） 前置6000万追焦双摄，100W超级快充</t>
+          <t>华为nova 10 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -23222,7 +23221,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>vivo Y77（12GB/256GB） 天玑930，120Hz高刷，5000万像素后置</t>
+          <t>vivo Y77（12GB/256GB）</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -23297,7 +23296,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>OPPO A97（12GB/256GB） 立体声双扬声器，5000毫安电池，4800万像素</t>
+          <t>OPPO A97（12GB/256GB）</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -23364,7 +23363,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>vivo Y77e（6GB/128GB） 200%大音量，5000毫安电池，超清护眼屏</t>
+          <t>vivo Y77e（6GB/128GB）</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -23439,7 +23438,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>vivo X90（8GB/128GB） 天玑 9200，自研芯片V2，VCS仿生光谱大底主摄</t>
+          <t>vivo X90（8GB/128GB）</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -23514,7 +23513,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>OPPO Find X6（12GB/256GB） 哈苏影像，80W闪充，天玑9200</t>
+          <t>OPPO Find X6（12GB/256GB）</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -23589,7 +23588,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>OPPO Find X6 Pro（12GB/256GB） 骁龙8，5000mAh，100W闪充</t>
+          <t>OPPO Find X6 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -23664,7 +23663,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>荣耀Magic5（8GB/256GB） 骁龙8Gen2，MagicOS7.1，6.73英寸OLED屏，66W有线快充</t>
+          <t>荣耀Magic5（8GB/256GB）</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -23739,7 +23738,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>荣耀Magic5至臻版（16GB/512GB） 第二代骁龙8，独立显示芯片，青海湖电池</t>
+          <t>荣耀Magic5至臻版（16GB/512GB）</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -23814,7 +23813,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>荣耀X40（6GB/128GB） OLED屏, 硬核曲屏，5000万摄像</t>
+          <t>荣耀X40（6GB/128GB）</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -23889,7 +23888,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>HUAWEI Mate50（8GB+256GB） 超光变XMAGE影像，6.7英寸，鸿蒙操作系统3.0</t>
+          <t>HUAWEI Mate50（8GB+256GB）</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -23964,7 +23963,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>HUAWEI Mate50（8GB+512GB） 超光变XMAGE影像，6.7英寸，鸿蒙操作系统3.0</t>
+          <t>HUAWEI Mate50（8GB+512GB）</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -24039,7 +24038,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60（12GB/256GB） 双向北斗卫星消息，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60（12GB/256GB）</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -24110,7 +24109,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60 Pro（12GB/256GB） 卫星通话，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -24181,7 +24180,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>华为Mate 60 RS 非凡大师（16GB/512GB） RAM容量:16GB ROM容量:512GB 电池容量:5000mAh 后置摄像头1 后置摄像头:4800万像素 有线充电:88 W（20V/4.4A） 前置摄像头1 前置摄像头:1300万像素 主 屏幕尺寸:6.82英寸</t>
+          <t>华为Mate 60 RS 非凡大师（16GB/512GB）</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -24248,7 +24247,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>苹果iPhone 15（128GB） 灵动岛，4800万像素主摄，2倍长焦</t>
+          <t>苹果iPhone 15（128GB）</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -24323,7 +24322,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Plus（128GB） 灵动岛，6.7英寸，4800万像素主摄</t>
+          <t>苹果iPhone 15 Plus（128GB）</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -24398,7 +24397,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro（128GB） 钛金属，A17 Pro芯片，4800万像素主摄</t>
+          <t>苹果iPhone 15 Pro（128GB）</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -24471,7 +24470,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro Max（256GB） 钛金属，6.7英寸，A17 Pro芯片</t>
+          <t>苹果iPhone 15 Pro Max（256GB）</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -24544,7 +24543,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Plus（256GB） 卫星通讯，60Hz屏幕，A15处理器</t>
+          <t>苹果iPhone 14 Plus（256GB）</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -24619,7 +24618,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Plus（512GB） 卫星通讯，60Hz屏幕，A15处理器</t>
+          <t>苹果iPhone 14 Plus（512GB）</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -24694,7 +24693,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>苹果iPhone 14（256GB） 超先进双摄系统，A15仿生芯片，6.1英寸屏幕</t>
+          <t>苹果iPhone 14（256GB）</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -24769,7 +24768,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>苹果iPhone 14（512GB） 超先进双摄系统，A15仿生芯片，6.1英寸屏幕</t>
+          <t>苹果iPhone 14（512GB）</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -24844,7 +24843,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro （256GB） 超瓷晶面板，视网膜XDR显示屏，Pro级摄像头系统</t>
+          <t>苹果iPhone 14 Pro （256GB）</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -24919,7 +24918,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro （512GB） 超瓷晶面板，视网膜XDR显示屏，Pro级摄像头系统</t>
+          <t>苹果iPhone 14 Pro （512GB）</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -25069,7 +25068,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro Max（256GB） A16处理器，4800万像素，120Hz刷新率</t>
+          <t>苹果iPhone 14 Pro Max（256GB）</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -25144,7 +25143,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro Max（512GB） A16处理器，4800万像素，120Hz刷新率</t>
+          <t>苹果iPhone 14 Pro Max（512GB）</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -25294,7 +25293,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>vivo X Fold+（12GB/256GB） 2K+屏幕巨幕，80W双电池闪充，双屏幕指纹</t>
+          <t>vivo X Fold+（12GB/256GB）</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -25369,7 +25368,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>OPPO Reno9（8GB/256GB） 骁龙778G，6400万水光人像镜头，120Hz OLED超清曲面屏，</t>
+          <t>OPPO Reno9（8GB/256GB）</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -25444,7 +25443,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>OPPO Find N2（12GB/256GB） 120Hz刷新，超轻折叠设计，多角度自由悬停2.0</t>
+          <t>OPPO Find N2（12GB/256GB）</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -25519,7 +25518,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>荣耀80（8BG/256GB） 1.6亿像素超清主摄，AI Vlog视频大师，全新Magic OS 7.0系统</t>
+          <t>荣耀80（8BG/256GB）</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -25594,7 +25593,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>荣耀80 Pro（8GB/256GB） 1.6亿像素超清主摄，骁龙8+旗舰芯片，AI Vlog视频大师</t>
+          <t>荣耀80 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -25669,7 +25668,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>荣耀Magic5 Pro（8GB/256GB） 骁龙8Gen2，MagicRing，Magic Text，GPU Turbo X</t>
+          <t>荣耀Magic5 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -25744,7 +25743,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>vivo X90 Pro+（12GB/256GB） 蔡司一英寸T*主摄，自研芯片V2，100X蔡司超清变焦</t>
+          <t>vivo X90 Pro+（12GB/256GB）</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -25819,7 +25818,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>vivo S16（8GB/128GB） 骁龙870，前置5000，66W闪充</t>
+          <t>vivo S16（8GB/128GB）</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -25894,7 +25893,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>vivo S16 Pro（12GB/256GB） 天玑8200，前置5000，原彩柔光环</t>
+          <t>vivo S16 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -25969,7 +25968,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>三星Galaxy A54（8GB/128GB） 光学防抖，IP67等级，5000毫安大电池</t>
+          <t>三星Galaxy A54（8GB/128GB）</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -26044,7 +26043,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>荣耀X40 GT（8GB/256GB） 游戏手机，骁龙888，66W快充</t>
+          <t>荣耀X40 GT（8GB/256GB）</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -26119,7 +26118,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>三星W23（16GB/512GB） 骁龙8+ Gen 1，旗舰影像，沉浸大屏，超强生产力</t>
+          <t>三星W23（16GB/512GB）</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -26190,7 +26189,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>三星W23 Flip（12GB/512GB） 骁龙8+ Gen 1，1200万像素，OLED折叠屏</t>
+          <t>三星W23 Flip（12GB/512GB）</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -26261,7 +26260,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>荣耀畅玩40（6GB/128GB） 5200mAh电池，高清护眼大屏，90Hz</t>
+          <t>荣耀畅玩40（6GB/128GB）</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -26336,7 +26335,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>荣耀畅玩40 Plus （6GB/128GB） 5000万像素，侧边指纹，90Hz</t>
+          <t>荣耀畅玩40 Plus （6GB/128GB）</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -26411,7 +26410,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>苹果iPhone 16e（128GB） 超视网膜XDR显示屏，A18处理器，6.1英寸显示屏</t>
+          <t>苹果iPhone 16e（128GB）</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -26480,7 +26479,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>华为Pocket S （8GB/128GB） 鸿蒙系统3.0，120Hz高刷，智慧外屏</t>
+          <t>华为Pocket S （8GB/128GB）</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -26555,7 +26554,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>华为Pocket S （8GB/256GB） 鸿蒙系统3.0，120Hz高刷，智慧外屏</t>
+          <t>华为Pocket S （8GB/256GB）</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -26630,7 +26629,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>OPPO A58（8GB/256GB） 90Hz高刷，5000万像素，天玑700</t>
+          <t>OPPO A58（8GB/256GB）</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -26705,7 +26704,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>vivo X90（8GB/256GB） 天玑 9200，自研芯片V2，VCS仿生光谱大底主摄</t>
+          <t>vivo X90（8GB/256GB）</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -26780,7 +26779,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>vivo X90（12GB/256GB） 天玑 9200，自研芯片V2，VCS仿生光谱大底主摄</t>
+          <t>vivo X90（12GB/256GB）</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -26855,7 +26854,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>vivo X90 Pro（12GB/256GB） 蔡司一英寸T*主摄，天玑 9200，自研芯片V2</t>
+          <t>vivo X90 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -26930,7 +26929,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>华为畅享50z（6GB/128GB） 5000万高清AI三摄，超能续航，握持舒适，上手轻盈</t>
+          <t>华为畅享50z（6GB/128GB）</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -27001,7 +27000,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>vivo S16e（8GB/128GB） 5000万像素，5nm芯片，OIS光学防抖</t>
+          <t>vivo S16e（8GB/128GB）</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -27076,7 +27075,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>vivo X Flip（12GB/256GB） 魔镜大外屏，悬停蔡司影像，骁龙8+芯片</t>
+          <t>vivo X Flip（12GB/256GB）</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -27151,7 +27150,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>荣耀80 GT（12GB/256GB） 超帧独显芯片，120Hz原画超帧屏，IMX800主摄</t>
+          <t>荣耀80 GT（12GB/256GB）</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -27226,7 +27225,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>vivo X Fold2（12GB/256GB） 120Hz折叠巨幕，120W双芯闪充，第二代骁龙8</t>
+          <t>vivo X Fold2（12GB/256GB）</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -27301,7 +27300,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>vivo S16e（12GB/256GB） 5000万像素，5nm芯片，OIS光学防抖</t>
+          <t>vivo S16e（12GB/256GB）</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -27376,7 +27375,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip5（8GB/256GB） CPU型号:高通 骁龙8 Gen2 CPU核心数:八核 ROM容量:256GB 电池容量:3700mAh 后置摄像头1 后置摄像头:1200万像素 有线充电:25w 前置摄像头1 前置摄像头:1000万像素</t>
+          <t>三星Galaxy Z Flip5（8GB/256GB）</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -27451,7 +27450,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold5（12GB/512GB） 闭合折叠，轻薄手感，PC般强大生产力</t>
+          <t>三星Galaxy Z Fold5（12GB/512GB）</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -27526,8 +27525,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>OPPO Reno 10（8GB/256GB） 超光影长焦镜头，骁龙778G
-5G次旗舰芯片，80W超级闪充</t>
+          <t>OPPO Reno 10（8GB/256GB）</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -27602,7 +27600,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>vivo Y53t（4GB/128GB） 5000mAh电池，双模5G，面部指纹双解锁</t>
+          <t>vivo Y53t（4GB/128GB）</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -27677,7 +27675,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>荣耀90（12GB/256GB） 2亿像素，零风险调光，骁龙7增强版</t>
+          <t>荣耀90（12GB/256GB）</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -27752,7 +27750,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>荣耀90 Pro（12GB/256GB） 2亿像素，零风险调光，100W充电</t>
+          <t>荣耀90 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -27827,7 +27825,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>三星Galaxy S23（8GB/256GB） 超视觉夜拍，第二代骁龙8，超亮全视护眼屏</t>
+          <t>三星Galaxy S23（8GB/256GB）</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -27902,7 +27900,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>三星Galaxy S23 Ultra（12GB/256GB） 超视觉夜拍，第二代骁龙8，S Pen书写</t>
+          <t>三星Galaxy S23 Ultra（12GB/256GB）</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -27977,7 +27975,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>三星Galaxy S23 Ultra（12GB/512GB） 超视觉夜拍，第二代骁龙8，S Pen书写</t>
+          <t>三星Galaxy S23 Ultra（12GB/512GB）</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -28052,7 +28050,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>三星Galaxy S24(8GB/256GB) 装甲铝边框，超视觉引擎，Galaxy AI</t>
+          <t>三星Galaxy S24(8GB/256GB)</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -28123,7 +28121,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>三星Galaxy S24 Ultra(12GB/256GB) Al智享生活办公，四长焦系统，SPen</t>
+          <t>三星Galaxy S24 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -28198,7 +28196,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>华为畅享 60（8GB+128GB） 鸿蒙3.0，麒麟710A，6000mAh电池</t>
+          <t>华为畅享 60（8GB+128GB）</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -28273,7 +28271,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>vivo Y78（8GB/128GB） 原色护眼屏，天玑7020，5000万主摄</t>
+          <t>vivo Y78（8GB/128GB）</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -28348,7 +28346,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>vivo Y78+（8GB/128GB） 120Hz，OLED曲屏，5000万OIS光学防抖，5000mAh</t>
+          <t>vivo Y78+（8GB/128GB）</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -28423,7 +28421,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>HUAWEI P60 Art版（12GB+512GB） 超聚光XMAGE影像，双向北斗卫星消息，鸿蒙系统3.1</t>
+          <t>HUAWEI P60 Art版（12GB+512GB）</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -28498,7 +28496,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>vivo S17（12GB/256GB） 5000万广角柔光，智慧柔光环，1.5K超视网膜屏</t>
+          <t>vivo S17（12GB/256GB）</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -28573,7 +28571,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>vivo S17 Pro（8GB/256GB） 5000万广角柔光，专业长焦人像镜头，天玑8200旗舰芯片</t>
+          <t>vivo S17 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -28648,7 +28646,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>vivo S17e（8GB/128GB） 6400万柔光人像，光学防抖，超感曲面屏</t>
+          <t>vivo S17e（8GB/128GB）</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -28723,7 +28721,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>OPPO Find N3（12GB/512GB） 超轻薄折叠，超光影折叠像素，国密认证安全芯片</t>
+          <t>OPPO Find N3（12GB/512GB）</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -28798,7 +28796,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>荣耀X50（8GB/128GB） 骁龙6芯片 ，1.5K，硬核曲屏</t>
+          <t>荣耀X50（8GB/128GB）</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -28873,7 +28871,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>荣耀X50 GT(12GB/256GB) 骁龙8+芯片，苍穹散热系统，灵龙触控引擎</t>
+          <t>荣耀X50 GT(12GB/256GB)</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -28948,7 +28946,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>vivo Y11 4G版（6GB/128GB） 5000毫安电池，800万像素，内存融合2.0</t>
+          <t>vivo Y11 4G版（6GB/128GB）</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -29019,7 +29017,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>HUAWEI nova 11（8GB/128GB） 6000万超广角人像，6.88毫米超薄臻彩直屏，屏幕指纹</t>
+          <t>HUAWEI nova 11（8GB/128GB）</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29094,7 +29092,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>HUAWEI nova 11 Pro（8GB/256GB） 120Hz，100W超级快充，前置6000万</t>
+          <t>HUAWEI nova 11 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -29169,7 +29167,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>华为nova 11 SE（256GB） 3200万高清自拍，一亿像素光影人像，HarmonyOS 4</t>
+          <t>华为nova 11 SE（256GB）</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -29242,7 +29240,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>vivo X90s（8GB/256GB） 天玑9200+，自研影像芯片V2，VCS仿生光谱大底主摄</t>
+          <t>vivo X90s（8GB/256GB）</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -29317,7 +29315,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>华为畅享 60X（8GB/128GB） 7000mAh长续航，6.95英寸影音大屏，澎湃音质</t>
+          <t>华为畅享 60X（8GB/128GB）</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -29392,7 +29390,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>荣耀X50i（8GB/256GB） 一亿像素，35w快充，护眼全视屏</t>
+          <t>荣耀X50i（8GB/256GB）</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -29467,7 +29465,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>华为畅享 60X（8GB/256GB） 7000mAh长续航，6.95英寸影音大屏，澎湃音质</t>
+          <t>华为畅享 60X（8GB/256GB）</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -29542,7 +29540,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>荣耀Magic V2（16GB/256GB） CPU型号:高通 骁龙8 Gen2 CPU核心数:八核 RAM容量:8GB ROM容量:256GB 电池容量:5000mAh 后置摄像头1 后置摄像头:5400万像素 有线充电:66w</t>
+          <t>荣耀Magic V2（16GB/256GB）</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -29617,7 +29615,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>vivo Y78（12GB/256GB） 原色护眼屏，天玑7020，5000万主摄</t>
+          <t>vivo Y78（12GB/256GB）</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -29692,7 +29690,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>华为畅享 60 Pro（8GB/128GB） 5000mAh电池，40W快充，无界全视屏</t>
+          <t>华为畅享 60 Pro（8GB/128GB）</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -29767,7 +29765,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>vivo S17t（12GB/512GB） 智慧柔光环，1.5k超视网膜护眼屏，前后5000W超光感人像</t>
+          <t>vivo S17t（12GB/512GB）</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -29842,7 +29840,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>vivo Y35+（8GB/256GB） 1080P高清护眼屏，5000万超清主摄，200%大音量</t>
+          <t>vivo Y35+（8GB/256GB）</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -29917,7 +29915,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>vivo Y35+（8GB/128GB） 1080P高清护眼屏，5000万超清主摄，200%大音量</t>
+          <t>vivo Y35+（8GB/128GB）</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -29992,7 +29990,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>vivo S17（12GB/512GB） 5000万广角柔光，智慧柔光环，1.5K超视网膜屏</t>
+          <t>vivo S17（12GB/512GB）</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -30067,7 +30065,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>三星W25(16GB/512GB) 2亿像素，新一代Bixby，第三代骁龙8</t>
+          <t>三星W25(16GB/512GB)</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -30134,7 +30132,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>三星W25 Flip(12GB/512GB) 5000万像素，IP48防水，陶瓷后壳</t>
+          <t>三星W25 Flip(12GB/512GB)</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30201,7 +30199,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>vivo X100（12GB/256GB） 蔡司APO超级长焦，天玑9300，5400mAh蓝海电池</t>
+          <t>vivo X100（12GB/256GB）</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -30276,7 +30274,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>vivo X100 Pro（12GB/256GB） 蔡司APO超级长焦，蓝晶×天玑9300，自研影像芯片V3</t>
+          <t>vivo X100 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -30351,7 +30349,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>vivo X Fold3（12GB/256GB） 219g超轻薄，5500mAh蓝海电池，超可靠铠羽架构</t>
+          <t>vivo X Fold3（12GB/256GB）</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30426,7 +30424,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>OPPO K11（12GB/512GB） CPU型号:高通 骁龙782G CPU核心数:八核 RAM容量:12GB ROM容量:512GB 电池容量:5000mAh 后置摄像头1 后置摄像头:5000万像素 有线充电:100w</t>
+          <t>OPPO K11（12GB/512GB）</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -30501,7 +30499,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>荣耀X50（12GB/256GB） 骁龙6芯片 ，1.5K，硬核曲屏</t>
+          <t>荣耀X50（12GB/256GB）</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -30576,7 +30574,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold5（12GB/1TB） 闭合折叠，轻薄手感，PC般强大生产力</t>
+          <t>三星Galaxy Z Fold5（12GB/1TB）</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -30651,7 +30649,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>OPPO Find N3 Flip（12GB/256GB） CPU型号:联发科 天玑9200 CPU核心数:八核 RAM容量:8GB ROM容量:256GB 电池容量:4300mAh 后置摄像头1 后置摄像头:5000万像素 有线充电:44w</t>
+          <t>OPPO Find N3 Flip（12GB/256GB）</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30726,7 +30724,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60 Pro（12GB/512GB） 卫星通话，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60 Pro（12GB/512GB）</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -30797,7 +30795,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60 Pro（12GB/1TB） 卫星通话，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60 Pro（12GB/1TB）</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -30868,7 +30866,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60（12GB/512GB） 双向北斗卫星消息，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60（12GB/512GB）</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -30939,7 +30937,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 60（12GB/1TB） 双向北斗卫星消息，超可靠玄武架构，全焦段超清影像</t>
+          <t>HUAWEI Mate 60（12GB/1TB）</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -31010,7 +31008,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>荣耀Magic Vs2（12GB/256GB） 超轻薄机身，零风险调光护眼双屏，5000mAh超长续航</t>
+          <t>荣耀Magic Vs2（12GB/256GB）</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -31085,7 +31083,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>华为Mate 60 Pro+（16GB/512GB） 双卫星通信，丹青弧时代之作，超可靠玄武架构</t>
+          <t>华为Mate 60 Pro+（16GB/512GB）</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -31156,7 +31154,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>荣耀V Purse（16GB/512GB） 外折屏，右上角打孔，厚度不足9mm</t>
+          <t>荣耀V Purse（16GB/512GB）</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -31231,7 +31229,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>华为Mate X5 （12GB/256GB） CPU型号:高通 骁龙8+ 4G CPU核心数:八核 RAM容量:12GB ROM容量:256GB 电池容量:5060mAh 后置摄像头1 后置摄像头:5000万像素 有线充电:66w</t>
+          <t>华为Mate X5 （12GB/256GB）</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -31499,7 +31497,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>华为Mate 60 Pro+ 16GB+1TB（16GB/1TB） 双卫星通信，丹青弧时代之作，超可靠玄武架构</t>
+          <t>华为Mate 60 Pro+ 16GB+1TB（16GB/1TB）</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -31570,7 +31568,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro（256GB） 钛金属，A17 Pro芯片，4800万像素主摄</t>
+          <t>苹果iPhone 15 Pro（256GB）</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -31643,7 +31641,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro（512GB） 钛金属，A17 Pro芯片，4800万像素主摄</t>
+          <t>苹果iPhone 15 Pro（512GB）</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -31789,7 +31787,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro Max（512GB） 钛金属，6.7英寸，A17 Pro芯片</t>
+          <t>苹果iPhone 15 Pro Max（512GB）</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -31935,7 +31933,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>苹果iPhone 15（256GB） 灵动岛，4800万像素主摄，2倍长焦</t>
+          <t>苹果iPhone 15（256GB）</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -32010,7 +32008,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>苹果iPhone 15（512GB） 灵动岛，4800万像素主摄，2倍长焦</t>
+          <t>苹果iPhone 15（512GB）</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -32085,7 +32083,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Plus（256GB） 灵动岛，6.7英寸，4800万像素主摄</t>
+          <t>苹果iPhone 15 Plus（256GB）</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -32160,7 +32158,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Plus（512GB） 灵动岛，6.7英寸，4800万像素主摄</t>
+          <t>苹果iPhone 15 Plus（512GB）</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -32235,7 +32233,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>三星W24 Flip（12GB/512GB） 大视野智能外屏，掌心折叠，立式自由拍摄</t>
+          <t>三星W24 Flip（12GB/512GB）</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -32306,7 +32304,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>三星W24（16GB/1TB） 超闭合折叠，尊奢铰链，轻型化陶瓷</t>
+          <t>三星W24（16GB/1TB）</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -32444,7 +32442,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>vivo Y100(8GB/128GB) 5000mAh电池，6400万OIS光学防抖，44W超快闪充</t>
+          <t>vivo Y100(8GB/128GB)</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -32519,7 +32517,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>荣耀Play8T（8GB/256GB） 6000mAh续航， 850nit高亮，大内存</t>
+          <t>荣耀Play8T（8GB/256GB）</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -32594,7 +32592,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>vivo Y78t 8GB+256GB 第一代骁龙6，6000mAh大电池，5000万超清影像</t>
+          <t>vivo Y78t 8GB+256GB 第一代</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -32744,7 +32742,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>荣耀100(12GB/256GB) 单反级写真相机，荣耀绿洲护眼屏，第三代骁龙7</t>
+          <t>荣耀100(12GB/256GB)</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -32819,7 +32817,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>OPPO Reno 11(8GB/256GB) 5000万单反级人像三摄，天玑8200旗舰芯，67W超级闪充</t>
+          <t>OPPO Reno 11(8GB/256GB)</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -32894,7 +32892,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>vivo X100（16GB/256GB） 蔡司APO超级长焦，天玑9300，5400mAh蓝海电池</t>
+          <t>vivo X100（16GB/256GB）</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -32969,7 +32967,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>vivo X100（16GB/512GB） 蔡司APO超级长焦，天玑9300，5400mAh蓝海电池</t>
+          <t>vivo X100（16GB/512GB）</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -33044,7 +33042,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>vivo X100（16GB/1TB） 蔡司APO超级长焦，天玑9300，5400mAh蓝海电池</t>
+          <t>vivo X100（16GB/1TB）</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -33119,7 +33117,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>荣耀100 Pro(12GB/256GB) 单反级写真相机，荣耀绿洲护眼屏，第二代骁龙8</t>
+          <t>荣耀100 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -33194,7 +33192,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>vivo Y100i（12GB/512GB） 直角立边，6.78英寸屏幕，120Hz高刷新率</t>
+          <t>vivo Y100i（12GB/512GB）</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -33269,7 +33267,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro（128GB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro（128GB）</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -33338,7 +33336,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>苹果iPhone 16（128GB） 4800万像素Fusion摄像头，五款抢眼靓色，搭载A18芯片</t>
+          <t>苹果iPhone 16（128GB）</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -33411,7 +33409,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro Max（256GB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro Max（256GB）</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -33480,7 +33478,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 70(12GB/512GB) 鸿蒙AI，红枫原色影像，超可靠玄武架构</t>
+          <t>HUAWEI Mate 70(12GB/512GB)</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -33547,7 +33545,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>vivo Y36(6GB/128GB) 轻薄有实力，5000mAh大电池，200%超级扬声器</t>
+          <t>vivo Y36(6GB/128GB)</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -33687,7 +33685,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>OPPO Find X7(12GB/256GB) 潮汐架构，全大核天玑9300，超光影三主摄</t>
+          <t>OPPO Find X7(12GB/256GB)</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -33762,7 +33760,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>vivo Y36m（6GB/128GB） 5000mAh大电池，200%超级扬声器，长续航</t>
+          <t>vivo Y36m（6GB/128GB）</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -33837,7 +33835,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>荣耀X50i+(12GB/256GB) 一亿像素超清记录，零风险调光OLED护眼屏，20GB(12+8)等效运存</t>
+          <t>荣耀X50i+(12GB/256GB)</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -33912,7 +33910,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>vivo S18（8GB/256GB） 第三代骁龙7,5000mAh,影棚级柔光环</t>
+          <t>vivo S18（8GB/256GB）</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -33987,7 +33985,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>vivo S18 Pro（12GB/256GB） 天玑9200+,影棚级柔光环,超薄蓝海电池</t>
+          <t>vivo S18 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -34062,7 +34060,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>荣耀Magic6(12GB/256GB) 单反级荣耀鹰眼相机，荣耀巨犀玻璃， 5450mAh</t>
+          <t>荣耀Magic6(12GB/256GB)</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -34137,7 +34135,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>华为nova 12 Ultra(512GB) 动态臻彩屏，100W智能快充，HarmonyOS</t>
+          <t>华为nova 12 Ultra(512GB)</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -34202,7 +34200,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>vivo S18e(12GB/256GB) 人像双补光环，超薄直屏，80W充电</t>
+          <t>vivo S18e(12GB/256GB)</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -34273,7 +34271,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>vivo S18（12GB/256GB） 第三代骁龙7,5000mAh,影棚级柔光环</t>
+          <t>vivo S18（12GB/256GB）</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -34348,7 +34346,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>vivo S18（12GB/512GB） 第三代骁龙7,5000mAh,影棚级柔光环</t>
+          <t>vivo S18（12GB/512GB）</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -34423,7 +34421,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>vivo S18（16GB/512GB） 第三代骁龙7,5000mAh,影棚级柔光环</t>
+          <t>vivo S18（16GB/512GB）</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -34498,7 +34496,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>vivo S18 Pro（16GB/256GB） 天玑9200+,影棚级柔光环,超薄蓝海电池</t>
+          <t>vivo S18 Pro（16GB/256GB）</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -34573,7 +34571,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>vivo S18e(12GB/512GB) 人像双补光环，超薄直屏，80W充电</t>
+          <t>vivo S18e(12GB/512GB)</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -34644,7 +34642,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>荣耀90 GT(12GB/256GB) 二代骁龙8旗舰芯 ，超凡帧画引擎，荣耀绿洲护眼屏</t>
+          <t>荣耀90 GT(12GB/256GB)</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -34719,7 +34717,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>华为nova 12 Pro 256GB 前置6000万人像追焦双摄，鸿蒙智慧通信，HarmonyOS</t>
+          <t>华为nova 12 Pro 256GB 前置6000万人像追焦双摄，鸿蒙智慧通信，</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -34784,7 +34782,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>华为nova 12 Pro 512GB 前置6000万人像追焦双摄，鸿蒙智慧通信，HarmonyOS</t>
+          <t>华为nova 12 Pro 512GB 前置6000万人像追焦双摄，鸿蒙智慧通信，</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -34914,7 +34912,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>华为nova 12 活力版 256GB 鸿蒙智能，6.88mm超薄，前置6000万</t>
+          <t>华为nova 12 活力版 256GB 鸿蒙智能，6.88mm</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -34979,7 +34977,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>华为nova 12 活力版 512GB 鸿蒙智能，6.88mm超薄，前置6000万</t>
+          <t>华为nova 12 活力版 512GB 鸿蒙智能，6.88mm</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -35044,7 +35042,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>vivo X100s(12GB/256GB) 蓝晶x天玑9300+，7.8mm超薄直屏，蔡司超级长焦</t>
+          <t>vivo X100s(12GB/256GB)</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -35119,7 +35117,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>OPPO Find X7 Ultra(12GB/256GB) 1英寸双潜望四主摄，哈苏影像，第三代骁龙8</t>
+          <t>OPPO Find X7 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -35194,7 +35192,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>华为畅享 70 Pro 256GB 1亿像素超清影像，40W超级快充，5000mAh大电池</t>
+          <t>华为畅享 70 Pro 256GB 1亿像素超清影像，40W超级快充，5000mAh</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -35267,7 +35265,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>华为畅享 70 Pro 128GB 1亿像素超清影像，40W超级快充，5000mAh大电池</t>
+          <t>华为畅享 70 Pro 128GB 1亿像素超清影像，40W超级快充，5000mAh</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -35470,7 +35468,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>荣耀Magic6 Pro(12GB/256GB) 单反级荣耀鹰眼相机，第三代骁龙8，荣耀巨犀玻璃</t>
+          <t>荣耀Magic6 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -35545,7 +35543,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>荣耀Magic6 Pro(16GB/1TB) 单反级荣耀鹰眼相机，第三代骁龙8，荣耀巨犀玻璃</t>
+          <t>荣耀Magic6 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -35620,7 +35618,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>三星Galaxy S24 Ultra(12GB/512GB)) Al智享生活办公，四长焦系统，SPen</t>
+          <t>三星Galaxy S24 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -35695,7 +35693,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>三星Galaxy S24 Ultra(12GB/1TB) Al智享生活办公，四长焦系统，SPen</t>
+          <t>三星Galaxy S24 Ultra(12GB/1TB)</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -35770,7 +35768,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>三星Galaxy S24(8GB/512GB) 装甲铝边框，超视觉引擎，Galaxy AI</t>
+          <t>三星Galaxy S24(8GB/512GB)</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -35841,7 +35839,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>三星Galaxy S24(12GB/256GB) 装甲铝边框，超视觉引擎，Galaxy AI</t>
+          <t>三星Galaxy S24(12GB/256GB)</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -35912,7 +35910,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>三星Galaxy S24+(12GB/256GB) 装甲铝边框，超视觉引擎，Galaxy AI</t>
+          <t>三星Galaxy S24+(12GB/256GB)</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -35983,7 +35981,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>三星Galaxy S24+(12GB/512GB) 装甲铝边框，超视觉引擎，Galaxy AI</t>
+          <t>三星Galaxy S24+(12GB/512GB)</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -36054,7 +36052,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>华为Pocket 2(12GB/256GB) 超平整超可靠，全焦段XMAGE四摄，紫外防晒检测</t>
+          <t>华为Pocket 2(12GB/256GB)</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -36121,7 +36119,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>华为Pocket 2(12GB/512GB) 超平整超可靠，全焦段XMAGE四摄，紫外防晒检测</t>
+          <t>华为Pocket 2(12GB/512GB)</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -36188,8 +36186,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold6(12GB/512GB) 大屏Galaxy AI，
-超时尚，骁龙8 Gen3</t>
+          <t>三星Galaxy Z Fold6(12GB/512GB)</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -36264,7 +36261,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>OPPO K12(8GB/256GB) 超抗摔金刚石架构，5500mAh超长续航，第三代骁龙7旗舰芯</t>
+          <t>OPPO K12(8GB/256GB)</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -36339,7 +36336,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70(12GB/1TB) 超高速风驰闪拍，超聚光微距长焦，双超级快充</t>
+          <t>HUAWEI Pura 70(12GB/1TB)</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -36406,7 +36403,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>荣耀Magic6至臻版(16GB/512GB) 第三代骁龙8，5000mAh电池，单反级超动态鹰眼相机</t>
+          <t>荣耀Magic6至臻版(16GB/512GB)</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -36481,7 +36478,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>荣耀Magic6 RSR保时捷设计(24GB/1TB) 经典六边形结构，单反级超动态鹰眼相机 ，荣耀叠光绿洲护眼屏</t>
+          <t>荣耀Magic6 RSR保时捷设计(24GB/1TB)</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -36556,7 +36553,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>vivo X Fold3 Pro(16GB/512GB) 236g机身超轻薄设计，等效5700mAh蓝海电池，超可靠铠羽架构</t>
+          <t>vivo X Fold3 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -36631,7 +36628,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>vivo X Fold3（16GB/256GB） 219g超轻薄，5500mAh蓝海电池，超可靠铠羽架构</t>
+          <t>vivo X Fold3（16GB/256GB）</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -36706,7 +36703,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>vivo X Fold3（16GB/512GB） 219g超轻薄，5500mAh蓝海电池，超可靠铠羽架构</t>
+          <t>vivo X Fold3（16GB/512GB）</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -36781,7 +36778,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>vivo X Fold3（16GB/1TB） 219g超轻薄，5500mAh蓝海电池，超可靠铠羽架构</t>
+          <t>vivo X Fold3（16GB/1TB）</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -36856,7 +36853,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>vivo X Fold3 Pro(16GB/1TB) 蔡司超级长焦|，236g机身超轻薄设计，等效5700mAh蓝海电池</t>
+          <t>vivo X Fold3 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -36931,7 +36928,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>OPPO A3 Pro(8GB/256GB) 满级防水，360°抗摔，四年耐用大电池</t>
+          <t>OPPO A3 Pro(8GB/256GB)</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -37006,7 +37003,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Ultra(16GB/1TB) 超聚光伸缩摄像头，超高速风驰闪拍，双卫星通信</t>
+          <t>HUAWEI Pura 70 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -37073,7 +37070,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Ultra(16GB/512GB) 超聚光伸缩摄像头，超高速风驰闪拍，双卫星通信</t>
+          <t>HUAWEI Pura 70 Ultra(16GB/512GB)</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -37140,7 +37137,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Pro(12GB/256GB) 风驰闪拍，超聚光微距长焦，北斗卫星图片消息</t>
+          <t>HUAWEI Pura 70 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -37207,7 +37204,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Pro(12GB/512GB) 风驰闪拍，超聚光微距长焦，北斗卫星图片消息</t>
+          <t>HUAWEI Pura 70 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -37274,7 +37271,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Pro(12GB/1TB) 风驰闪拍，超聚光微距长焦，北斗卫星图片消息</t>
+          <t>HUAWEI Pura 70 Pro(12GB/1TB)</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -37341,7 +37338,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Pro+(16GB/512GB) 风驰闪拍，超聚光微距长焦，双卫星通信</t>
+          <t>HUAWEI Pura 70 Pro+(16GB/512GB)</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -37408,7 +37405,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>HUAWEI Pura 70 Pro+(16GB/1TB) 风驰闪拍，超聚光微距长焦，双卫星通信</t>
+          <t>HUAWEI Pura 70 Pro+(16GB/1TB)</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -37475,7 +37472,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>vivo Y200i(8GB/256GB) 轻薄6000mAh+44W，120Hz金刚护眼屏，IP64级生活防尘防水</t>
+          <t>vivo Y200i(8GB/256GB)</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -37550,7 +37547,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>vivo Y200i(12GB/256GB) 轻薄6000mAh+44W，120Hz金刚护眼屏，IP64级生活防尘防水</t>
+          <t>vivo Y200i(12GB/256GB)</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -37625,7 +37622,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>vivo Y200i(12GB/512GB) 轻薄6000mAh+44W，120Hz金刚护眼屏，IP64级生活防尘防水</t>
+          <t>vivo Y200i(12GB/512GB)</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -37700,7 +37697,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>vivo X100 Ultra(12GB/256GB) 蔡司2亿APO超级长焦，1英寸云台机主摄，蓝图影像</t>
+          <t>vivo X100 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -37775,7 +37772,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>vivo S19(8GB/256GB) 薄至7.19mm，影棚级柔光环，超薄蓝海电池</t>
+          <t>vivo S19(8GB/256GB)</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -37850,7 +37847,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>vivo X100s Pro(12GB/256GB) 蔡司APO超级长焦，蓝晶x天玑9300+，蓝海电池</t>
+          <t>vivo X100s Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -37925,7 +37922,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>vivo Y200 GT(8GB/128GB) 高通第三代骁龙7，144Hz 1.5k金刚护眼屏，6000mAh蓝海电池+80W</t>
+          <t>vivo Y200 GT(8GB/128GB)</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -38000,7 +37997,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>vivo X100 Ultra(16GB/256GB) 蔡司2亿APO超级长焦，1英寸云台机主摄，蓝图影像</t>
+          <t>vivo X100 Ultra(16GB/256GB)</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -38075,7 +38072,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>vivo X100 Ultra(16GB/1TB) 蔡司2亿APO超级长焦，1英寸云台机主摄，蓝图影像</t>
+          <t>vivo X100 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -38150,7 +38147,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>vivo X100s(16GB/512GB) 蓝晶x天玑9300+，7.8mm超薄直屏，蔡司超级长焦</t>
+          <t>vivo X100s(16GB/512GB)</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -38225,7 +38222,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>vivo X100s Pro(16GB/512GB) 蔡司APO超级长焦，蓝晶x天玑9300+，蓝海电池</t>
+          <t>vivo X100s Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -38300,7 +38297,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>vivo X100s Pro(16GB/1TB) 蔡司APO超级长焦，蓝晶x天玑9300+，蓝海电池</t>
+          <t>vivo X100s Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -38375,7 +38372,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>vivo Y200t(8GB/128GB) CPU型号:高通 骁龙6 Gen1 CPU核心数:八核 RAM容量:8GB ROM容量:128GB 电池容量:6000mAh 后置摄像头1 后置摄像头:5000万像素 有线充电:44w</t>
+          <t>vivo Y200t(8GB/128GB)</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -38450,7 +38447,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>vivo Y100i（12GB/256GB） 直角立边，6.78英寸屏幕，120Hz高刷新率</t>
+          <t>vivo Y100i（12GB/256GB）</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -38525,7 +38522,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>三星Galaxy C55(8GB/256GB) 后置5000万三摄，前置5000万自拍，120Hz柔性大屏</t>
+          <t>三星Galaxy C55(8GB/256GB)</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -38596,7 +38593,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>三星Galaxy C55(12GB/256GB) 后置5000万三摄，前置5000万自拍，120Hz柔性大屏</t>
+          <t>三星Galaxy C55(12GB/256GB)</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -38667,7 +38664,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>OPPO Reno 12(12GB/256GB) 超美小直屏，安卓Live图，天玑 8250 星速版</t>
+          <t>OPPO Reno 12(12GB/256GB)</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -38742,7 +38739,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>vivo Y200(8GB/128GB) 120Hz金刚曲面屏，索尼5000万超清影像，6000mAh蓝海电池+80W</t>
+          <t>vivo Y200(8GB/128GB)</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -38817,7 +38814,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>荣耀200(12GB/256GB) 5000万雅顾光影主摄，荣耀绿洲护眼屏，5200mAh青海湖电池</t>
+          <t>荣耀200(12GB/256GB)</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -38892,7 +38889,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>荣耀200 Pro(12GB/256GB) 三主摄写真相机，绿洲护眼屏，青海湖电池</t>
+          <t>荣耀200 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -38967,7 +38964,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>vivo Y200 GT(12GB/512GB) 高通第三代骁龙7，144Hz 1.5k金刚护眼屏，6000mAh蓝海电池+80W</t>
+          <t>vivo Y200 GT(12GB/512GB)</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -39334,7 +39331,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>荣耀200(12GB/512GB) 5000万雅顾光影主摄，荣耀绿洲护眼屏，5200mAh青海湖电池</t>
+          <t>荣耀200(12GB/512GB)</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -39409,7 +39406,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>vivo Y36t(6GB/128GB) 超感轻薄设计，6GB融合内存，超大音量</t>
+          <t>vivo Y36t(6GB/128GB)</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -39484,7 +39481,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>荣耀畅玩50(6GB/128GB) 5200毫安电池，高亮清晰大屏，防跌耐摔</t>
+          <t>荣耀畅玩50(6GB/128GB)</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -39559,7 +39556,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>华为畅享 70S(8GB/128GB) AOD护眼大屏，畅享X键，6000毫安电池</t>
+          <t>华为畅享 70S(8GB/128GB)</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -39630,7 +39627,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>vivo Y100t(8GB/256GB) 120W超快闪充，天玑8200，OIS防抖</t>
+          <t>vivo Y100t(8GB/256GB)</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -39705,7 +39702,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>vivo Y100t(12GB/256GB) 120W超快闪充，天玑8200，OIS防抖</t>
+          <t>vivo Y100t(12GB/256GB)</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -39780,7 +39777,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>vivo Y100t(12GB/512GB) 120W超快闪充，天玑8200，OIS防抖</t>
+          <t>vivo Y100t(12GB/512GB)</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -39855,7 +39852,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>vivo S19 Pro(12GB/512GB) 轻薄曲屏，流畅运行，超清人像</t>
+          <t>vivo S19 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -39930,7 +39927,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>vivo S19(12GB/256GB) 薄至7.19mm，影棚级柔光环，超薄蓝海电池</t>
+          <t>vivo S19(12GB/256GB)</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -40005,7 +40002,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>vivo S19(12GB/512GB) 薄至7.19mm，影棚级柔光环，超薄蓝海电池</t>
+          <t>vivo S19(12GB/512GB)</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -40080,7 +40077,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>vivo S19(16GB/512GB) 薄至7.19mm，影棚级柔光环，超薄蓝海电池</t>
+          <t>vivo S19(16GB/512GB)</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -40155,7 +40152,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>荣耀畅玩50 Plus(8GB/256GB) 超大双存，超长续航，双倍大音量</t>
+          <t>荣耀畅玩50 Plus(8GB/256GB)</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -40230,7 +40227,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>荣耀Magic V Flip(12GB/256GB) 超轻薄折叠机身，青海湖电池，4英寸大外屏</t>
+          <t>荣耀Magic V Flip(12GB/256GB)</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -40305,7 +40302,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>荣耀畅玩60 Plus(12GB/256GB) 6000mAh超大电池，100%双扬大音量，SGS五星抗跌耐摔认证</t>
+          <t>荣耀畅玩60 Plus(12GB/256GB)</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -40380,7 +40377,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>vivo X200 Pro(12GB/256GB) 蔡司2亿APO超级长焦，天玑9400，蔡司大师色彩屏</t>
+          <t>vivo X200 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -40455,7 +40452,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>荣耀Magic V3(12GB/256GB) 第三代青海湖电池，金刚巨犀玻璃，第三代骁龙8</t>
+          <t>荣耀Magic V3(12GB/256GB)</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -40530,7 +40527,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>OPPO A3(8GB/256GB) 双面抗摔耐磨，超亮阳光屏，满级生活防水</t>
+          <t>OPPO A3(8GB/256GB)</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -40601,7 +40598,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>荣耀Magic Vs3(12GB/256GB) 9.8mm轻薄机身，5000mAh青海湖电池，荣耀绿洲护眼屏</t>
+          <t>荣耀Magic Vs3(12GB/256GB)</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -40901,7 +40898,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>HUAWEI nova 13(256GB) 前置6000万超广角人像，AI修图，北斗卫星图片消息</t>
+          <t>HUAWEI nova 13(256GB)</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -40966,7 +40963,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>vivo Y37 5G版(4GB/128GB) 灵动外观，5000mAh电池，90Hz高亮护眼屏</t>
+          <t>vivo Y37 5G版(4GB/128GB)</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -41041,7 +41038,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>vivo Y37 5G版(6GB/128GB) 灵动外观，5000mAh电池，90Hz高亮护眼屏</t>
+          <t>vivo Y37 5G版(6GB/128GB)</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -41116,7 +41113,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>三星Galaxy S25 Ultra(12GB/256GB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -41331,7 +41328,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>vivo Y300 Pro(8GB/128GB) 6500mAh超薄蓝海电池+80W，全等深微四曲屏，SGS五星抗摔认证</t>
+          <t>vivo Y300 Pro(8GB/128GB)</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -41479,7 +41476,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>vivo Y36c(6GB/128GB) 天玑6300，5000毫安大电池，高亮护眼屏</t>
+          <t>vivo Y36c(6GB/128GB)</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -41554,7 +41551,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>vivo Y37m(4GB/128GB) 天玑6300，5000毫安大电池，高亮护眼屏</t>
+          <t>vivo Y37m(4GB/128GB)</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -41629,7 +41626,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>华为Mate XT 非凡大师(16GB/512GB) 全球首个三折叠屏手机，10.2 英寸，首发十档可变光圈折暨影像</t>
+          <t>华为Mate XT 非凡大师(16GB/512GB)</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -41692,7 +41689,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>华为Mate XT 非凡大师(16GB/1TB) 全球首个三折叠屏手机，10.2 英寸，首发十档可变光圈折暨影像</t>
+          <t>华为Mate XT 非凡大师(16GB/1TB)</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -41755,7 +41752,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>荣耀Magic7(12GB/256GB) 骁龙8至尊版，绿洲护眼屏，巨犀玻璃</t>
+          <t>荣耀Magic7(12GB/256GB)</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -41830,7 +41827,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>苹果iPhone 16（256GB） 4800万像素Fusion摄像头，五款抢眼靓色，搭载A18芯片</t>
+          <t>苹果iPhone 16（256GB）</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -41903,7 +41900,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>苹果iPhone 16（512GB） 4800万像素Fusion摄像头，五款抢眼靓色，搭载A18芯片</t>
+          <t>苹果iPhone 16（512GB）</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -41976,7 +41973,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro（256GB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro（256GB）</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -42045,7 +42042,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro（512GB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro（512GB）</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -42114,7 +42111,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro（1TB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro（1TB）</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -42329,7 +42326,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro Max（512GB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro Max（512GB）</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -42398,7 +42395,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>苹果iPhone 16 Pro Max（1TB） 超视网膜XDR显示屏，钛金属边框，A18 Pro芯片</t>
+          <t>苹果iPhone 16 Pro Max（1TB）</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -42467,7 +42464,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>华为Mate XT 非凡大师(16GB/256GB) 全球首个三折叠屏手机，10.2 英寸，首发十档可变光圈折暨影像</t>
+          <t>华为Mate XT 非凡大师(16GB/256GB)</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -42530,7 +42527,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>荣耀Play9T(8GB/128GB) 6000毫安大电池，防水抗跌，双扬声器</t>
+          <t>荣耀Play9T(8GB/128GB)</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -42605,7 +42602,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>OPPO Find X8 Pro(12GB/256GB) 无影抓拍，天玑9400，AI一键问屏</t>
+          <t>OPPO Find X8 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -42755,7 +42752,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>vivo X200 Pro mini(12GB/256GB) 蔡司超级长焦，5700mAh蓝海电池，6.31英寸纤薄小直屏</t>
+          <t>vivo X200 Pro mini(12GB/256GB)</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -42830,7 +42827,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>OPPO K12 Plus（8GB/256GB） 第三代骁龙7，6400mAh大容量电池</t>
+          <t>OPPO K12 Plus（8GB/256GB）</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -42905,7 +42902,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>vivo X200(12GB/256GB) 天玑9400，全等深微四曲面屏，蔡司超级长焦</t>
+          <t>vivo X200(12GB/256GB)</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -42980,7 +42977,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>vivo X200 Pro mini(16GB/512GB) 蔡司超级长焦，5700mAh蓝海电池，6.31英寸纤薄小直屏</t>
+          <t>vivo X200 Pro mini(16GB/512GB)</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -43055,7 +43052,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>vivo X200 Pro mini(16GB/1TB) 蔡司超级长焦，5700mAh蓝海电池，6.31英寸纤薄小直屏</t>
+          <t>vivo X200 Pro mini(16GB/1TB)</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -43130,7 +43127,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>vivo X200(12GB/512GB) 天玑9400，全等深微四曲面屏，蔡司超级长焦</t>
+          <t>vivo X200(12GB/512GB)</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -43205,7 +43202,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>vivo X200(16GB/512GB) 天玑9400，全等深微四曲面屏，蔡司超级长焦</t>
+          <t>vivo X200(16GB/512GB)</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -43280,7 +43277,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>vivo X200(16GB/1TB) 天玑9400，全等深微四曲面屏，蔡司超级长焦</t>
+          <t>vivo X200(16GB/1TB)</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -43355,7 +43352,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>vivo X200 Pro(16GB/512GB) 蔡司2亿APO超级长焦，天玑9400，蔡司大师色彩屏</t>
+          <t>vivo X200 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -43430,7 +43427,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>vivo X200 Pro(16GB/1TB/卫星通信版) 蔡司2亿APO超级长焦，天玑9400，蔡司大师色彩屏</t>
+          <t>vivo X200 Pro(16GB/1TB/卫星通信版)</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -43580,7 +43577,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>荣耀X60 Pro(8GB/128GB) 青海湖电池，绿洲护眼屏，抗摔防水耐磨</t>
+          <t>荣耀X60 Pro(8GB/128GB)</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -43655,7 +43652,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>OPPO A3i（8GB/256GB） 超硬核抗摔架构，120Hz高刷超亮屏</t>
+          <t>OPPO A3i（8GB/256GB）</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -43730,7 +43727,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>HUAWEI nova 13 Pro（256GB） 前后多焦段人像，AI修图，北斗卫星图片信息</t>
+          <t>HUAWEI nova 13 Pro（256GB）</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -43795,7 +43792,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>荣耀Magic7 Pro(12GB/256GB) 荣耀AI鹰眼相机，骁龙8至尊版，第三代青海湖电池</t>
+          <t>荣耀Magic7 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -43870,7 +43867,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>HUAWEI nova 13(512GB) 前置6000万超广角人像，AI修图，北斗卫星图片消息</t>
+          <t>HUAWEI nova 13(512GB)</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -43935,7 +43932,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>HUAWEI nova 13 Pro（512GB） 前后多焦段人像，AI修图，北斗卫星图片信息</t>
+          <t>HUAWEI nova 13 Pro（512GB）</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -44000,7 +43997,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>OPPO Find X8(16GB/1TB) 潮汐引擎，天玑9400，四等边直屏</t>
+          <t>OPPO Find X8(16GB/1TB)</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -44075,7 +44072,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>荣耀Magic7 Pro(16GB/512GB) 荣耀AI鹰眼相机，骁龙8至尊版，第三代青海湖电池</t>
+          <t>荣耀Magic7 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -44150,7 +44147,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>荣耀Magic7(16GB/1TB) 骁龙8至尊版，绿洲护眼屏，巨犀玻璃</t>
+          <t>荣耀Magic7(16GB/1TB)</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -44225,7 +44222,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>三星W25(16GB/1TB) 2亿像素，新一代Bixby，第三代骁龙8</t>
+          <t>三星W25(16GB/1TB)</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -44292,7 +44289,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>vivo S20 Pro(12GB/256GB) 柔光四主摄，蓝晶×天玑9300+，超级潜望长焦</t>
+          <t>vivo S20 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -44367,7 +44364,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>vivo S20(8GB/256GB) 6500mAh超薄长续航，7.19mm轻薄直屏，5000万防畸变柔光自拍</t>
+          <t>vivo S20(8GB/256GB)</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -44442,7 +44439,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>荣耀300(8GB/256GB) 单反级雅顾人像，5000万潜望长焦，第三代骁龙7旗舰芯</t>
+          <t>荣耀300(8GB/256GB)</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -44517,7 +44514,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>荣耀300 Pro（12GB/256GB） 单反级雅顾人像，5000万潜望长焦，第三代骁龙8</t>
+          <t>荣耀300 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -44592,7 +44589,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>OPPO Reno 13(12GB/256GB) AI实况照，IP69防水，双芯抢网</t>
+          <t>OPPO Reno 13(12GB/256GB)</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -44667,7 +44664,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X6(12GB/512GB) 分布式玄武架构，鸿蒙大屏AI，红枫原色影像</t>
+          <t>HUAWEI Mate X6(12GB/512GB)</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -44730,7 +44727,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 70(12GB/256GB) 鸿蒙AI，红枫原色影像，超可靠玄武架构</t>
+          <t>HUAWEI Mate 70(12GB/256GB)</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -45112,7 +45109,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 70 RS 非凡大师(16GB/512GB) 双层OLED临境显示，高亮钛玄武架构，传奇星钻设计</t>
+          <t>HUAWEI Mate 70 RS 非凡大师(16GB/512GB)</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -45179,7 +45176,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>OPPO Reno 13(12GB/512GB) AI实况照，IP69防水，双芯抢网</t>
+          <t>OPPO Reno 13(12GB/512GB)</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -45254,7 +45251,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>华为Mate 70 RS 非凡大师(16GB/1TB) 双层OLED临境显示，高亮钛玄武架构，传奇星钻设计</t>
+          <t>华为Mate 70 RS 非凡大师(16GB/1TB)</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -45321,7 +45318,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X6 典藏版(16GB/512GB) 分布式玄武架构，鸿蒙大屏AI，红枫原色影像</t>
+          <t>HUAWEI Mate X6 典藏版(16GB/512GB)</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -45384,7 +45381,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X6 典藏版(16GB/1TB) 分布式玄武架构，鸿蒙大屏AI，红枫原色影像</t>
+          <t>HUAWEI Mate X6 典藏版(16GB/1TB)</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -45447,7 +45444,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X6(12GB/256GB) 分布式玄武架构，鸿蒙大屏AI，红枫原色影像</t>
+          <t>HUAWEI Mate X6(12GB/256GB)</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -45510,7 +45507,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>荣耀GT(12GB/256GB) 第三代骁龙8，绿洲护眼屏，荣耀幻影引擎</t>
+          <t>荣耀GT(12GB/256GB)</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -45585,7 +45582,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>荣耀GT(12GB/512GB) 第三代骁龙8，绿洲护眼屏，荣耀幻影引擎</t>
+          <t>荣耀GT(12GB/512GB)</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -45660,7 +45657,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>vivo Y300(8GB/128GB) 新一代超级扬声器，6500mAh超薄蓝海电池，超抗摔护眼直屏</t>
+          <t>vivo Y300(8GB/128GB)</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -45735,7 +45732,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>vivo Y300(12GB/512GB) 新一代超级扬声器，6500mAh超薄蓝海电池，超抗摔护眼直屏</t>
+          <t>vivo Y300(12GB/512GB)</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -45810,7 +45807,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>荣耀Magic7 RSR(24GB/1TB) 2亿超感光潜望长焦，骁龙8至尊版，双卫星通信</t>
+          <t>荣耀Magic7 RSR(24GB/1TB)</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -45885,7 +45882,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>OPPO Find X8 Ultra(12GB/256GB) 骁龙8至尊版，极窄边直屏，AI一键闪记</t>
+          <t>OPPO Find X8 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -45960,7 +45957,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>华为畅享 70X(128GB) 鸿蒙安全，华为巨鲸长续航，双曲护眼屏</t>
+          <t>华为畅享 70X(128GB)</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -46025,7 +46022,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>华为畅享 70X(256GB) 鸿蒙安全，华为巨鲸长续航，双曲护眼屏</t>
+          <t>华为畅享 70X(256GB)</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -46090,7 +46087,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>华为畅享 70X(512GB) 鸿蒙安全，华为巨鲸长续航，双曲护眼屏</t>
+          <t>华为畅享 70X(512GB)</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -46155,7 +46152,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>三星Galaxy S25(12GB/256GB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25(12GB/256GB)</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -46222,7 +46219,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>三星Galaxy S25+(12GB/256GB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25+(12GB/256GB)</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -46289,7 +46286,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>三星Galaxy S25(12GB/512GB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25(12GB/512GB)</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -46356,7 +46353,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>三星Galaxy S25 Ultra(12GB/512GB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -46427,7 +46424,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>三星Galaxy S25 Ultra(16GB/1TB) 超拟人AI助理，骁龙8至尊版，AI拍照</t>
+          <t>三星Galaxy S25 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -46498,7 +46495,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>OPPO Find N5(12GB/256GB) AI 5G折叠屏，骁龙8至尊版，超长续航电池</t>
+          <t>OPPO Find N5(12GB/256GB)</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -46573,7 +46570,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>苹果iPhone 16e（256GB） 超视网膜XDR显示屏，A18处理器，6.1英寸显示屏</t>
+          <t>苹果iPhone 16e（256GB）</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -46642,7 +46639,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>苹果iPhone 16e（512GB） 超视网膜XDR显示屏，A18处理器，6.1英寸显示屏</t>
+          <t>苹果iPhone 16e（512GB）</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -46711,7 +46708,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>OPPO A5 活力版(8GB/256GB) 天玑6300，IP69满级防水，360°抗摔</t>
+          <t>OPPO A5 活力版(8GB/256GB)</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -46786,7 +46783,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>HUAWEI Pura X(12GB/256GB) 1610阔型屏，鸿蒙操作系统 5，红枫原色影像</t>
+          <t>HUAWEI Pura X(12GB/256GB)</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -46853,7 +46850,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>HUAWEI Pura X(12GB/512GB) 1610阔型屏，鸿蒙操作系统 5，红枫原色影像</t>
+          <t>HUAWEI Pura X(12GB/512GB)</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -46920,7 +46917,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>HUAWEI Pura X(16GB/512GB/典藏版) 1610阔型屏，鸿蒙操作系统 5，红枫原色影像</t>
+          <t>HUAWEI Pura X(16GB/512GB/典藏版)</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -46985,7 +46982,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>HUAWEI Pura X(16GB/1TB/典藏版) 1610阔型屏，鸿蒙操作系统 5，红枫原色影像</t>
+          <t>HUAWEI Pura X(16GB/1TB/典藏版)</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -47052,7 +47049,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>华为Mate 70 Pro 优享版(12GB/256GB) 鸿蒙AI，红枫原色影像，超可靠玄武架构</t>
+          <t>华为Mate 70 Pro 优享版(12GB/256GB)</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -47115,7 +47112,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>华为Mate 70 Pro 优享版(12GB/512GB) 鸿蒙AI，红枫原色影像，超可靠玄武架构</t>
+          <t>华为Mate 70 Pro 优享版(12GB/512GB)</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -47178,7 +47175,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>vivo Y300 Pro+(8GB/128GB) 7300mAh超薄蓝海电池，超耐用金刚磐石架构，高效强芯第三代骁龙7s</t>
+          <t>vivo Y300 Pro+(8GB/128GB)</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -47253,7 +47250,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>三星Galaxy A56(8GB/256GB) 5000万像素，5000mAh大电池，7.4mm机身</t>
+          <t>三星Galaxy A56(8GB/256GB)</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -47324,7 +47321,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>三星Galaxy A56(12GB/256GB) 5000万像素，5000mAh大电池，7.4mm机身</t>
+          <t>三星Galaxy A56(12GB/256GB)</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -47395,7 +47392,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>OPPO Find X8s(12GB/256GB) 极窄四等边，天玑9400+，哈苏人像</t>
+          <t>OPPO Find X8s(12GB/256GB)</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -47470,7 +47467,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>OPPO Find X8s(12GB/512GB) 极窄四等边，天玑9400+，哈苏人像</t>
+          <t>OPPO Find X8s(12GB/512GB)</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -47545,7 +47542,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>OPPO Find X8s+(12GB/256GB) 极窄四等边，哈苏人像，AI一键日记</t>
+          <t>OPPO Find X8s+(12GB/256GB)</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -47620,7 +47617,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>OPPO Find X8 Ultra(16GB/512GB) 骁龙8至尊版，极窄边直屏，AI一键闪记</t>
+          <t>OPPO Find X8 Ultra(16GB/512GB)</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -47695,7 +47692,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>OPPO Find X8 Ultra(16GB/1TB/卫星版) 骁龙8至尊版，极窄边直屏，AI一键闪记，卫星通信</t>
+          <t>OPPO Find X8 Ultra(16GB/1TB/卫星版)</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -47770,7 +47767,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>vivo X200s(12GB/256GB) 蓝晶x天玑 9400+，6200mAh蓝海电池，湿手秒开超声波指纹</t>
+          <t>vivo X200s(12GB/256GB)</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -47845,7 +47842,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>vivo X200 Ultra（12GB/256GB） 蔡司三大定焦大师镜头，蓝图自研影像双芯，全焦段OIS光学防抖</t>
+          <t>vivo X200 Ultra（12GB/256GB）</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -47920,7 +47917,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>荣耀Power(8GB/256GB) 8000mAh青海湖电池，荣耀自研C1+通讯芯片，十面抗摔</t>
+          <t>荣耀Power(8GB/256GB)</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -47995,7 +47992,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>华为Pura 70(12GB/512GB/北斗卫星消息版) 北斗卫星消息，超聚光微距长焦，双超级快充</t>
+          <t>华为Pura 70(12GB/512GB/北斗卫星消息版)</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -48062,7 +48059,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>华为Pura 70(12GB/512GB/标准版) 超高速风驰闪拍，超聚光微距长焦，双超级快充</t>
+          <t>华为Pura 70(12GB/512GB/标准版)</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -48127,7 +48124,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>华为Pura 70(12GB/256GB/标准版) 超高速风驰闪拍，超聚光微距长焦，双超级快充</t>
+          <t>华为Pura 70(12GB/256GB/标准版)</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -48194,7 +48191,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>OPPO K12s(8GB/128GB) 7000mAh五年长寿大电池，80W超级闪充，5G AI</t>
+          <t>OPPO K12s(8GB/128GB)</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -48269,7 +48266,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>荣耀GT Pro(12GB/256GB) 骁龙8至尊领先版，7200mAh青海湖电池，AI鹰眼相机</t>
+          <t>荣耀GT Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -48344,7 +48341,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>vivo X200s(16GB/256GB) 蓝晶x天玑 9400+，6200mAh蓝海电池，湿手秒开超声波指纹</t>
+          <t>vivo X200s(16GB/256GB)</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -48419,7 +48416,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>vivo X200s(12GB/512GB) 蓝晶x天玑 9400+，6200mAh蓝海电池，湿手秒开超声波指纹</t>
+          <t>vivo X200s(12GB/512GB)</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -48494,7 +48491,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>vivo X200s(16GB/512GB) 蓝晶x天玑 9400+，6200mAh蓝海电池，湿手秒开超声波指纹</t>
+          <t>vivo X200s(16GB/512GB)</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -48569,7 +48566,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>vivo X200s(16GB/1TB) 蓝晶x天玑 9400+，6200mAh蓝海电池，湿手秒开超声波指纹</t>
+          <t>vivo X200s(16GB/1TB)</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -48644,7 +48641,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>vivo X200 Ultra（16GB/512GB） 蔡司三大定焦大师镜头，蓝图自研影像双芯，全焦段OIS光学防抖</t>
+          <t>vivo X200 Ultra（16GB/512GB）</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -48719,7 +48716,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>vivo X200 Ultra（16GB/1TB） 蔡司三大定焦大师镜头，蓝图自研影像双芯，全焦段OIS光学防抖</t>
+          <t>vivo X200 Ultra（16GB/1TB）</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -48794,7 +48791,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>荣耀X70i(8GB/256GB) 一亿像素，AI拍照键，大屏AI</t>
+          <t>荣耀X70i(8GB/256GB)</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -48869,7 +48866,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>荣耀X70i(12GB/256GB) 一亿像素，AI拍照键，大屏AI</t>
+          <t>荣耀X70i(12GB/256GB)</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -48944,7 +48941,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>荣耀X70i(12GB/512GB) 一亿像素，AI拍照键，大屏AI</t>
+          <t>荣耀X70i(12GB/512GB)</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -49019,7 +49016,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>华为畅享 80（128GB） 6620mAh电池超能续航，玄甲架构，双五星超耐摔</t>
+          <t>华为畅享 80（128GB）</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -49084,7 +49081,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>华为畅享 80（256GB） 6620mAh电池超能续航，玄甲架构，双五星超耐摔</t>
+          <t>华为畅享 80（256GB）</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -49149,7 +49146,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>华为畅享 80（512GB） 6620mAh电池超能续航，玄甲架构，双五星超耐摔</t>
+          <t>华为畅享 80（512GB）</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -49214,7 +49211,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>华为畅享 70X活力版(128GB) 6100mAh华为巨鲸电池，1.5K臻彩护眼屏，5000万高清影像</t>
+          <t>华为畅享 70X活力版(128GB)</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -49279,7 +49276,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>vivo Y300i(8GB/256GB) 全面抗摔金刚盾玻璃 ，6500mAh超薄蓝海电池， 400%双扬大音量</t>
+          <t>vivo Y300i(8GB/256GB)</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -49354,7 +49351,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>vivo Y300i(12GB/256GB) 全面抗摔金刚盾玻璃 ，6500mAh超薄蓝海电池， 400%双扬大音量</t>
+          <t>vivo Y300i(12GB/256GB)</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -49429,7 +49426,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>vivo Y300i(12GB/512GB) 全面抗摔金刚盾玻璃 ，6500mAh超薄蓝海电池， 400%双扬大音量</t>
+          <t>vivo Y300i(12GB/512GB)</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -49504,7 +49501,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>vivo Y300i(8GB/128GB) 全面抗摔金刚盾玻璃 ，6500mAh超薄蓝海电池， 400%双扬大音量</t>
+          <t>vivo Y300i(8GB/128GB)</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -49579,7 +49576,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>三星Galaxy S25 Edge（12GB/256GB） 2亿像素，超纤薄机身，Galaxy AI</t>
+          <t>三星Galaxy S25 Edge（12GB/256GB）</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -49654,7 +49651,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>三星Galaxy S25 Edge（12GB/512GB） 2亿像素，超纤薄机身，Galaxy AI</t>
+          <t>三星Galaxy S25 Edge（12GB/512GB）</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -49729,7 +49726,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>OPPO Reno14(12GB/256GB) 天玑 8350 旗舰芯，6000mAh长寿耐用大电池，ColorOS 15系统</t>
+          <t>OPPO Reno14(12GB/256GB)</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -49804,7 +49801,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>华为nova 14 Ultra（256GB） 全焦段红枫质感人像，天通北斗双卫星通信，鸿蒙AI</t>
+          <t>华为nova 14 Ultra（256GB）</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -49869,7 +49866,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>华为nova 14 Pro（256GB） 多焦段红枫质感人像，鸿蒙AI，鸿蒙智慧通信</t>
+          <t>华为nova 14 Pro（256GB）</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -49934,7 +49931,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>华为nova 14（256GB） 置多焦段质感人像，鸿蒙AI，100W华为超级快充Turbo</t>
+          <t>华为nova 14（256GB）</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -49999,7 +49996,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>vivo Y300 GT(8GB/256GB) 7620mAh超薄蓝海电池，天玑8400满血版，军工级耐用品质</t>
+          <t>vivo Y300 GT(8GB/256GB)</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -50074,7 +50071,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>vivo S30 Pro mini(12GB/256GB) 6.31英寸多彩小直屏，希区柯克变焦实况，6500mAh小屏续航战神</t>
+          <t>vivo S30 Pro mini(12GB/256GB)</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -50149,7 +50146,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>vivo S30 Pro mini(12GB/512GB) 6.31英寸多彩小直屏，希区柯克变焦实况，6500mAh小屏续航战神</t>
+          <t>vivo S30 Pro mini(12GB/512GB)</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -50224,7 +50221,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>vivo S30 Pro mini(16GB/512GB) 6.31英寸多彩小直屏，希区柯克变焦实况，6500mAh小屏续航战神</t>
+          <t>vivo S30 Pro mini(16GB/512GB)</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -50299,7 +50296,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>vivo S30(12GB/256GB) 多彩轻薄直屏，5000 万索尼超级潜望长焦，全球首批高通第四代骁龙 7</t>
+          <t>vivo S30(12GB/256GB)</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -50374,7 +50371,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>vivo S30(12GB/512GB) 多彩轻薄直屏，5000 万索尼超级潜望长焦，全球首批高通第四代骁龙 7</t>
+          <t>vivo S30(12GB/512GB)</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -50449,7 +50446,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>vivo S30(16GB/512GB) 多彩轻薄直屏，5000 万索尼超级潜望长焦，全球首批高通第四代骁龙 7</t>
+          <t>vivo S30(16GB/512GB)</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -50524,7 +50521,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>华为nova 14（512GB） 置多焦段质感人像，鸿蒙AI，100W华为超级快充Turbo</t>
+          <t>华为nova 14（512GB）</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -50589,7 +50586,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>华为nova 14 Pro（512GB） 多焦段红枫质感人像，鸿蒙AI，鸿蒙智慧通信</t>
+          <t>华为nova 14 Pro（512GB）</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -50654,7 +50651,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>华为nova 14 Pro（512GB/昆仑玻璃版） 多焦段红枫质感人像，鸿蒙AI，鸿蒙智慧通信</t>
+          <t>华为nova 14 Pro（512GB/昆仑玻璃版）</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -50719,7 +50716,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>华为nova 14 Ultra（512GB） 全焦段红枫质感人像，天通北斗双卫星通信，鸿蒙AI</t>
+          <t>华为nova 14 Ultra（512GB）</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -50849,7 +50846,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>荣耀400(12GB/256GB) 第四代骁龙7移动平台，2亿超清写真人像，荣耀青海湖电池</t>
+          <t>荣耀400(12GB/256GB)</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -50924,7 +50921,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>荣耀400 Pro(12GB/256GB) 2亿超清写真人像，7200mAh青海湖大电池，荣耀绿洲护眼屏</t>
+          <t>荣耀400 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -50999,7 +50996,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>荣耀400 Pro(12GB/512GB) 2亿超清写真人像，7200mAh青海湖大电池，荣耀绿洲护眼屏</t>
+          <t>荣耀400 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -51141,7 +51138,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>华为Pura 80 Pro+（16GB/512GB） 一英寸高动态主摄，个性色卡 AI辅助构图，全新鸿蒙AI</t>
+          <t>华为Pura 80 Pro+（16GB/512GB）</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -51208,7 +51205,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>华为Pura 80 Pro(12GB/256GB) 一英寸主摄，个性色卡 AI辅助构图，全新鸿蒙AI</t>
+          <t>华为Pura 80 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -51275,7 +51272,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>荣耀X60 GT（12GB/256GB） 骁龙旗舰芯片，荣耀绿洲护眼屏，6300mAh青海湖电池</t>
+          <t>荣耀X60 GT（12GB/256GB）</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -51350,7 +51347,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>华为Pura 80 Ultra（16GB/512GB） 一英寸超高动态主摄，超大底双长焦，全新鸿蒙AI</t>
+          <t>华为Pura 80 Ultra（16GB/512GB）</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -51417,7 +51414,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>华为Pura 80 Ultra（16GB/1TB） 一英寸超高动态主摄，超大底双长焦，全新鸿蒙AI</t>
+          <t>华为Pura 80 Ultra（16GB/1TB）</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -51484,7 +51481,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>华为Pura 80 Pro(12GB/512GB) 一英寸主摄，个性色卡 AI辅助构图，全新鸿蒙AI</t>
+          <t>华为Pura 80 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -51551,7 +51548,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>华为Pura 80 Pro+（16GB/1TB） 一英寸高动态主摄，个性色卡 AI辅助构图，全新鸿蒙AI</t>
+          <t>华为Pura 80 Pro+（16GB/1TB）</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -51752,7 +51749,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>vivo X Fold5（12GB/256GB） 等效6000mAh蓝海电池，蔡司超级长焦，三防折叠屏</t>
+          <t>vivo X Fold5（12GB/256GB）</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -51827,7 +51824,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>vivo X Fold5（12GB/512GB） 等效6000mAh蓝海电池，蔡司超级长焦，三防折叠屏</t>
+          <t>vivo X Fold5（12GB/512GB）</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -51902,7 +51899,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>vivo X Fold5（16GB+512GB） 等效6000mAh蓝海电池，蔡司超级长焦，三防折叠屏</t>
+          <t>vivo X Fold5（16GB+512GB）</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -51977,7 +51974,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>荣耀Magic V5（12GB/256GB） 骁龙8至尊版，青海湖刀片电池，AI鹰眼相机</t>
+          <t>荣耀Magic V5（12GB/256GB）</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -52052,7 +52049,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>荣耀X70(8GB/128GB) 金标十面抗摔，IP69防水，8300mAh电池</t>
+          <t>荣耀X70(8GB/128GB)</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -52127,7 +52124,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>荣耀X70(8GB/256GB) 金标十面抗摔，IP69防水，8300mAh电池</t>
+          <t>荣耀X70(8GB/256GB)</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -52202,7 +52199,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>荣耀X70(12GB/256GB) 金标十面抗摔，IP69防水，8300mAh电池</t>
+          <t>荣耀X70(12GB/256GB)</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -52277,7 +52274,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>荣耀X70(12GB/512GB) 金标十面抗摔，IP69防水，8300mAh电池</t>
+          <t>荣耀X70(12GB/512GB)</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -52486,7 +52483,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip7（12GB/256GB） 多模态Galaxy Al，超大视野智能外屏，5000万超清主摄</t>
+          <t>三星Galaxy Z Flip7（12GB/256GB）</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -52557,7 +52554,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip7（12GB/512GB） 多模态Galaxy Al，超大视野智能外屏，5000万超清主摄</t>
+          <t>三星Galaxy Z Flip7（12GB/512GB）</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -52628,7 +52625,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip7 FE（8GB/256GB） Al大视野智能外屏，5000万像素超清相机，多模态Galaxy AI</t>
+          <t>三星Galaxy Z Flip7 FE（8GB/256GB）</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -52703,7 +52700,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>OPPO K13 Turbo Pro(12GB/256GB) 疾风散热引擎，潮汐引擎，第四代骁龙8s</t>
+          <t>OPPO K13 Turbo Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -52778,7 +52775,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>OPPO K13 Turbo（12GB/256GB） 疾风散热引擎，潮汐引擎，天玑8450</t>
+          <t>OPPO K13 Turbo（12GB/256GB）</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -52853,7 +52850,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>荣耀Magic V Flip2（12GB/256GB） 2亿超清写真自拍，5500mAh青海湖电池，4英寸大外屏</t>
+          <t>荣耀Magic V Flip2（12GB/256GB）</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -52928,7 +52925,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>vivo Y500(8GB/128GB) 耐用抗摔，流畅高刷，稳定续航</t>
+          <t>vivo Y500(8GB/128GB)</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -53003,7 +53000,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>vivo Y50 5G(4GB+128GB) 超长续航，可靠耐用，五星抗摔</t>
+          <t>vivo Y50 5G(4GB+128GB)</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -53078,7 +53075,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>vivo Y50 5G(12GB+256GB) 超长续航，可靠耐用，五星抗摔</t>
+          <t>vivo Y50 5G(12GB+256GB)</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -53153,7 +53150,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>苹果iPhone 17（256GB） A19芯片，4800万像素融合式双摄系统，6.3英寸</t>
+          <t>苹果iPhone 17（256GB）</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -53226,7 +53223,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro（256GB） 视网膜XDR显示屏，铝金属一体成型机身，A19 Pro 芯片</t>
+          <t>苹果iPhone 17 Pro（256GB）</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -53293,7 +53290,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>华为Mate XTs 非凡大师（16GB/256GB） 三折叠大屏，鸿蒙大屏AI，红枫原色影像</t>
+          <t>华为Mate XTs 非凡大师（16GB/256GB）</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -53360,7 +53357,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro Max（256GB） 超视网膜XDR显示屏，铝金属一体成型机身，A19 Pro芯片</t>
+          <t>苹果iPhone 17 Pro Max（256GB）</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -53498,7 +53495,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>vivo Y500(8GB/256GB) 耐用抗摔，流畅高刷，稳定续航</t>
+          <t>vivo Y500(8GB/256GB)</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -53573,7 +53570,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>vivo Y500(12GB/256GB) 耐用抗摔，流畅高刷，稳定续航</t>
+          <t>vivo Y500(12GB/256GB)</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -53648,7 +53645,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>vivo Y500(12GB/512GB) 耐用抗摔，流畅高刷，稳定续航</t>
+          <t>vivo Y500(12GB/512GB)</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -53723,7 +53720,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>华为Mate XTs 非凡大师（16GB/1TB） 三折叠大屏，鸿蒙大屏AI，红枫原色影像</t>
+          <t>华为Mate XTs 非凡大师（16GB/1TB）</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -53790,7 +53787,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>OPPO A6 Pro(8GB/256GB) 越级流畅双引擎，IP69 满级防水，超抗摔金刚石架构</t>
+          <t>OPPO A6 Pro(8GB/256GB)</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -53865,7 +53862,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>苹果iPhone 17（512GB） A19芯片，4800万像素融合式双摄系统，6.3英寸</t>
+          <t>苹果iPhone 17（512GB）</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -53938,7 +53935,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro（512GB） 视网膜XDR显示屏，铝金属一体成型机身，A19 Pro 芯片</t>
+          <t>苹果iPhone 17 Pro（512GB）</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -54072,7 +54069,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro Max（512GB） 超视网膜XDR显示屏，铝金属一体成型机身，A19 Pro芯片</t>
+          <t>苹果iPhone 17 Pro Max（512GB）</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -54139,7 +54136,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro Max（1TB） 超视网膜XDR显示屏，铝金属一体成型机身，A19 Pro芯片</t>
+          <t>苹果iPhone 17 Pro Max（1TB）</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -54206,7 +54203,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro Max（2TB） 超视网膜XDR显示屏，铝金属一体成型机身，A19 Pro芯片</t>
+          <t>苹果iPhone 17 Pro Max（2TB）</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -54415,7 +54412,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>OPPO A6i(6GB/128GB) IP65生活防水，超抗摔金刚石架构，6000mAh耐用电池</t>
+          <t>OPPO A6i(6GB/128GB)</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -54490,7 +54487,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>vivo X300 Pro（12GB+256GB） 蔡司2亿APO超级长焦，蓝图影像双芯，OriginOS 6</t>
+          <t>vivo X300 Pro（12GB+256GB）</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -54565,7 +54562,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>vivo X300(12GB/256GB) 蔡司2亿超级主摄，蔡司APO超级长焦，5年持久流畅</t>
+          <t>vivo X300(12GB/256GB)</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -54640,7 +54637,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>OPPO Find X9(12GB/256GB) 4K超清实况照片，7025mAh，天玑9500</t>
+          <t>OPPO Find X9(12GB/256GB)</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -54715,7 +54712,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Pro(12GB/256GB) 天玑9500，哈苏2亿超清长焦镜头，7500mAh电池</t>
+          <t>OPPO Find X9 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -54790,7 +54787,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>vivo Y300t(8GB/128GB) 6500mAh超薄蓝海电池，天玑7300长久流畅芯，全功能NFC</t>
+          <t>vivo Y300t(8GB/128GB)</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -54865,7 +54862,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>vivo Y300t(8GB/256GB) 6500mAh超薄蓝海电池，天玑7300长久流畅芯，全功能NFC</t>
+          <t>vivo Y300t(8GB/256GB)</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -54940,7 +54937,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>vivo Y300t(12GB/512GB) 6500mAh超薄蓝海电池，天玑7300长久流畅芯，全功能NFC</t>
+          <t>vivo Y300t(12GB/512GB)</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -55015,7 +55012,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>荣耀Magic8(12GB/256GB) YOYO智能体，超夜神长焦，第五代骁龙8至尊版</t>
+          <t>荣耀Magic8(12GB/256GB)</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -55090,7 +55087,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>荣耀Magic8(12GB/512GB) YOYO智能体，超夜神长焦，第五代骁龙8至尊版</t>
+          <t>荣耀Magic8(12GB/512GB)</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -55165,7 +55162,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>荣耀Magic8(16GB/512GB) YOYO智能体，超夜神长焦，第五代骁龙8至尊版</t>
+          <t>荣耀Magic8(16GB/512GB)</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -55240,7 +55237,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro(12GB/256GB) 第五代骁龙8至尊版，2亿超夜神长焦，双3D解锁</t>
+          <t>荣耀Magic8 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -55315,7 +55312,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro(12GB/512GB) 第五代骁龙8至尊版，2亿超夜神长焦，双3D解锁</t>
+          <t>荣耀Magic8 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -55390,7 +55387,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro(16GB/512GB) 第五代骁龙8至尊版，2亿超夜神长焦，双3D解锁</t>
+          <t>荣耀Magic8 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -55465,7 +55462,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro(16GB/1TB) 第五代骁龙8至尊版，2亿超夜神长焦，双3D解锁</t>
+          <t>荣耀Magic8 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -55540,7 +55537,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>三星W26（16GB/512GB） 超高端尊奢质感机身设计，2亿像素主摄，骁龙8至尊版</t>
+          <t>三星W26（16GB/512GB）</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -55615,7 +55612,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>三星W26（16GB/1TB） 超高端尊奢质感机身设计，2亿像素主摄，骁龙8至尊版</t>
+          <t>三星W26（16GB/1TB）</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -55690,7 +55687,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>OPPO Find X9(12GB/512GB) 4K超清实况照片，7025mAh，天玑9500</t>
+          <t>OPPO Find X9(12GB/512GB)</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -55765,7 +55762,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>vivo X300(16GB/256GB) 蔡司2亿超级主摄，蔡司APO超级长焦，5年持久流畅</t>
+          <t>vivo X300(16GB/256GB)</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -55840,7 +55837,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>vivo X300(12GB+512GB) 蔡司2亿超级主摄，蔡司APO超级长焦，5年持久流畅</t>
+          <t>vivo X300(12GB+512GB)</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -55915,7 +55912,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>vivo X300( 16GB/512GB) 蔡司2亿超级主摄，蔡司APO超级长焦，5年持久流畅</t>
+          <t>vivo X300( 16GB/512GB)</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -55990,7 +55987,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>vivo X300(16GB/1TB) 蔡司2亿超级主摄，蔡司APO超级长焦，5年持久流畅</t>
+          <t>vivo X300(16GB/1TB)</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -56065,7 +56062,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>vivo X300 Pro（16GB+512GB） 蔡司2亿APO超级长焦，蓝图影像双芯，OriginOS 6</t>
+          <t>vivo X300 Pro（16GB+512GB）</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -56140,7 +56137,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>vivo X300 Pro（16GB+1TB） 蔡司2亿APO超级长焦，蓝图影像双芯，OriginOS 6</t>
+          <t>vivo X300 Pro（16GB+1TB）</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -56215,7 +56212,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>vivo X300 Pro（16GB+1TB摄影师套装） 蔡司2亿APO超级长焦，蓝图影像双芯，OriginOS 6</t>
+          <t>vivo X300 Pro（16GB+1TB摄影师套装）</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -56290,7 +56287,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Pro(12GB/512GB) 天玑9500，哈苏2亿超清长焦镜头，7500mAh电池</t>
+          <t>OPPO Find X9 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -56365,7 +56362,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Pro(16GB/512GB) 天玑9500，哈苏2亿超清长焦镜头，7500mAh电池</t>
+          <t>OPPO Find X9 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -56440,7 +56437,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Pro(16GB/1TB) 天玑9500，哈苏2亿超清长焦镜头，7500mAh电池</t>
+          <t>OPPO Find X9 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -56515,7 +56512,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>华为nova 14 活力版（256GB） 前后双5000万超清影像，鸿蒙安全纯净防诈，鸿蒙智慧通信</t>
+          <t>华为nova 14 活力版（256GB）</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -56580,7 +56577,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>华为nova 14 活力版（512GB） 前后双5000万超清影像，鸿蒙安全纯净防诈，鸿蒙智慧通信</t>
+          <t>华为nova 14 活力版（512GB）</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -56714,7 +56711,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>OPPO K13s（8GB/256GB） 第三代骁龙7，山海通信增强芯片，超流畅ColorOS 15</t>
+          <t>OPPO K13s（8GB/256GB）</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -56789,7 +56786,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>OPPO K13s（12GB/512GB） 第三代骁龙7，山海通信增强芯片，超流畅ColorOS 15</t>
+          <t>OPPO K13s（12GB/512GB）</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -56864,7 +56861,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80(12GB/256GB) 麒麟9020芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80(12GB/256GB)</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -56935,7 +56932,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>华为Mate 70 Air(12GB/256GB) 超薄长续航，7英寸华为临境大屏，红枫原色影像</t>
+          <t>华为Mate 70 Air(12GB/256GB)</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -57006,7 +57003,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>华为Mate 70 Air(12GB/512GB) 超薄长续航，7英寸华为临境大屏，红枫原色影像</t>
+          <t>华为Mate 70 Air(12GB/512GB)</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -57077,7 +57074,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>vivo Y500 Pro(8GB/128GB) 2亿HP5旗舰级主摄，7000mAh蓝海电池，IP68+IP69满级防水</t>
+          <t>vivo Y500 Pro(8GB/128GB)</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -57152,7 +57149,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>vivo Y500 Pro(8GB/256GB) 2亿HP5旗舰级主摄，7000mAh蓝海电池，IP68+IP69满级防水</t>
+          <t>vivo Y500 Pro(8GB/256GB)</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -57227,7 +57224,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>vivo Y500 Pro(12GB/256GB) 2亿HP5旗舰级主摄，7000mAh蓝海电池，IP68+IP69满级防水</t>
+          <t>vivo Y500 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -57302,7 +57299,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>vivo Y500 Pro(12GB/512GB) 2亿HP5旗舰级主摄，7000mAh蓝海电池，IP68+IP69满级防水</t>
+          <t>vivo Y500 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -57377,7 +57374,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>OPPO Reno15(12GB/256GB) 2亿超清影像，出圈实况，精致小直屏</t>
+          <t>OPPO Reno15(12GB/256GB)</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -57452,7 +57449,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>OPPO Reno15(12GB/512GB) 2亿超清影像，出圈实况，精致小直屏</t>
+          <t>OPPO Reno15(12GB/512GB)</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -57527,7 +57524,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>OPPO Reno15 Pro(12GB+256GB) 天玑8450，2亿像素超清影像，出圈实况</t>
+          <t>OPPO Reno15 Pro(12GB+256GB)</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -57602,7 +57599,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>OPPO Reno15 Pro(12GB/512GB) 天玑8450，2亿像素超清影像，出圈实况</t>
+          <t>OPPO Reno15 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -57677,7 +57674,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro(12GB/256GB) 麒麟9030系列芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -57744,7 +57741,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro Max(16GB/512GB) 麒麟9030 Pro芯片，全金属玄武架构，超透亮灵珑</t>
+          <t>HUAWEI Mate 80 Pro Max(16GB/512GB)</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -57811,7 +57808,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 RS 非凡大师(20GB/512GB) 超广色域灵珑屏，高亮钛玄武架构，第二代红枫影像</t>
+          <t>HUAWEI Mate 80 RS 非凡大师(20GB/512GB)</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -57882,7 +57879,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>荣耀500(12GB/256GB) 骁龙8至尊旗舰芯，8000mAh青海湖大电池，2亿Al超清影像系统</t>
+          <t>荣耀500(12GB/256GB)</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -57957,7 +57954,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>荣耀500 Pro(12GB/256GB) 骁龙8至尊旗舰芯，青海湖电池，AI手机</t>
+          <t>荣耀500 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -58032,7 +58029,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>荣耀500 Pro(12GB/512GB) 骁龙8至尊旗舰芯，青海湖电池，AI手机</t>
+          <t>荣耀500 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -58107,7 +58104,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>荣耀500 Pro(16GB/512GB) 骁龙8至尊旗舰芯，青海湖电池，AI手机</t>
+          <t>荣耀500 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -58182,7 +58179,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>荣耀500 Pro(16GB/1TB) 骁龙8至尊旗舰芯，青海湖电池，AI手机</t>
+          <t>荣耀500 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -58257,7 +58254,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>HUAWEI Mate X7（12GB/512GB） 麒麟9030 Pro芯片，超可靠折叠玄武架构，第二代红枫影像</t>
+          <t>HUAWEI Mate X7（12GB/512GB）</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -58324,7 +58321,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>荣耀500(12GB/512GB) 骁龙8至尊旗舰芯，8000mAh青海湖大电池，2亿Al超清影像系统</t>
+          <t>荣耀500(12GB/512GB)</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -58399,7 +58396,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>荣耀500(16GB/512GB) 骁龙8至尊旗舰芯，8000mAh青海湖大电池，2亿Al超清影像系统</t>
+          <t>荣耀500(16GB/512GB)</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -58474,7 +58471,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80(12GB/512GB) 麒麟9020芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80(12GB/512GB)</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -58545,7 +58542,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80(16GB/512GB) 麒麟9020芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80(16GB/512GB)</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -58616,7 +58613,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro(12GB/512GB) 麒麟9030系列芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -58683,7 +58680,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro(16GB/512GB) 麒麟9030系列芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -58750,7 +58747,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro(16GB/1TB) 麒麟9030系列芯片，第二代红枫影像，鸿蒙AI</t>
+          <t>HUAWEI Mate 80 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -58817,7 +58814,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>华为Mate X7（12GB/256GB） 麒麟9030 Pro芯片，超可靠折叠玄武架构，第二代红枫影像</t>
+          <t>华为Mate X7（12GB/256GB）</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -58884,7 +58881,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>华为Mate X7 典藏版（16GB/512GB） 麒麟9030 Pro芯片，超可靠折叠玄武架构，第二代红枫影像</t>
+          <t>华为Mate X7 典藏版（16GB/512GB）</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -58951,7 +58948,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>华为Mate X7 典藏版（16GB/1TB） 麒麟9030 Pro芯片，超可靠折叠玄武架构，第二代红枫影像</t>
+          <t>华为Mate X7 典藏版（16GB/1TB）</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -59018,7 +59015,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 RS 非凡大师(20GB/1TB) 超广色域灵珑屏，高亮钛玄武架构，第二代红枫影像</t>
+          <t>HUAWEI Mate 80 RS 非凡大师(20GB/1TB)</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -59089,7 +59086,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro Max(16GB/1TB) 麒麟9030 Pro芯片，全金属玄武架构，超透亮灵珑</t>
+          <t>HUAWEI Mate 80 Pro Max(16GB/1TB)</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -59156,7 +59153,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>华为Mate X7 典藏版（16GB/1TB/手写笔套装） 麒麟9030 Pro芯片，超可靠折叠玄武架构，第二代红枫影像</t>
+          <t>华为Mate X7 典藏版（16GB/1TB/手写笔套装）</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -59223,7 +59220,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>vivo S50(12GB/256GB) 主摄级长焦Live，高通第三代骁龙8s，湿手秒开超声波指纹2.0</t>
+          <t>vivo S50(12GB/256GB)</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -59294,7 +59291,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>vivo S50 Pro mini(12GB/256GB) 长焦Live神器，高通第五代骁龙 8，超声波指纹 2.0</t>
+          <t>vivo S50 Pro mini(12GB/256GB)</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -59369,7 +59366,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>三星Galaxy Z TriFold（16GB/512GB） 多功能大屏幕，Galaxy Al，2亿像素广角摄像头</t>
+          <t>三星Galaxy Z TriFold（16GB/512GB）</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -59444,7 +59441,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>三星Galaxy Z TriFold（16GB/1TB） 多功能大屏幕，Galaxy Al，2亿像素广角摄像头</t>
+          <t>三星Galaxy Z TriFold（16GB/1TB）</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -59519,7 +59516,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>OPPO A6l（12GB/256GB） 超抗摔金刚石架构，第三代高通骁龙7，长寿大电池</t>
+          <t>OPPO A6l（12GB/256GB）</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -59594,7 +59591,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>vivo S50 Pro mini(12GB/512GB) 长焦Live神器，高通第五代骁龙 8，超声波指纹 2.0</t>
+          <t>vivo S50 Pro mini(12GB/512GB)</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -59669,7 +59666,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>vivo S50 Pro mini(16GB/512GB) 长焦Live神器，高通第五代骁龙 8，超声波指纹 2.0</t>
+          <t>vivo S50 Pro mini(16GB/512GB)</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -59744,7 +59741,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>vivo S50(16GB/256GB) 主摄级长焦Live，高通第三代骁龙8s，湿手秒开超声波指纹2.0</t>
+          <t>vivo S50(16GB/256GB)</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -59815,7 +59812,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>vivo(S50 12GB/512GB) 主摄级长焦Live，高通第三代骁龙8s，湿手秒开超声波指纹2.0</t>
+          <t>vivo(S50 12GB/512GB) 主摄级长焦Live，高通第三代</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -59886,7 +59883,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>vivo S50(16GB/512GB) 主摄级长焦Live，高通第三代骁龙8s，湿手秒开超声波指纹2.0</t>
+          <t>vivo S50(16GB/512GB)</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -59957,7 +59954,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>华为nova 15（256GB） 多焦段红枫影像，麒麟8020芯片，鸿蒙AI</t>
+          <t>华为nova 15（256GB）</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -60026,7 +60023,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>华为nova 15 Ultra（256GB） 麒麟9系芯片，前后红枫影像，鸿蒙AI</t>
+          <t>华为nova 15 Ultra（256GB）</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -60095,7 +60092,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>荣耀WIN(12GB/256GB) 第五代骁龙8至尊旗舰芯，巨无霸青海湖电池，荣耀东风涡轮散热</t>
+          <t>荣耀WIN(12GB/256GB)</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -60170,7 +60167,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>OPPO Reno15c(12GB/256GB) 5000万像素高清长焦，出圈实况，超流畅ColorOS 16</t>
+          <t>OPPO Reno15c(12GB/256GB)</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -60245,7 +60242,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>荣耀畅玩60A（6GB/128GB） 5300mAh大电池，天玑6300，大屏大音量</t>
+          <t>荣耀畅玩60A（6GB/128GB）</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -60320,7 +60317,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>华为nova 15（512GB） 多焦段红枫影像，麒麟8020芯片，鸿蒙AI</t>
+          <t>华为nova 15（512GB）</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -60389,7 +60386,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>华为nova 15 Pro（256GB） 星耀架构，前后红枫影像，麒麟9010S 芯片</t>
+          <t>华为nova 15 Pro（256GB）</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -60458,7 +60455,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>华为nova 15 Pro（512GB） 星耀架构，前后红枫影像，麒麟9010S 芯片</t>
+          <t>华为nova 15 Pro（512GB）</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -60527,7 +60524,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>华为nova 15 Ultra（512GB） 麒麟9系芯片，前后红枫影像，鸿蒙AI</t>
+          <t>华为nova 15 Ultra（512GB）</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -60596,7 +60593,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>华为nova 15 Ultra（1TB） 麒麟9系芯片，前后红枫影像，鸿蒙AI</t>
+          <t>华为nova 15 Ultra（1TB）</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -60665,7 +60662,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>荣耀WIN(12GB/512GB) 第五代骁龙8至尊旗舰芯，巨无霸青海湖电池，荣耀东风涡轮散热</t>
+          <t>荣耀WIN(12GB/512GB)</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -60740,7 +60737,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>荣耀WIN(16GB/512GB) 第五代骁龙8至尊旗舰芯，巨无霸青海湖电池，荣耀东风涡轮散热</t>
+          <t>荣耀WIN(16GB/512GB)</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -60815,7 +60812,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>荣耀WIN RT(12GB/256GB) 骁龙8至尊旗舰芯，10000mAh青海湖电池，荣耀AI绿洲护眼电竞屏</t>
+          <t>荣耀WIN RT(12GB/256GB)</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -60890,7 +60887,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>荣耀WIN RT(16GB/256GB) 骁龙8至尊旗舰芯，10000mAh青海湖电池，荣耀AI绿洲护眼电竞屏</t>
+          <t>荣耀WIN RT(16GB/256GB)</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -60965,7 +60962,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>荣耀WIN RT(12GB/512GB) 骁龙8至尊旗舰芯，10000mAh青海湖电池，荣耀AI绿洲护眼电竞屏</t>
+          <t>荣耀WIN RT(12GB/512GB)</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -61040,7 +61037,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>荣耀WIN RT(16GB/512GB) 骁龙8至尊旗舰芯，10000mAh青海湖电池，荣耀AI绿洲护眼电竞屏</t>
+          <t>荣耀WIN RT(16GB/512GB)</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -61115,7 +61112,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>荣耀WIN RT(16GB/1TB) 骁龙8至尊旗舰芯，10000mAh青海湖电池，荣耀AI绿洲护眼电竞屏</t>
+          <t>荣耀WIN RT(16GB/1TB)</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -61190,7 +61187,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>荣耀Power2(12GB/256GB) 10080mAh青海湖电池，电梯信号王，天玑8500 Elite</t>
+          <t>荣耀Power2(12GB/256GB)</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -61265,7 +61262,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>荣耀Power2(12GB/512GB) 10080mAh青海湖电池，电梯信号王，天玑8500 Elite</t>
+          <t>荣耀Power2(12GB/512GB)</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -61340,7 +61337,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro Air(12GB/256GB) Pro 级影像旗舰级三摄，青海湖电池，天玑9500芯片</t>
+          <t>荣耀Magic8 Pro Air(12GB/256GB)</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -61415,7 +61412,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro Air(12GB/512GB) Pro 级影像旗舰级三摄，青海湖电池，天玑9500芯片</t>
+          <t>荣耀Magic8 Pro Air(12GB/512GB)</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -61490,7 +61487,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>荣耀Magic8 Pro Air(16GB/512GB) Pro 级影像旗舰级三摄，青海湖电池，天玑9500芯片</t>
+          <t>荣耀Magic8 Pro Air(16GB/512GB)</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -61565,7 +61562,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>荣耀Magic8 RSR保时捷设计(16GB/512GB) 第五代骁龙8至尊版，保时捷设计，2亿超夜神长焦</t>
+          <t>荣耀Magic8 RSR保时捷设计(16GB/512GB)</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -61640,7 +61637,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>荣耀Magic8 RSR保时捷设计(24GB/1TB) 第五代骁龙8至尊版，保时捷设计，2亿超夜神长焦</t>
+          <t>荣耀Magic8 RSR保时捷设计(24GB/1TB)</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -61715,7 +61712,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>三星Galaxy S26（12GB/256GB） 第五代骁龙8至尊版，智慧GalaxyAI，超视觉影像</t>
+          <t>三星Galaxy S26（12GB/256GB）</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -61786,7 +61783,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>三星Galaxy S26+（12GB+512GB） 第五代骁龙8至尊版，高性能影像系统，智慧Galaxy AI</t>
+          <t>三星Galaxy S26+（12GB+512GB）</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -61857,8 +61854,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>三星Galaxy S26 Ultra(12GB/512GB) 防窥屏，亿像素主摄，
-第五代骁龙8至尊版</t>
+          <t>三星Galaxy S26 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -61925,8 +61921,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>三星Galaxy S26 Ultra(16GB/1TB) 防窥屏，亿像素主摄，
-第五代骁龙8至尊版</t>
+          <t>三星Galaxy S26 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -61993,8 +61988,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>三星Galaxy S26 Ultra(12GB/256GB) 防窥屏，亿像素主摄，
-第五代骁龙8至尊版</t>
+          <t>三星Galaxy S26 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -62061,7 +62055,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>OPPO Find N6(12GB/256GB) 第五代骁龙8至尊版，哈苏2亿超清四摄，无感折痕</t>
+          <t>OPPO Find N6(12GB/256GB)</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -62136,7 +62130,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>荣耀Robot Phone（12GB/512GB） 钛合金灵巧云台，ARRI电影，YOYO机器人模式</t>
+          <t>荣耀Robot Phone（12GB/512GB）</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -62211,7 +62205,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>荣耀Magic V6(12GB/256GB) 至臻黑钻屏，第五代骁龙8至尊版，AI会议参谋</t>
+          <t>荣耀Magic V6(12GB/256GB)</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -62286,7 +62280,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>荣耀Magic V6(12GB/512GB) 至臻黑钻屏，第五代骁龙8至尊版，AI会议参谋</t>
+          <t>荣耀Magic V6(12GB/512GB)</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -62361,7 +62355,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>苹果iPhone 17e（256GB） A19芯片，4800万像素融合式摄像头，超视网膜XDR显示屏</t>
+          <t>苹果iPhone 17e（256GB）</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -62432,7 +62426,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>苹果iPhone 17e（512GB） A19芯片，4800万像素融合式摄像头，超视网膜XDR显示屏</t>
+          <t>苹果iPhone 17e（512GB）</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -62572,7 +62566,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 128GB 8500mAh巨鲸大电池，鸿蒙AI，流畅丝滑</t>
+          <t>华为畅享90 Pro Max 128GB 8500mAh巨鲸</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -62641,7 +62635,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>OPPO Find N6(16GB/512GB) 第五代骁龙8至尊版，哈苏2亿超清四摄，无感折痕</t>
+          <t>OPPO Find N6(16GB/512GB)</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -62716,7 +62710,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>vivo X300 Ultra(12GB/256GB) 蔡司大师镜头群，全焦段4K 120fps 10 bit Log，vivo色彩科学</t>
+          <t>vivo X300 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -62791,7 +62785,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro Max 风驰版(16GB/512GB) 麒麟9030 Pro芯片，风驰散热架构，超空间内存技术</t>
+          <t>HUAWEI Mate 80 Pro Max 风驰版(16GB/512GB)</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -62858,7 +62852,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>HUAWEI Mate 80 Pro Max 风驰版(16GB/1TB) 麒麟9030 Pro芯片，风驰散热架构，超空间内存技术</t>
+          <t>HUAWEI Mate 80 Pro Max 风驰版(16GB/1TB)</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -62925,7 +62919,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 256GB 8500mAh巨鲸大电池，鸿蒙AI，流畅丝滑</t>
+          <t>华为畅享90 Pro Max 256GB 8500mAh巨鲸</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -62994,7 +62988,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 512GB 8500mAh巨鲸大电池，鸿蒙AI，流畅丝滑</t>
+          <t>华为畅享90 Pro Max 512GB 8500mAh巨鲸</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -63132,7 +63126,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>华为畅享 90 128GB 麒麟8系芯片，超强性能，华为巨鲸电池</t>
+          <t>华为畅享 90 128GB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -63201,7 +63195,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>华为畅享 90 256GB 麒麟8系芯片，超强性能，华为巨鲸电池</t>
+          <t>华为畅享 90 256GB</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -63270,7 +63264,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>OPPO K15 Pro(12GB/256GB) IPX9满级防水 ，7500mAh大电池 ，5000万像素</t>
+          <t>OPPO K15 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -63345,7 +63339,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>OPPO K15 Pro+(12GB/256GB) 疾风散热引擎， 8000mAh大电池，IPX9满级防水</t>
+          <t>OPPO K15 Pro+(12GB/256GB)</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -63420,7 +63414,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>vivo X300s(12GB/256GB) 蔡司2亿超级主摄，蔡司APO超级长焦，144Hz 蔡司大师色彩屏</t>
+          <t>vivo X300s(12GB/256GB)</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -63495,7 +63489,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>vivo X300 Ultra(16GB/1TB) 蔡司大师镜头群，全焦段4K 120fps 10 bit Log，vivo色彩科学</t>
+          <t>vivo X300 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -63570,7 +63564,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>vivo X300 Ultra(12GB/512GB) 蔡司大师镜头群，全焦段4K 120fps 10 bit Log，vivo色彩科学</t>
+          <t>vivo X300 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -63645,7 +63639,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>vivo X300 Ultra(16GB/512GB) 蔡司大师镜头群，全焦段4K 120fps 10 bit Log，vivo色彩科学</t>
+          <t>vivo X300 Ultra(16GB/512GB)</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -63720,7 +63714,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>vivo X300 Ultra(16GB/1TB摄影师套装) 蔡司大师镜头群，全焦段4K 120fps 10 bit Log，vivo色彩科学</t>
+          <t>vivo X300 Ultra(16GB/1TB摄影师套装)</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -63795,7 +63789,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>vivo X300s(16GB/1TB) 蔡司2亿超级主摄，蔡司APO超级长焦，144Hz 蔡司大师色彩屏</t>
+          <t>vivo X300s(16GB/1TB)</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -63870,7 +63864,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>vivo X300s(12GB/512GB) 蔡司2亿超级主摄，蔡司APO超级长焦，144Hz 蔡司大师色彩屏</t>
+          <t>vivo X300s(12GB/512GB)</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -63945,7 +63939,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>vivo X300s()16GB/+512GB 蔡司2亿超级主摄，蔡司APO超级长焦，144Hz 蔡司大师色彩屏</t>
+          <t>vivo X300s()16GB/+512GB</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -64020,7 +64014,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>vivo X300s(16GB/1TB摄影师套装) 蔡司2亿超级主摄，蔡司APO超级长焦，144Hz 蔡司大师色彩屏</t>
+          <t>vivo X300s(16GB/1TB摄影师套装)</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -64166,7 +64160,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro Max(16GB/512GB) 超大底 2 亿长焦，XMAGE 智拍，抗反光耐刮昆仑玻璃</t>
+          <t>华为Pura 90 Pro Max(16GB/512GB)</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -64237,7 +64231,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro Max(12GB/512GB) 超大底 2 亿长焦，XMAGE 智拍，抗反光耐刮昆仑玻璃</t>
+          <t>华为Pura 90 Pro Max(12GB/512GB)</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -64308,7 +64302,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro Max(16GB/1TB) 超大底 2 亿长焦，XMAGE 智拍，抗反光耐刮昆仑玻璃</t>
+          <t>华为Pura 90 Pro Max(16GB/1TB)</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -64379,7 +64373,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro Max(12GB/256GB) 超大底 2 亿长焦，XMAGE 智拍，抗反光耐刮昆仑玻璃</t>
+          <t>华为Pura 90 Pro Max(12GB/256GB)</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -64450,7 +64444,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro(16GB/512GB) 超聚光微距长焦，XMAGE 智拍，红枫影像 2.0</t>
+          <t>华为Pura 90 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -64521,7 +64515,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro(12GB/512GB) 超聚光微距长焦，XMAGE 智拍，红枫影像 2.0</t>
+          <t>华为Pura 90 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -64592,7 +64586,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro(12GB/256GB) 超聚光微距长焦，XMAGE 智拍，红枫影像 2.0</t>
+          <t>华为Pura 90 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -64663,7 +64657,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>OPPO Find X9s Pro(12GB/256GB) 2亿大底超清主摄，2亿长焦，80W超级闪充</t>
+          <t>OPPO Find X9s Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -64738,7 +64732,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>华为Pura X Max(12GB/256GB) 双面阔型屏，AI 灵感妙创，小艺伴随式 AI</t>
+          <t>华为Pura X Max(12GB/256GB)</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -64809,7 +64803,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Ultra(12GB/256GB) 10倍光变天眼长焦 ，双2亿超大底镜头，100w超级闪充</t>
+          <t>OPPO Find X9 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -64884,9 +64878,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>OPPO A6s Pro(8GB/256GB) 天玑6360 Max，
-7000mAh电池容量，
-80W超级闪充</t>
+          <t>OPPO A6s Pro(8GB/256GB)</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -64961,7 +64953,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>华为Pura X Max(12GB/512GB) 双面阔型屏，AI 灵感妙创，小艺伴随式 AI</t>
+          <t>华为Pura X Max(12GB/512GB)</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -65032,7 +65024,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>华为Pura X Max(16GB/512GB/典藏版) 双面阔型屏，AI 灵感妙创，小艺伴随式 AI</t>
+          <t>华为Pura X Max(16GB/512GB/典藏版)</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -65103,7 +65095,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>华为Pura X Max(16GB/1TB/典藏版) 双面阔型屏，AI 灵感妙创，小艺伴随式 AI</t>
+          <t>华为Pura X Max(16GB/1TB/典藏版)</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -65174,7 +65166,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>华为Pura 90 Pro(16GB/1TB) 超聚光微距长焦，XMAGE 智拍，红枫影像 2.0</t>
+          <t>华为Pura 90 Pro(16GB/1TB)</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -65385,7 +65377,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Ultra(12GB/512GB) 10倍光变天眼长焦 ，双2亿超大底镜头，100w超级闪充</t>
+          <t>OPPO Find X9 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -65460,7 +65452,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Ultra(16GB/512GB) 10倍光变天眼长焦 ，双2亿超大底镜头，100w超级闪充</t>
+          <t>OPPO Find X9 Ultra(16GB/512GB)</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -65535,7 +65527,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>OPPO Find X9 Ultra(16GB/1TB/卫星通信版) 10倍光变天眼长焦 ，双2亿超大底镜头，100w超级闪充</t>
+          <t>OPPO Find X9 Ultra(16GB/1TB/卫星通信版)</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -65610,7 +65602,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>OPPO Find X9s Pro(12GB/512GB) 2亿大底超清主摄，2亿长焦，80W超级闪充</t>
+          <t>OPPO Find X9s Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -65685,7 +65677,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>OPPO Find X9s Pro(16GB/512GB) 2亿大底超清主摄，2亿长焦，80W超级闪充</t>
+          <t>OPPO Find X9s Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -65760,7 +65752,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>vivo Y600 Pro（8GB/256GB） 天玑7300e，1.5K悦目护眼屏，10200mAh耐超低温蓝海电池</t>
+          <t>vivo Y600 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -65835,7 +65827,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>vivo Y6（8GB/128GB） 第二代骁龙4，1200nits真护眼屏，7200mAh长续航</t>
+          <t>vivo Y6（8GB/128GB）</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -65910,7 +65902,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>vivo Y60(6GB/128GB) 6500mAh耐用大电池，整机抗跌耐摔，全局无频闪护眼屏</t>
+          <t>vivo Y60(6GB/128GB)</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -65985,7 +65977,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>vivo Y60(6GB/256GB) 6500mAh耐用大电池，整机抗跌耐摔，全局无频闪护眼屏</t>
+          <t>vivo Y60(6GB/256GB)</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -66060,7 +66052,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>vivo Y60(8GB/256GB) 6500mAh耐用大电池，整机抗跌耐摔，全局无频闪护眼屏</t>
+          <t>vivo Y60(8GB/256GB)</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -66135,7 +66127,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>vivo Y600 Pro（8GB/256GB） 天玑7300e，1.5K悦目护眼屏，10200mAh耐超低温蓝海电池</t>
+          <t>vivo Y600 Pro（8GB/256GB）</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -66210,7 +66202,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>vivo Y600 Pro（8GB/512GB） 天玑7300e，1.5K悦目护眼屏，10200mAh耐超低温蓝海电池</t>
+          <t>vivo Y600 Pro（8GB/512GB）</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -66285,7 +66277,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>vivo Y600 Pro（12GB/256GB） 天玑7300e，1.5K悦目护眼屏，10200mAh耐超低温蓝海电池</t>
+          <t>vivo Y600 Pro（12GB/256GB）</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -66360,7 +66352,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>vivo Y600 Pro（12GB/512GB） 天玑7300e，1.5K悦目护眼屏，10200mAh耐超低温蓝海电池</t>
+          <t>vivo Y600 Pro（12GB/512GB）</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -66435,7 +66427,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>OPPO Reno16(12GB/256GB) 2亿像素，超清四摄，超流畅更AI ColorOS</t>
+          <t>OPPO Reno16(12GB/256GB)</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -66510,7 +66502,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>OPPO Reno16 Pro(12GB/256GB) 2亿超清云台主摄，实况随心贴，AI 一键闪记</t>
+          <t>OPPO Reno16 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -66585,7 +66577,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>荣耀畅玩70C(4GB/128GB) 5300mAh耐用电池，长辈简易模式，整机抗摔</t>
+          <t>荣耀畅玩70C(4GB/128GB)</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -66660,7 +66652,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>荣耀畅玩70C(4GB/64GB) 5300mAh耐用电池，长辈简易模式，整机抗摔</t>
+          <t>荣耀畅玩70C(4GB/64GB)</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -66735,7 +66727,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>荣耀Play11 Plus（8GB/256GB） 天玑6500 Elite，一体化金属中框，荣耀绿洲护眼屏</t>
+          <t>荣耀Play11 Plus（8GB/256GB）</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -66810,7 +66802,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>荣耀600 Pro(12GB/256GB) 2亿超清大底影像，三重星光幻彩设计，8600mAh青海湖大电池</t>
+          <t>荣耀600 Pro(12GB/256GB)</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -66885,7 +66877,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>荣耀600 Pro(12GB/512GB) 2亿超清大底影像，三重星光幻彩设计，8600mAh青海湖大电池</t>
+          <t>荣耀600 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -66960,7 +66952,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>荣耀600 Pro(16GB/512GB) 2亿超清大底影像，三重星光幻彩设计，8600mAh青海湖大电池</t>
+          <t>荣耀600 Pro(16GB/512GB)</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -67035,7 +67027,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>荣耀600 超级版(12GB/256GB) 4k闪光微单Live，8600mAh青海湖大电池，2亿超清大底影像</t>
+          <t>荣耀600 超级版(12GB/256GB)</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -67110,7 +67102,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>荣耀600 超级版(12GB/512GB) 4k闪光微单Live，8600mAh青海湖大电池，2亿超清大底影像</t>
+          <t>荣耀600 超级版(12GB/512GB)</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -67185,7 +67177,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>vivo Y600 Turbo(12GB/256GB) 第四代骁龙7s流畅芯，9000mAh蓝海电池，IP68+IP69防水认证</t>
+          <t>vivo Y600 Turbo(12GB/256GB)</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -67260,7 +67252,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>vivo Y600 Turbo(8GB/256GB) 第四代骁龙7s流畅芯，9000mAh蓝海电池，IP68+IP69防水认证</t>
+          <t>vivo Y600 Turbo(8GB/256GB)</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -67335,7 +67327,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>vivo Y600 Turbo(12GB/512GB) 第四代骁龙7s流畅芯，9000mAh蓝海电池，IP68+IP69防水认证</t>
+          <t>vivo Y600 Turbo(12GB/512GB)</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -67410,7 +67402,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>OPPO Reno16(16GB/256GB) 2亿像素，超清四摄，超流畅更AI ColorOS</t>
+          <t>OPPO Reno16(16GB/256GB)</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -67485,7 +67477,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>OPPO Reno16(12GB/512GB) 2亿像素，超清四摄，超流畅更AI ColorOS</t>
+          <t>OPPO Reno16(12GB/512GB)</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -67560,7 +67552,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>OPPO Reno16(16GB/512GB) 2亿像素，超清四摄，超流畅更AI ColorOS</t>
+          <t>OPPO Reno16(16GB/512GB)</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -67635,7 +67627,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>OPPO (16GB/1TB) 2亿像素，超清四摄，超流畅更AI ColorOS</t>
+          <t>OPPO (16GB/1TB)</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -67710,7 +67702,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>OPPO Reno16 Pro(12GB/512GB) 2亿超清云台主摄，实况随心贴，AI 一键闪记</t>
+          <t>OPPO Reno16 Pro(12GB/512GB)</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -67785,7 +67777,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>荣耀600 元气版(8GB/256GB) 5000万索尼超清主摄，8000nits绿洲护眼屏，7000mAh轻薄长续航</t>
+          <t>荣耀600 元气版(8GB/256GB)</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -67860,7 +67852,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>荣耀600 元气版(12GB/256GB) 5000万索尼超清主摄，8000nits绿洲护眼屏，7000mAh轻薄长续航</t>
+          <t>荣耀600 元气版(12GB/256GB)</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -67935,7 +67927,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>荣耀600 元气版(12GB/512GB) 5000万索尼超清主摄，8000nits绿洲护眼屏，7000mAh轻薄长续航</t>
+          <t>荣耀600 元气版(12GB/512GB)</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -68010,7 +68002,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>vivo S60（12GB/256GB） 4K原生感Live，4K星光Live，云台级防抖主摄</t>
+          <t>vivo S60（12GB/256GB）</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -68085,7 +68077,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>荣耀WIN Turbo(12GB/256GB) 10000mAh青海湖电池， 荣耀鸿燕信号王，天玑8500竞速版芯片</t>
+          <t>荣耀WIN Turbo(12GB/256GB)</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -68156,7 +68148,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>华为nova 16（256GB） 后置红枫影像，麒麟9010S 芯片，7000mAh 巨鲸电池</t>
+          <t>华为nova 16（256GB）</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -68225,7 +68217,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>华为nova 16z（12GB/256GB） 后置红枫影像，100 W华为超级快充，鸿蒙AI趣玩</t>
+          <t>华为nova 16z（12GB/256GB）</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -68296,7 +68288,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>华为nova 16 Pro（256GB） 2亿红枫影像，麒麟9010S 芯片，7000mAh 巨鲸电池</t>
+          <t>华为nova 16 Pro（256GB）</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -68365,7 +68357,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>华为nova 16 Ultra（12GB/1TB） 2亿红枫影像，麒麟9010S芯片，7000mAh巨鲸电池</t>
+          <t>华为nova 16 Ultra（12GB/1TB）</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -68436,7 +68428,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>荣耀WIN Turbo(12GB/512GB) 10000mAh青海湖电池， 荣耀鸿燕信号王，天玑8500竞速版芯片</t>
+          <t>荣耀WIN Turbo(12GB/512GB)</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -68507,7 +68499,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>荣耀WIN Turbo(16GB/512GB) 10000mAh青海湖电池， 荣耀鸿燕信号王，天玑8500竞速版芯片</t>
+          <t>荣耀WIN Turbo(16GB/512GB)</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -68578,7 +68570,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>vivo S60（12GB/512GB） 4K原生感Live，4K星光Live，云台级防抖主摄</t>
+          <t>vivo S60（12GB/512GB）</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -68653,7 +68645,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>vivo S60（16GB/512GB） 4K原生感Live，4K星光Live，云台级防抖主摄</t>
+          <t>vivo S60（16GB/512GB）</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -68728,7 +68720,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>vivo S50t(12GB/512GB) 长焦Live神器，高通第三代骁龙 8s，湿手秒开超声波指纹 2.0</t>
+          <t>vivo S50t(12GB/512GB)</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -68803,7 +68795,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>vivo S50t(16GB/512GB) 长焦Live神器，高通第三代骁龙 8s，湿手秒开超声波指纹 2.0</t>
+          <t>vivo S50t(16GB/512GB)</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -68878,7 +68870,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>vivo S60元气版(8GB/256GB) 4K原生感Live，湿手秒开超声波指纹 2.0，7200mAh超薄蓝海电池</t>
+          <t>vivo S60元气版(8GB/256GB)</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -68953,7 +68945,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>vivo S60元气版(12GB/256GB) 4K原生感Live，湿手秒开超声波指纹 2.0，7200mAh超薄蓝海电池</t>
+          <t>vivo S60元气版(12GB/256GB)</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -69028,7 +69020,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>vivo S60元气版(12GB/512GB) 4K原生感Live，湿手秒开超声波指纹 2.0，7200mAh超薄蓝海电池</t>
+          <t>vivo S60元气版(12GB/512GB)</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -69103,7 +69095,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>华为nova 16 Ultra（12GB/256GB） 2亿红枫影像，麒麟9010S芯片，7000mAh巨鲸电池</t>
+          <t>华为nova 16 Ultra（12GB/256GB）</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -69174,7 +69166,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>华为nova 16 Ultra（12GB/512GB） 2亿红枫影像，麒麟9010S芯片，7000mAh巨鲸电池</t>
+          <t>华为nova 16 Ultra（12GB/512GB）</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -69245,7 +69237,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>华为nova 16（512GB） 后置红枫影像，麒麟9010S 芯片，7000mAh 巨鲸电池</t>
+          <t>华为nova 16（512GB）</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -69314,7 +69306,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>华为nova 16z（12GB/512GB） 后置红枫影像，100 W华为超级快充，鸿蒙AI趣玩</t>
+          <t>华为nova 16z（12GB/512GB）</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -69385,7 +69377,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>华为nova 16 Pro（512GB） 2亿红枫影像，麒麟9010S 芯片，7000mAh 巨鲸电池</t>
+          <t>华为nova 16 Pro（512GB）</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -69454,7 +69446,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>华为nova 16 Pro（1TB） 2亿红枫影像，麒麟9010S 芯片，7000mAh 巨鲸电池</t>
+          <t>华为nova 16 Pro（1TB） 2亿红枫影像，</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -69523,7 +69515,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>vivo X Fold6(12GB/256GB) 原子工作台，蔡司2亿超级主摄，等效7000mAh蓝海电池</t>
+          <t>vivo X Fold6(12GB/256GB)</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -69598,7 +69590,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>荣耀X80 Pro Max(8GB/128GB) 11000mAh大电池，金标抗摔，深度防水</t>
+          <t>荣耀X80 Pro Max(8GB/128GB)</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -69673,7 +69665,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>荣耀X80 Pro Max(8GB/256GB) 11000mAh大电池，金标抗摔，深度防水</t>
+          <t>荣耀X80 Pro Max(8GB/256GB)</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -69748,7 +69740,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>荣耀X80 Pro Max(8GB/512GB) 11000mAh大电池，金标抗摔，深度防水</t>
+          <t>荣耀X80 Pro Max(8GB/512GB)</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -69823,7 +69815,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>荣耀X80 Pro Max(12GB/512GB) 11000mAh大电池，金标抗摔，深度防水</t>
+          <t>荣耀X80 Pro Max(12GB/512GB)</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -69898,7 +69890,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>vivo X Fold6(12GB/512GB) 原子工作台，蔡司2亿超级主摄，等效7000mAh蓝海电池</t>
+          <t>vivo X Fold6(12GB/512GB)</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -69973,7 +69965,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>vivo X Fold6(16GB/512GB) 原子工作台，蔡司2亿超级主摄，等效7000mAh蓝海电池</t>
+          <t>vivo X Fold6(16GB/512GB)</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -70048,7 +70040,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>vivo X Fold6(16GB/1TB) 原子工作台，蔡司2亿超级主摄，等效7000mAh蓝海电池</t>
+          <t>vivo X Fold6(16GB/1TB)</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -70123,7 +70115,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>vivo X Fold6(16GB/1TB/折叠专业影像套装) 原子工作台，蔡司2亿超级主摄，等效7000mAh蓝海电池</t>
+          <t>vivo X Fold6(16GB/1TB/折叠专业影像套装)</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -70198,7 +70190,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>OPPO A7 Pro Max(8GB/128GB) 万级大电池，前后5000万像素，防水抗摔</t>
+          <t>OPPO A7 Pro Max(8GB/128GB)</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -70273,7 +70265,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold8（12GB/256GB） 第五代骁龙8至尊版，4:3宽幅内屏，4.5mm口袋便携</t>
+          <t>三星Galaxy Z Fold8（12GB/256GB）</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -70344,7 +70336,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold8（12GB/512GB） 第五代骁龙8至尊版，4:3宽幅内屏，4.5mm口袋便携</t>
+          <t>三星Galaxy Z Fold8（12GB/512GB）</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -70415,7 +70407,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip8(12GB/256GB) 智能外屏，超轻薄掌心折叠，5000万像素</t>
+          <t>三星Galaxy Z Flip8(12GB/256GB)</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -70482,7 +70474,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Flip8(12GB/512GB) 智能外屏，超轻薄掌心折叠，5000万像素</t>
+          <t>三星Galaxy Z Flip8(12GB/512GB)</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -70549,7 +70541,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold8 Ultra(12GB/256GB) 215g 4.1mm超轻薄，旗舰性能两亿影像，高亮超清大屏</t>
+          <t>三星Galaxy Z Fold8 Ultra(12GB/256GB)</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -70612,7 +70604,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold8 Ultra(12GB/512GB) 215g 4.1mm超轻薄，旗舰性能两亿影像，高亮超清大屏</t>
+          <t>三星Galaxy Z Fold8 Ultra(12GB/512GB)</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -70675,7 +70667,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>三星Galaxy Z Fold8 Ultra(16GB/1TB) 215g 4.1mm超轻薄，旗舰性能两亿影像，高亮超清大屏</t>
+          <t>三星Galaxy Z Fold8 Ultra(16GB/1TB)</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -70738,7 +70730,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>OPPO K15（12GB/256GB） 天玑7360 SUPER处理器，前后 5000万像素超清三摄，新一代疾风散热引擎</t>
+          <t>OPPO K15（12GB/256GB）</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -70813,7 +70805,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>OPPO A7 Pro Max(12GB/256GB) 万级大电池，前后5000万像素，防水抗摔</t>
+          <t>OPPO A7 Pro Max(12GB/256GB)</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -70888,7 +70880,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>OPPO A7 Pro Max(12GB/512GB) 万级大电池，前后5000万像素，防水抗摔</t>
+          <t>OPPO A7 Pro Max(12GB/512GB)</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -70963,7 +70955,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>华为nova 16 SE（128GB） 麒麟8020芯片，5000 万 RYYB红枫影像，8500mAh巨鲸大电池</t>
+          <t>华为nova 16 SE（128GB）</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -71036,7 +71028,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>OPPO A7 Pro Max(8GB/256GB) 万级大电池，前后5000万像素，防水抗摔</t>
+          <t>OPPO A7 Pro Max(8GB/256GB)</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -71111,7 +71103,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>华为nova 16 SE（256GB） 麒麟8020芯片，5000 万 RYYB红枫影像，8500mAh巨鲸大电池</t>
+          <t>华为nova 16 SE（256GB）</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -71184,7 +71176,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>华为nova 16 SE（512GB） 麒麟8020芯片，5000 万 RYYB红枫影像，8500mAh巨鲸大电池</t>
+          <t>华为nova 16 SE（512GB）</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -71255,7 +71247,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>荣耀Robot Phone（16GB/1TB） 钛合金灵巧云台，ARRI电影，YOYO机器人模式</t>
+          <t>荣耀Robot Phone（16GB/1TB）</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -71330,7 +71322,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>华为Pura X View(12GB/256GB) 沉浸阔直板，超轻薄长续航，HarmonyOS 7</t>
+          <t>华为Pura X View(12GB/256GB)</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -71401,7 +71393,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>华为Pura X View(12GB/512GB) 沉浸阔直板，超轻薄长续航，HarmonyOS 7</t>
+          <t>华为Pura X View(12GB/512GB)</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -71472,7 +71464,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>华为Pura X View(12GB/1TB) 沉浸阔直板，超轻薄长续航，HarmonyOS 7</t>
+          <t>华为Pura X View(12GB/1TB)</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -71543,7 +71535,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>华为Mate XT 2 非凡大师（16GB/512GB） 全新展翼三折叠，麒麟9050 Pro，第三代红枫影像</t>
+          <t>华为Mate XT 2 非凡大师（16GB/512GB）</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -71600,7 +71592,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>华为Mate XT 2 非凡大师（16GB/1TB） 全新展翼三折叠，麒麟9050 Pro，第三代红枫影像</t>
+          <t>华为Mate XT 2 非凡大师（16GB/1TB）</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -71657,7 +71649,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>华为Mate XT 2 非凡大师（16GB/1TB/灵盾防窥屏） 全新展翼三折叠，麒麟9050 Pro，第三代红枫影像</t>
+          <t>华为Mate XT 2 非凡大师（16GB/1TB/灵盾防窥屏）</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -71714,7 +71706,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>华为Mate XT 2 非凡大师（16GB/2TB/手写笔套装/灵盾防窥屏） 全新展翼三折叠，麒麟9050 Pro，第三代红枫影像</t>
+          <t>华为Mate XT 2 非凡大师（16GB/2TB/手写笔套装/灵盾防窥屏）</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -71771,7 +71763,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>华为Mate XT 2 非凡大师（16GB/256GB） 全新展翼三折叠，麒麟9050 Pro，第三代红枫影像</t>
+          <t>华为Mate XT 2 非凡大师（16GB/256GB）</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -71828,7 +71820,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro（256GB） iPhone 实力巅峰，性能与摄像头表现满级，电池续航大进化</t>
+          <t>苹果iPhone 18 Pro（256GB）</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -71885,7 +71877,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>苹果iPhone Duo（256GB） 超视网膜XDR可折叠屏，A20 Pro芯片，融合式双摄</t>
+          <t>苹果iPhone Duo（256GB）</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -71938,7 +71930,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro Max（256GB） 超视网膜XDR显示屏，铝金属一体成型机身，A20 Pro芯片</t>
+          <t>苹果iPhone 18 Pro Max（256GB）</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -71995,7 +71987,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro（512GB） iPhone 实力巅峰，性能与摄像头表现满级，电池续航大进化</t>
+          <t>苹果iPhone 18 Pro（512GB）</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -72142,7 +72134,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>苹果iPhone Duo（512GB） 超视网膜XDR可折叠屏，A20 Pro芯片，融合式双摄</t>
+          <t>苹果iPhone Duo（512GB）</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -72195,7 +72187,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>苹果iPhone Duo（1TB） 超视网膜XDR可折叠屏，A20 Pro芯片，融合式双摄</t>
+          <t>苹果iPhone Duo（1TB）</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -72248,7 +72240,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>苹果iPhone Duo（2TB） 超视网膜XDR可折叠屏，A20 Pro芯片，融合式双摄</t>
+          <t>苹果iPhone Duo（2TB）</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -72301,7 +72293,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro Max（512GB） 超视网膜XDR显示屏，铝金属一体成型机身，A20 Pro芯片</t>
+          <t>苹果iPhone 18 Pro Max（512GB）</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -72350,7 +72342,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro Max（1TB） 超视网膜XDR显示屏，铝金属一体成型机身，A20 Pro芯片</t>
+          <t>苹果iPhone 18 Pro Max（1TB）</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -72399,7 +72391,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro Max（2TB） 超视网膜XDR显示屏，铝金属一体成型机身，A20 Pro芯片</t>
+          <t>苹果iPhone 18 Pro Max（2TB）</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -72448,7 +72440,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>vivo X500 Pro Max(12GB/256GB) 蔡司2亿APO超级长焦，蓝晶×天玑9600 Pro，蔡司超动态主摄</t>
+          <t>vivo X500 Pro Max(12GB/256GB)</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">

--- a/code/data/phones_clean.xlsx
+++ b/code/data/phones_clean.xlsx
@@ -602,7 +602,9 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -724,7 +726,9 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>16</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -785,7 +789,9 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -846,7 +852,9 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>32</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1096,7 +1104,9 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>16</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1157,7 +1167,9 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>32</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1728,7 +1740,9 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>16</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -2029,7 +2043,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（电信版） siri语音，面部检测，视网膜Retina技术</t>
+          <t>苹果iPhone 5（电信版）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2138,7 +2152,9 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>8</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
@@ -2167,7 +2183,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（白色） 目前白色和黑色价格基本没有差距，支持Siri语音控制功能，3.5英寸屏幕单手操作较合适</t>
+          <t>苹果iPhone 4S（白色）</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2178,7 +2194,9 @@
       <c r="D28" t="n">
         <v>3050</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>1420</v>
@@ -2248,7 +2266,9 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>32</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
@@ -2301,7 +2321,9 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>64</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
@@ -2393,7 +2415,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（联通版） 联通合约机，合约期机卡不分离，也可购买裸机，电池不能拆卸，不能自由的安装应用程序</t>
+          <t>苹果iPhone 4S（联通版）</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2462,7 +2484,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>苹果iPhone 4S（电信版） Siri语音，IOS7系统，1080P视频录制</t>
+          <t>苹果iPhone 4S（电信版）</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2517,7 +2539,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（联通版） 联通合约机，也可购买裸机，分为16/32/64GB不同容量版本，价格较贵，充电接口不通用</t>
+          <t>苹果iPhone 5（联通版）</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2659,7 +2681,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>苹果iPhone 5（彩色版） 市场上没有行货，只有欧版/港版，价格和普通版相近，只是把普通版换了外壳，有粉色、蓝色、金色</t>
+          <t>苹果iPhone 5（彩色版）</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -24993,7 +25015,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro （1TB） 超瓷晶面板，视网膜XDR显示屏，Pro级摄像头系统</t>
+          <t>苹果iPhone 14 Pro （1TB）</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -25218,7 +25240,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>苹果iPhone 14 Pro Max（1TB） A16处理器，4800万像素，120Hz刷新率</t>
+          <t>苹果iPhone 14 Pro Max（1TB）</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -31714,7 +31736,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro（1TB） 钛金属，A17 Pro芯片，4800万像素主摄</t>
+          <t>苹果iPhone 15 Pro（1TB）</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -31860,7 +31882,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>苹果iPhone 15 Pro Max（1TB） 钛金属，6.7英寸，A17 Pro芯片</t>
+          <t>苹果iPhone 15 Pro Max（1TB）</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -32592,7 +32614,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>vivo Y78t 8GB+256GB 第一代</t>
+          <t>vivo Y78t 8GB+256GB</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -32667,7 +32689,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>OPPO A2 5G( 12GB/256GB) 大内存，33W超级闪充，金刚石抗摔结构</t>
+          <t>OPPO A2 5G( 12GB/256GB)</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -33620,7 +33642,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>华为nova 12 256GB 鸿蒙智慧通信，100W智能快充Turbo，前置6000万</t>
+          <t>华为nova 12 256GB</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -34717,7 +34739,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>华为nova 12 Pro 256GB 前置6000万人像追焦双摄，鸿蒙智慧通信，</t>
+          <t>华为nova 12 Pro 256GB</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -34782,7 +34804,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>华为nova 12 Pro 512GB 前置6000万人像追焦双摄，鸿蒙智慧通信，</t>
+          <t>华为nova 12 Pro 512GB</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -34847,7 +34869,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>华为nova 12 512GB 鸿蒙智慧通信，100W智能快充Turbo，前置6000万</t>
+          <t>华为nova 12 512GB</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -34912,7 +34934,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>华为nova 12 活力版 256GB 鸿蒙智能，6.88mm</t>
+          <t>华为nova 12 活力版 256GB</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -34977,7 +34999,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>华为nova 12 活力版 512GB 鸿蒙智能，6.88mm</t>
+          <t>华为nova 12 活力版 512GB</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -35192,7 +35214,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>华为畅享 70 Pro 256GB 1亿像素超清影像，40W超级快充，5000mAh</t>
+          <t>华为畅享 70 Pro 256GB</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -35265,7 +35287,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>华为畅享 70 Pro 128GB 1亿像素超清影像，40W超级快充，5000mAh</t>
+          <t>华为畅享 70 Pro 128GB</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -35338,7 +35360,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>华为畅享 70  128GB 6000mAh超长续航，畅享X键 一键畅享，5000万像素高清摄影</t>
+          <t>华为畅享 70  128GB</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -35403,7 +35425,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>华为畅享 70  256GB 6000mAh超长续航，畅享X键 一键畅享，5000万像素高清摄影</t>
+          <t>华为畅享 70  256GB</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -39114,7 +39136,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Samsung（三星）Galaxy A55 8GB+256GB 光学防抖，IP67，AI人像拍摄</t>
+          <t>Samsung（三星）Galaxy A55 8GB+256GB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -39185,7 +39207,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Samsung（三星）Galaxy A55 12GB+256GB 光学防抖，IP67，AI人像拍摄</t>
+          <t>Samsung（三星）Galaxy A55 12GB+256GB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -39256,7 +39278,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>vivo S19 Pro（8GB/256GB) 轻薄曲屏，流畅运行，超清人像</t>
+          <t>vivo S19 Pro（8GB/256GB)</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -41184,7 +41206,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>华为novaFlip 6.88mm轻薄可靠，鸿蒙AI趣玩，后置5000万悬停自拍</t>
+          <t>华为novaFlip</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -50781,7 +50803,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>华为nova 14 Ultra （1TB） 全焦段红枫质感人像，天通北斗双卫星通信，鸿蒙AI</t>
+          <t>华为nova 14 Ultra （1TB）</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -53424,7 +53446,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Apple（苹果）iPhone Air 256GB 1800万像素Center Stage前摄，全天电池续航，A19 Pro芯片</t>
+          <t>Apple（苹果）iPhone Air 256GB</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -54002,7 +54024,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>苹果iPhone 17 Pro（1TB） 视网膜XDR显示屏，铝金属一体成型机身，A19 Pro 芯片</t>
+          <t>苹果iPhone 17 Pro（1TB）</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -54270,7 +54292,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Apple（苹果）iPhone Air 512GB 1800万像素Center Stage前摄，全天电池续航，A19 Pro芯片</t>
+          <t>Apple（苹果）iPhone Air 512GB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -54341,7 +54363,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Apple（苹果）iPhone Air 1TB 1800万像素Center Stage前摄，全天电池续航，A19 Pro芯片</t>
+          <t>Apple（苹果）iPhone Air 1TB</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -56642,7 +56664,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>HUAWEI nova Flip S 256GB SGS 120万次弯折耐久认证，鸿蒙AI趣玩，后置5000万悬停自拍</t>
+          <t>HUAWEI nova Flip S 256GB</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -59812,7 +59834,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>vivo(S50 12GB/512GB) 主摄级长焦Live，高通第三代</t>
+          <t>vivo(S50 12GB/512GB)</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -62566,7 +62588,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 128GB 8500mAh巨鲸</t>
+          <t>华为畅享90 Pro Max 128GB</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -62919,7 +62941,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 256GB 8500mAh巨鲸</t>
+          <t>华为畅享90 Pro Max 256GB</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -62988,7 +63010,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>华为畅享90 Pro Max 512GB 8500mAh巨鲸</t>
+          <t>华为畅享90 Pro Max 512GB</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -64089,7 +64111,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>华为Pura 90 超轻薄长续航，AI 智拍，红枫影像</t>
+          <t>华为Pura 90</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -65237,7 +65259,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>华为Pura 90 12GB+512GB 超轻薄长续航，AI 智拍，红枫影像</t>
+          <t>华为Pura 90 12GB+512GB</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -65308,7 +65330,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>华为Pura 90 16GB+512GB 超轻薄长续航，AI 智拍，红枫影像</t>
+          <t>华为Pura 90 16GB+512GB</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -69446,7 +69468,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>华为nova 16 Pro（1TB） 2亿红枫影像，</t>
+          <t>华为nova 16 Pro（1TB）</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -71195,7 +71217,9 @@
           <t>2756x1272px</t>
         </is>
       </c>
-      <c r="G979" t="inlineStr"/>
+      <c r="G979" t="n">
+        <v>8500</v>
+      </c>
       <c r="H979" t="inlineStr">
         <is>
           <t>八核</t>
@@ -72036,7 +72060,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro（ 1TB） iPhone 实力巅峰，性能与摄像头表现满级，电池续航大进化</t>
+          <t>苹果iPhone 18 Pro（ 1TB）</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -72085,7 +72109,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>苹果iPhone 18 Pro（2TB） iPhone 实力巅峰，性能与摄像头表现满级，电池续航大进化</t>
+          <t>苹果iPhone 18 Pro（2TB）</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">

--- a/code/data/phones_clean.xlsx
+++ b/code/data/phones_clean.xlsx
@@ -528,7 +528,9 @@
           <t>320×480px</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>2775</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
@@ -540,8 +542,12 @@
           <t>ARM11</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>128</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
@@ -589,7 +595,9 @@
           <t>320×480px</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>2775</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
@@ -601,7 +609,9 @@
           <t>ARM11</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
       <c r="L3" t="n">
         <v>16</v>
       </c>
@@ -652,7 +662,9 @@
           <t>320×480px</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>2775</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
@@ -664,8 +676,12 @@
           <t>ARM11</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>128</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -713,7 +729,9 @@
           <t>320×480px</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>2775</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
@@ -725,7 +743,9 @@
           <t>ARM11</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
       <c r="L5" t="n">
         <v>16</v>
       </c>
@@ -776,7 +796,9 @@
           <t>480x320px</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>2775</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
@@ -788,7 +810,9 @@
           <t>ARM Cortex-A8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
       <c r="L6" t="n">
         <v>8</v>
       </c>
@@ -839,7 +863,9 @@
           <t>480x320px</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>2775</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
@@ -851,7 +877,9 @@
           <t>ARM Cortex-A8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
       <c r="L7" t="n">
         <v>32</v>
       </c>
@@ -902,7 +930,9 @@
           <t>480x320px</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>2775</v>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
@@ -914,7 +944,9 @@
           <t>ARM Cortex-A8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
       <c r="L8" t="n">
         <v>16</v>
       </c>
@@ -965,7 +997,9 @@
           <t>320×480px</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>2775</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
@@ -977,7 +1011,9 @@
           <t>ARM11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
       <c r="L9" t="n">
         <v>8</v>
       </c>
@@ -1028,7 +1064,9 @@
           <t>480x320px</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>2775</v>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1078,9 @@
           <t>ARM Cortex-A8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
       <c r="L10" t="n">
         <v>32</v>
       </c>
@@ -1091,7 +1131,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>2775</v>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
@@ -1103,7 +1145,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
       <c r="L11" t="n">
         <v>16</v>
       </c>
@@ -1154,7 +1198,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>2775</v>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
@@ -1166,7 +1212,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
       <c r="L12" t="n">
         <v>32</v>
       </c>
@@ -1217,7 +1265,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>2775</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -1229,8 +1279,12 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>128</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1278,7 +1332,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>2775</v>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
@@ -1290,8 +1346,12 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>128</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1339,7 +1399,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>2775</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
@@ -1351,8 +1413,12 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>128</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
@@ -1400,7 +1466,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>2775</v>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
@@ -1412,7 +1480,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
       <c r="L16" t="n">
         <v>16</v>
       </c>
@@ -1534,7 +1604,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>2775</v>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -1546,7 +1618,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
       <c r="L18" t="n">
         <v>32</v>
       </c>
@@ -1597,7 +1671,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2775</v>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1609,7 +1685,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
       <c r="L19" t="n">
         <v>32</v>
       </c>
@@ -1723,7 +1801,9 @@
       <c r="D21" t="n">
         <v>3150</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>1420</v>
@@ -1739,7 +1819,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
       <c r="L21" t="n">
         <v>16</v>
       </c>
@@ -1928,7 +2010,9 @@
           <t>960x640px</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>2775</v>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -1940,7 +2024,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
       <c r="L24" t="n">
         <v>32</v>
       </c>
@@ -2151,7 +2237,9 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
       <c r="L27" t="n">
         <v>8</v>
       </c>
@@ -2212,8 +2300,12 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>128</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
@@ -2249,7 +2341,9 @@
       <c r="D29" t="n">
         <v>4600</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>1420</v>
@@ -2265,7 +2359,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
       <c r="L29" t="n">
         <v>32</v>
       </c>
@@ -2304,7 +2400,9 @@
       <c r="D30" t="n">
         <v>4900</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>1420</v>
@@ -2320,7 +2418,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
       <c r="L30" t="n">
         <v>64</v>
       </c>
@@ -2385,8 +2485,12 @@
           <t>苹果 A4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>128</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
@@ -2452,7 +2556,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
       <c r="L32" t="n">
         <v>8</v>
       </c>
@@ -2495,7 +2601,9 @@
       <c r="D33" t="n">
         <v>2399</v>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>1420</v>
@@ -2511,7 +2619,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
       <c r="L33" t="n">
         <v>8</v>
       </c>
@@ -3073,7 +3183,9 @@
           <t>苹果 A5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>4</v>
+      </c>
       <c r="L41" t="n">
         <v>8</v>
       </c>
@@ -3258,7 +3370,9 @@
       <c r="D44" t="n">
         <v>2799</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>1510</v>
@@ -3603,7 +3717,9 @@
       <c r="D49" t="n">
         <v>2070</v>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>1810</v>
@@ -3660,7 +3776,9 @@
       <c r="D50" t="n">
         <v>2300</v>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>2915</v>
@@ -3934,7 +4052,9 @@
       <c r="D54" t="n">
         <v>2320</v>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>1715</v>
@@ -3991,7 +4111,9 @@
       <c r="D55" t="n">
         <v>2860</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>2750</v>
@@ -4265,7 +4387,9 @@
       <c r="D59" t="n">
         <v>1899</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>1642</v>
@@ -4322,7 +4446,9 @@
       <c r="D60" t="n">
         <v>1998</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>1960</v>
@@ -4379,7 +4505,9 @@
       <c r="D61" t="n">
         <v>3199</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>2910</v>
@@ -4941,7 +5069,9 @@
       <c r="D69" t="n">
         <v>3899</v>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>1821</v>
@@ -4998,7 +5128,9 @@
       <c r="D70" t="n">
         <v>3288</v>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>2675</v>
@@ -5055,7 +5187,9 @@
       <c r="D71" t="n">
         <v>5999</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>2716</v>
@@ -5259,7 +5393,7 @@
         <v>4499</v>
       </c>
       <c r="E74" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5334,7 +5468,9 @@
       <c r="D75" t="n">
         <v>6999</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>2658</v>
@@ -5391,7 +5527,9 @@
       <c r="D76" t="n">
         <v>6800</v>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>2658</v>
@@ -5448,7 +5586,9 @@
       <c r="D77" t="n">
         <v>5520</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>3174</v>
@@ -5505,7 +5645,9 @@
       <c r="D78" t="n">
         <v>8188</v>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>3174</v>
@@ -5562,7 +5704,9 @@
       <c r="D79" t="n">
         <v>3599</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>2942</v>
@@ -5620,7 +5764,7 @@
         <v>6399</v>
       </c>
       <c r="E80" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6063,7 +6207,7 @@
         <v>1798</v>
       </c>
       <c r="E86" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6284,7 +6428,7 @@
         <v>999</v>
       </c>
       <c r="E89" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -6359,7 +6503,7 @@
         <v>1399</v>
       </c>
       <c r="E90" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7010,7 +7154,7 @@
         <v>12999</v>
       </c>
       <c r="E99" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7085,7 +7229,9 @@
       <c r="D100" t="n">
         <v>3999</v>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>4200</v>
@@ -7147,7 +7293,7 @@
         <v>5899</v>
       </c>
       <c r="E101" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -7223,7 +7369,7 @@
         <v>1599</v>
       </c>
       <c r="E102" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -7519,7 +7665,7 @@
         <v>1398</v>
       </c>
       <c r="E106" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8119,7 +8265,7 @@
         <v>1849</v>
       </c>
       <c r="E114" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -8344,7 +8490,7 @@
         <v>2999</v>
       </c>
       <c r="E117" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -8419,7 +8565,7 @@
         <v>5988</v>
       </c>
       <c r="E118" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -8494,7 +8640,7 @@
         <v>8888</v>
       </c>
       <c r="E119" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -8569,7 +8715,7 @@
         <v>6488</v>
       </c>
       <c r="E120" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -8719,7 +8865,7 @@
         <v>3388</v>
       </c>
       <c r="E122" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -8794,7 +8940,7 @@
         <v>3999</v>
       </c>
       <c r="E123" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -8869,7 +9015,7 @@
         <v>4999</v>
       </c>
       <c r="E124" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9094,7 +9240,7 @@
         <v>3699</v>
       </c>
       <c r="E127" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9319,7 +9465,7 @@
         <v>3399</v>
       </c>
       <c r="E130" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -9394,7 +9540,7 @@
         <v>1699</v>
       </c>
       <c r="E131" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9544,7 +9690,7 @@
         <v>3298</v>
       </c>
       <c r="E133" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -9694,7 +9840,7 @@
         <v>2399</v>
       </c>
       <c r="E135" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9769,7 +9915,7 @@
         <v>2398</v>
       </c>
       <c r="E136" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -9844,7 +9990,7 @@
         <v>3088</v>
       </c>
       <c r="E137" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10216,7 +10362,7 @@
         <v>1498</v>
       </c>
       <c r="E142" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -10733,7 +10879,7 @@
         <v>1399</v>
       </c>
       <c r="E149" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -10808,7 +10954,7 @@
         <v>2798</v>
       </c>
       <c r="E150" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -10958,7 +11104,7 @@
         <v>2299</v>
       </c>
       <c r="E152" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11183,7 +11329,7 @@
         <v>2699</v>
       </c>
       <c r="E155" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -11258,7 +11404,7 @@
         <v>3399</v>
       </c>
       <c r="E156" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -11333,7 +11479,7 @@
         <v>6999</v>
       </c>
       <c r="E157" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -11408,7 +11554,7 @@
         <v>8999</v>
       </c>
       <c r="E158" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -11483,7 +11629,7 @@
         <v>12999</v>
       </c>
       <c r="E159" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -11558,7 +11704,7 @@
         <v>5299</v>
       </c>
       <c r="E160" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -11783,7 +11929,7 @@
         <v>3199</v>
       </c>
       <c r="E163" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -11858,7 +12004,7 @@
         <v>3299</v>
       </c>
       <c r="E164" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -11933,7 +12079,7 @@
         <v>3999</v>
       </c>
       <c r="E165" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12083,7 +12229,7 @@
         <v>2199</v>
       </c>
       <c r="E167" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12396,7 +12542,9 @@
           <t>苹果 A15</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>4</v>
+      </c>
       <c r="L171" t="n">
         <v>128</v>
       </c>
@@ -12440,7 +12588,7 @@
         <v>2999</v>
       </c>
       <c r="E172" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -12515,7 +12663,7 @@
         <v>1998</v>
       </c>
       <c r="E173" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -12665,7 +12813,7 @@
         <v>4198</v>
       </c>
       <c r="E175" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13391,7 +13539,7 @@
         <v>1198</v>
       </c>
       <c r="E185" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -13541,7 +13689,7 @@
         <v>11999</v>
       </c>
       <c r="E187" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -13616,7 +13764,7 @@
         <v>3599</v>
       </c>
       <c r="E188" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -13691,7 +13839,7 @@
         <v>6799</v>
       </c>
       <c r="E189" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -13842,7 +13990,7 @@
         <v>4199</v>
       </c>
       <c r="E191" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -13917,7 +14065,7 @@
         <v>2398</v>
       </c>
       <c r="E192" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14364,7 +14512,7 @@
         <v>12999</v>
       </c>
       <c r="E198" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -14664,7 +14812,7 @@
         <v>1798</v>
       </c>
       <c r="E202" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -14739,7 +14887,7 @@
         <v>1299</v>
       </c>
       <c r="E203" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -14889,7 +15037,7 @@
         <v>1698</v>
       </c>
       <c r="E205" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -14964,7 +15112,7 @@
         <v>4988</v>
       </c>
       <c r="E206" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15039,7 +15187,7 @@
         <v>6988</v>
       </c>
       <c r="E207" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15114,7 +15262,7 @@
         <v>3299</v>
       </c>
       <c r="E208" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15189,7 +15337,7 @@
         <v>3899</v>
       </c>
       <c r="E209" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -15339,7 +15487,7 @@
         <v>2598</v>
       </c>
       <c r="E211" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -15635,7 +15783,7 @@
         <v>2599</v>
       </c>
       <c r="E215" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -15860,7 +16008,7 @@
         <v>1799</v>
       </c>
       <c r="E218" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -15935,7 +16083,7 @@
         <v>3299</v>
       </c>
       <c r="E219" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16010,7 +16158,7 @@
         <v>2399</v>
       </c>
       <c r="E220" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16085,7 +16233,7 @@
         <v>1699</v>
       </c>
       <c r="E221" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16160,7 +16308,7 @@
         <v>2999</v>
       </c>
       <c r="E222" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16235,7 +16383,7 @@
         <v>2999</v>
       </c>
       <c r="E223" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -16310,7 +16458,7 @@
         <v>3399</v>
       </c>
       <c r="E224" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -16385,7 +16533,7 @@
         <v>2699</v>
       </c>
       <c r="E225" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -16532,7 +16680,7 @@
         <v>2999</v>
       </c>
       <c r="E227" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -16607,7 +16755,7 @@
         <v>1099</v>
       </c>
       <c r="E228" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -16682,7 +16830,7 @@
         <v>4299</v>
       </c>
       <c r="E229" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -16757,7 +16905,7 @@
         <v>2099</v>
       </c>
       <c r="E230" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -16832,7 +16980,7 @@
         <v>3499</v>
       </c>
       <c r="E231" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -16903,7 +17051,7 @@
         <v>3699</v>
       </c>
       <c r="E232" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17053,7 +17201,7 @@
         <v>1599</v>
       </c>
       <c r="E234" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17128,7 +17276,7 @@
         <v>5999</v>
       </c>
       <c r="E235" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17203,7 +17351,7 @@
         <v>1199</v>
       </c>
       <c r="E236" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -17278,7 +17426,7 @@
         <v>2399</v>
       </c>
       <c r="E237" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -17353,7 +17501,7 @@
         <v>2949</v>
       </c>
       <c r="E238" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -17428,7 +17576,7 @@
         <v>1699</v>
       </c>
       <c r="E239" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -17578,7 +17726,7 @@
         <v>8999</v>
       </c>
       <c r="E241" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -17653,7 +17801,7 @@
         <v>3399</v>
       </c>
       <c r="E242" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -17728,7 +17876,7 @@
         <v>5299</v>
       </c>
       <c r="E243" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18026,7 +18174,7 @@
         <v>4399</v>
       </c>
       <c r="E247" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
@@ -18172,7 +18320,7 @@
         <v>2599</v>
       </c>
       <c r="E249" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18322,7 +18470,7 @@
         <v>2399</v>
       </c>
       <c r="E251" t="n">
-        <v>7.09</v>
+        <v>7.1</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -18397,7 +18545,7 @@
         <v>2599</v>
       </c>
       <c r="E252" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -18994,7 +19142,9 @@
           <t>苹果 A15</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="n">
+        <v>4</v>
+      </c>
       <c r="L260" t="n">
         <v>256</v>
       </c>
@@ -19063,7 +19213,9 @@
           <t>苹果 A15</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="n">
+        <v>4</v>
+      </c>
       <c r="L261" t="n">
         <v>512</v>
       </c>
@@ -19132,7 +19284,9 @@
           <t>苹果 A15</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="n">
+        <v>4</v>
+      </c>
       <c r="L262" t="n">
         <v>1024</v>
       </c>
@@ -19326,7 +19480,7 @@
         <v>2699</v>
       </c>
       <c r="E265" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -19476,7 +19630,7 @@
         <v>1699</v>
       </c>
       <c r="E267" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -19551,7 +19705,7 @@
         <v>2199</v>
       </c>
       <c r="E268" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -19701,7 +19855,7 @@
         <v>1799</v>
       </c>
       <c r="E270" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -19851,7 +20005,7 @@
         <v>4399</v>
       </c>
       <c r="E272" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -19926,7 +20080,7 @@
         <v>5999</v>
       </c>
       <c r="E273" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20001,7 +20155,7 @@
         <v>2989</v>
       </c>
       <c r="E274" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20076,7 +20230,7 @@
         <v>2699</v>
       </c>
       <c r="E275" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20151,7 +20305,7 @@
         <v>3699</v>
       </c>
       <c r="E276" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20226,7 +20380,7 @@
         <v>4499</v>
       </c>
       <c r="E277" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -20302,7 +20456,7 @@
         <v>1999</v>
       </c>
       <c r="E278" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -20452,7 +20606,7 @@
         <v>1699</v>
       </c>
       <c r="E280" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -20527,7 +20681,7 @@
         <v>1299</v>
       </c>
       <c r="E281" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -20677,7 +20831,7 @@
         <v>1399</v>
       </c>
       <c r="E283" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -20752,7 +20906,7 @@
         <v>2999</v>
       </c>
       <c r="E284" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -20827,7 +20981,7 @@
         <v>1999</v>
       </c>
       <c r="E285" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -20902,7 +21056,7 @@
         <v>1099</v>
       </c>
       <c r="E286" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -20977,7 +21131,7 @@
         <v>2699</v>
       </c>
       <c r="E287" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21052,7 +21206,7 @@
         <v>5899</v>
       </c>
       <c r="E288" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -21128,7 +21282,7 @@
         <v>6499</v>
       </c>
       <c r="E289" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -21270,7 +21424,7 @@
         <v>2199</v>
       </c>
       <c r="E291" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -21345,7 +21499,7 @@
         <v>2199</v>
       </c>
       <c r="E292" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -21558,7 +21712,7 @@
         <v>1499</v>
       </c>
       <c r="E295" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -21633,7 +21787,7 @@
         <v>2499</v>
       </c>
       <c r="E296" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -21708,7 +21862,7 @@
         <v>2599</v>
       </c>
       <c r="E297" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -21783,7 +21937,7 @@
         <v>3399</v>
       </c>
       <c r="E298" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22083,7 +22237,7 @@
         <v>2699</v>
       </c>
       <c r="E302" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -22154,7 +22308,7 @@
         <v>1999</v>
       </c>
       <c r="E303" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -22229,7 +22383,7 @@
         <v>3699</v>
       </c>
       <c r="E304" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -22300,7 +22454,7 @@
         <v>2699</v>
       </c>
       <c r="E305" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -22375,7 +22529,7 @@
         <v>3699</v>
       </c>
       <c r="E306" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -22450,7 +22604,7 @@
         <v>12999</v>
       </c>
       <c r="E307" t="n">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -22525,7 +22679,7 @@
         <v>3999</v>
       </c>
       <c r="E308" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -22600,7 +22754,7 @@
         <v>1999</v>
       </c>
       <c r="E309" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -22896,7 +23050,7 @@
         <v>3299</v>
       </c>
       <c r="E313" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -22971,7 +23125,7 @@
         <v>1799</v>
       </c>
       <c r="E314" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23046,7 +23200,7 @@
         <v>1249</v>
       </c>
       <c r="E315" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -23184,7 +23338,7 @@
         <v>3999</v>
       </c>
       <c r="E317" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -23255,7 +23409,7 @@
         <v>1999</v>
       </c>
       <c r="E318" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -23330,7 +23484,7 @@
         <v>1999</v>
       </c>
       <c r="E319" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -23397,7 +23551,7 @@
         <v>1499</v>
       </c>
       <c r="E320" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -23472,7 +23626,7 @@
         <v>3699</v>
       </c>
       <c r="E321" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -23547,7 +23701,7 @@
         <v>4499</v>
       </c>
       <c r="E322" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -23622,7 +23776,7 @@
         <v>5999</v>
       </c>
       <c r="E323" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -23697,7 +23851,7 @@
         <v>3999</v>
       </c>
       <c r="E324" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -23772,7 +23926,7 @@
         <v>6699</v>
       </c>
       <c r="E325" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -23847,7 +24001,7 @@
         <v>1499</v>
       </c>
       <c r="E326" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24072,7 +24226,7 @@
         <v>5499</v>
       </c>
       <c r="E329" t="n">
-        <v>6.69</v>
+        <v>6.7</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -24143,7 +24297,7 @@
         <v>6499</v>
       </c>
       <c r="E330" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -24214,7 +24368,7 @@
         <v>11999</v>
       </c>
       <c r="E331" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -24438,7 +24592,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" t="n">
+        <v>2775</v>
+      </c>
       <c r="H334" t="inlineStr">
         <is>
           <t>六核</t>
@@ -24511,7 +24667,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
+      <c r="G335" t="n">
+        <v>2775</v>
+      </c>
       <c r="H335" t="inlineStr">
         <is>
           <t>六核</t>
@@ -25327,7 +25485,7 @@
         <v>9999</v>
       </c>
       <c r="E346" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -25552,7 +25710,7 @@
         <v>2699</v>
       </c>
       <c r="E349" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -25627,7 +25785,7 @@
         <v>3499</v>
       </c>
       <c r="E350" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -25702,7 +25860,7 @@
         <v>5199</v>
       </c>
       <c r="E351" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -25777,7 +25935,7 @@
         <v>6499</v>
       </c>
       <c r="E352" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -25852,7 +26010,7 @@
         <v>2499</v>
       </c>
       <c r="E353" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -25927,7 +26085,7 @@
         <v>3299</v>
       </c>
       <c r="E354" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26077,7 +26235,7 @@
         <v>2099</v>
       </c>
       <c r="E356" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -26294,7 +26452,7 @@
         <v>1399</v>
       </c>
       <c r="E359" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -26369,7 +26527,7 @@
         <v>1199</v>
       </c>
       <c r="E360" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -26451,7 +26609,9 @@
           <t>2532x1170px</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" t="n">
+        <v>2775</v>
+      </c>
       <c r="H361" t="inlineStr">
         <is>
           <t>六核</t>
@@ -26663,7 +26823,7 @@
         <v>1699</v>
       </c>
       <c r="E364" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -26738,7 +26898,7 @@
         <v>3999</v>
       </c>
       <c r="E365" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -26813,7 +26973,7 @@
         <v>4499</v>
       </c>
       <c r="E366" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -26888,7 +27048,7 @@
         <v>5499</v>
       </c>
       <c r="E367" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -26963,7 +27123,7 @@
         <v>1199</v>
       </c>
       <c r="E368" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27034,7 +27194,7 @@
         <v>2099</v>
       </c>
       <c r="E369" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27109,7 +27269,7 @@
         <v>5999</v>
       </c>
       <c r="E370" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -27184,7 +27344,7 @@
         <v>3299</v>
       </c>
       <c r="E371" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -27259,7 +27419,7 @@
         <v>8999</v>
       </c>
       <c r="E372" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -27334,7 +27494,7 @@
         <v>2499</v>
       </c>
       <c r="E373" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -27634,7 +27794,7 @@
         <v>999</v>
       </c>
       <c r="E377" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -27784,7 +27944,7 @@
         <v>3299</v>
       </c>
       <c r="E379" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28230,7 +28390,7 @@
         <v>1299</v>
       </c>
       <c r="E385" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -28305,7 +28465,7 @@
         <v>1399</v>
       </c>
       <c r="E386" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -28380,7 +28540,7 @@
         <v>1799</v>
       </c>
       <c r="E387" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -28455,7 +28615,7 @@
         <v>8988</v>
       </c>
       <c r="E388" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -28530,7 +28690,7 @@
         <v>2799</v>
       </c>
       <c r="E389" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -28605,7 +28765,7 @@
         <v>3099</v>
       </c>
       <c r="E390" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -28680,7 +28840,7 @@
         <v>2099</v>
       </c>
       <c r="E391" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -28755,7 +28915,7 @@
         <v>9999</v>
       </c>
       <c r="E392" t="n">
-        <v>7.82</v>
+        <v>7.8</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -28830,7 +28990,7 @@
         <v>1399</v>
       </c>
       <c r="E393" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -28905,7 +29065,7 @@
         <v>2199</v>
       </c>
       <c r="E394" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -28980,7 +29140,7 @@
         <v>999</v>
       </c>
       <c r="E395" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -29126,7 +29286,7 @@
         <v>3499</v>
       </c>
       <c r="E397" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -29201,7 +29361,7 @@
         <v>1999</v>
       </c>
       <c r="E398" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -29226,7 +29386,9 @@
           <t>高通 骁龙680</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="n">
+        <v>12</v>
+      </c>
       <c r="L398" t="n">
         <v>256</v>
       </c>
@@ -29274,7 +29436,7 @@
         <v>3999</v>
       </c>
       <c r="E399" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -29349,7 +29511,7 @@
         <v>1799</v>
       </c>
       <c r="E400" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -29499,7 +29661,7 @@
         <v>1999</v>
       </c>
       <c r="E402" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -29574,7 +29736,7 @@
         <v>8999</v>
       </c>
       <c r="E403" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -29649,7 +29811,7 @@
         <v>1999</v>
       </c>
       <c r="E404" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -29799,7 +29961,7 @@
         <v>2999</v>
       </c>
       <c r="E406" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -29874,7 +30036,7 @@
         <v>1599</v>
       </c>
       <c r="E407" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -29949,7 +30111,7 @@
         <v>1799</v>
       </c>
       <c r="E408" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -30024,7 +30186,7 @@
         <v>2999</v>
       </c>
       <c r="E409" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -30233,7 +30395,7 @@
         <v>3999</v>
       </c>
       <c r="E412" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -30308,7 +30470,7 @@
         <v>4999</v>
       </c>
       <c r="E413" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -30383,7 +30545,7 @@
         <v>6999</v>
       </c>
       <c r="E414" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -30533,7 +30695,7 @@
         <v>1799</v>
       </c>
       <c r="E416" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -30758,7 +30920,7 @@
         <v>6999</v>
       </c>
       <c r="E419" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -30829,7 +30991,7 @@
         <v>7999</v>
       </c>
       <c r="E420" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -30900,7 +31062,7 @@
         <v>5999</v>
       </c>
       <c r="E421" t="n">
-        <v>6.69</v>
+        <v>6.7</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -30971,7 +31133,7 @@
         <v>6999</v>
       </c>
       <c r="E422" t="n">
-        <v>6.69</v>
+        <v>6.7</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -31042,7 +31204,7 @@
         <v>6999</v>
       </c>
       <c r="E423" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -31117,7 +31279,7 @@
         <v>8999</v>
       </c>
       <c r="E424" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -31188,7 +31350,7 @@
         <v>6599</v>
       </c>
       <c r="E425" t="n">
-        <v>7.71</v>
+        <v>7.7</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -31263,7 +31425,7 @@
         <v>13999</v>
       </c>
       <c r="E426" t="n">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -31330,7 +31492,7 @@
         <v>14999</v>
       </c>
       <c r="E427" t="n">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -31397,7 +31559,7 @@
         <v>15999</v>
       </c>
       <c r="E428" t="n">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -31464,7 +31626,7 @@
         <v>16999</v>
       </c>
       <c r="E429" t="n">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -31531,7 +31693,7 @@
         <v>9999</v>
       </c>
       <c r="E430" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -31609,7 +31771,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" t="n">
+        <v>2775</v>
+      </c>
       <c r="H431" t="inlineStr">
         <is>
           <t>六核</t>
@@ -31682,7 +31846,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
+      <c r="G432" t="n">
+        <v>2775</v>
+      </c>
       <c r="H432" t="inlineStr">
         <is>
           <t>六核</t>
@@ -31755,7 +31921,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
+      <c r="G433" t="n">
+        <v>2775</v>
+      </c>
       <c r="H433" t="inlineStr">
         <is>
           <t>六核</t>
@@ -31828,7 +31996,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
+      <c r="G434" t="n">
+        <v>2775</v>
+      </c>
       <c r="H434" t="inlineStr">
         <is>
           <t>六核</t>
@@ -31901,7 +32071,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
+      <c r="G435" t="n">
+        <v>2775</v>
+      </c>
       <c r="H435" t="inlineStr">
         <is>
           <t>六核</t>
@@ -32409,7 +32581,7 @@
         <v>12999</v>
       </c>
       <c r="E442" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -32476,7 +32648,7 @@
         <v>1399</v>
       </c>
       <c r="E443" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -32626,7 +32798,7 @@
         <v>1299</v>
       </c>
       <c r="E445" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -32701,7 +32873,7 @@
         <v>1699</v>
       </c>
       <c r="E446" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -32926,7 +33098,7 @@
         <v>4299</v>
       </c>
       <c r="E449" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -33001,7 +33173,7 @@
         <v>4599</v>
       </c>
       <c r="E450" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -33076,7 +33248,7 @@
         <v>4999</v>
       </c>
       <c r="E451" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -33151,7 +33323,7 @@
         <v>3399</v>
       </c>
       <c r="E452" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -33226,7 +33398,7 @@
         <v>1599</v>
       </c>
       <c r="E453" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -33308,7 +33480,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
+      <c r="G454" t="n">
+        <v>2775</v>
+      </c>
       <c r="H454" t="inlineStr">
         <is>
           <t>六核</t>
@@ -33377,7 +33551,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
+      <c r="G455" t="n">
+        <v>2775</v>
+      </c>
       <c r="H455" t="inlineStr">
         <is>
           <t>六核</t>
@@ -33450,7 +33626,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr"/>
+      <c r="G456" t="n">
+        <v>2775</v>
+      </c>
       <c r="H456" t="inlineStr">
         <is>
           <t>六核</t>
@@ -33579,7 +33757,7 @@
         <v>1399</v>
       </c>
       <c r="E458" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -33671,7 +33849,9 @@
         </is>
       </c>
       <c r="J459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="n">
+        <v>12</v>
+      </c>
       <c r="L459" t="n">
         <v>256</v>
       </c>
@@ -33719,7 +33899,7 @@
         <v>3999</v>
       </c>
       <c r="E460" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -33794,7 +33974,7 @@
         <v>1499</v>
       </c>
       <c r="E461" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -33944,7 +34124,7 @@
         <v>2299</v>
       </c>
       <c r="E463" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -34019,7 +34199,7 @@
         <v>3199</v>
       </c>
       <c r="E464" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -34094,7 +34274,7 @@
         <v>4399</v>
       </c>
       <c r="E465" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -34169,7 +34349,7 @@
         <v>4699</v>
       </c>
       <c r="E466" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -34186,7 +34366,9 @@
         </is>
       </c>
       <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="n">
+        <v>12</v>
+      </c>
       <c r="L466" t="n">
         <v>512</v>
       </c>
@@ -34234,7 +34416,7 @@
         <v>2099</v>
       </c>
       <c r="E467" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -34305,7 +34487,7 @@
         <v>2599</v>
       </c>
       <c r="E468" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -34380,7 +34562,7 @@
         <v>2799</v>
       </c>
       <c r="E469" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -34455,7 +34637,7 @@
         <v>2999</v>
       </c>
       <c r="E470" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -34530,7 +34712,7 @@
         <v>3499</v>
       </c>
       <c r="E471" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -34605,7 +34787,7 @@
         <v>2299</v>
       </c>
       <c r="E472" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -34751,7 +34933,7 @@
         <v>3999</v>
       </c>
       <c r="E474" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -34768,7 +34950,9 @@
         </is>
       </c>
       <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="n">
+        <v>12</v>
+      </c>
       <c r="L474" t="n">
         <v>256</v>
       </c>
@@ -34816,7 +35000,7 @@
         <v>4399</v>
       </c>
       <c r="E475" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -34833,7 +35017,9 @@
         </is>
       </c>
       <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="n">
+        <v>12</v>
+      </c>
       <c r="L475" t="n">
         <v>512</v>
       </c>
@@ -34898,7 +35084,9 @@
         </is>
       </c>
       <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="n">
+        <v>12</v>
+      </c>
       <c r="L476" t="n">
         <v>512</v>
       </c>
@@ -34963,7 +35151,9 @@
         </is>
       </c>
       <c r="J477" t="inlineStr"/>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="n">
+        <v>12</v>
+      </c>
       <c r="L477" t="n">
         <v>256</v>
       </c>
@@ -35028,7 +35218,9 @@
         </is>
       </c>
       <c r="J478" t="inlineStr"/>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="n">
+        <v>12</v>
+      </c>
       <c r="L478" t="n">
         <v>512</v>
       </c>
@@ -35076,7 +35268,7 @@
         <v>3999</v>
       </c>
       <c r="E479" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -35151,7 +35343,7 @@
         <v>5999</v>
       </c>
       <c r="E480" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -35251,7 +35443,9 @@
           <t>高通 骁龙680</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="n">
+        <v>12</v>
+      </c>
       <c r="L481" t="n">
         <v>256</v>
       </c>
@@ -35324,7 +35518,9 @@
           <t>高通 骁龙680</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="n">
+        <v>12</v>
+      </c>
       <c r="L482" t="n">
         <v>128</v>
       </c>
@@ -35372,7 +35568,7 @@
         <v>1199</v>
       </c>
       <c r="E483" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -35389,7 +35585,9 @@
         </is>
       </c>
       <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="n">
+        <v>12</v>
+      </c>
       <c r="L483" t="n">
         <v>128</v>
       </c>
@@ -35437,7 +35635,7 @@
         <v>1399</v>
       </c>
       <c r="E484" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -35454,7 +35652,9 @@
         </is>
       </c>
       <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="n">
+        <v>12</v>
+      </c>
       <c r="L484" t="n">
         <v>256</v>
       </c>
@@ -36086,7 +36286,7 @@
         <v>7499</v>
       </c>
       <c r="E493" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -36153,7 +36353,7 @@
         <v>7999</v>
       </c>
       <c r="E494" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -36587,7 +36787,7 @@
         <v>9999</v>
       </c>
       <c r="E500" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -36662,7 +36862,7 @@
         <v>7499</v>
       </c>
       <c r="E501" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -36737,7 +36937,7 @@
         <v>7999</v>
       </c>
       <c r="E502" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -36812,7 +37012,7 @@
         <v>8999</v>
       </c>
       <c r="E503" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -36887,7 +37087,7 @@
         <v>10999</v>
       </c>
       <c r="E504" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -37506,7 +37706,7 @@
         <v>1599</v>
       </c>
       <c r="E513" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -37581,7 +37781,7 @@
         <v>1799</v>
       </c>
       <c r="E514" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -37656,7 +37856,7 @@
         <v>1999</v>
       </c>
       <c r="E515" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -37731,7 +37931,7 @@
         <v>6499</v>
       </c>
       <c r="E516" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -37806,7 +38006,7 @@
         <v>2499</v>
       </c>
       <c r="E517" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -37881,7 +38081,7 @@
         <v>4999</v>
       </c>
       <c r="E518" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -37956,7 +38156,7 @@
         <v>1599</v>
       </c>
       <c r="E519" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -38031,7 +38231,7 @@
         <v>7299</v>
       </c>
       <c r="E520" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -38106,7 +38306,7 @@
         <v>7999</v>
       </c>
       <c r="E521" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -38181,7 +38381,7 @@
         <v>4699</v>
       </c>
       <c r="E522" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -38256,7 +38456,7 @@
         <v>5599</v>
       </c>
       <c r="E523" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -38331,7 +38531,7 @@
         <v>6199</v>
       </c>
       <c r="E524" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -38406,7 +38606,7 @@
         <v>1199</v>
       </c>
       <c r="E525" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -38481,7 +38681,7 @@
         <v>1288</v>
       </c>
       <c r="E526" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -38773,7 +38973,7 @@
         <v>1499</v>
       </c>
       <c r="E530" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -38923,7 +39123,7 @@
         <v>3499</v>
       </c>
       <c r="E532" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -38998,7 +39198,7 @@
         <v>2299</v>
       </c>
       <c r="E533" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -39073,7 +39273,7 @@
         <v>1699</v>
       </c>
       <c r="E534" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -39290,7 +39490,7 @@
         <v>3299</v>
       </c>
       <c r="E537" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -39440,7 +39640,7 @@
         <v>799</v>
       </c>
       <c r="E539" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -39515,7 +39715,7 @@
         <v>888</v>
       </c>
       <c r="E540" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -39590,7 +39790,7 @@
         <v>1199</v>
       </c>
       <c r="E541" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -39661,7 +39861,7 @@
         <v>1499</v>
       </c>
       <c r="E542" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -39736,7 +39936,7 @@
         <v>1398</v>
       </c>
       <c r="E543" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -39811,7 +40011,7 @@
         <v>1899</v>
       </c>
       <c r="E544" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -39886,7 +40086,7 @@
         <v>3799</v>
       </c>
       <c r="E545" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -39961,7 +40161,7 @@
         <v>2699</v>
       </c>
       <c r="E546" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -40036,7 +40236,7 @@
         <v>2999</v>
       </c>
       <c r="E547" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -40111,7 +40311,7 @@
         <v>3299</v>
       </c>
       <c r="E548" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -40336,7 +40536,7 @@
         <v>1499</v>
       </c>
       <c r="E551" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -40411,7 +40611,7 @@
         <v>5299</v>
       </c>
       <c r="E552" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -40486,7 +40686,7 @@
         <v>8999</v>
       </c>
       <c r="E553" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -40632,7 +40832,7 @@
         <v>6999</v>
       </c>
       <c r="E555" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -40949,7 +41149,9 @@
         </is>
       </c>
       <c r="J559" t="inlineStr"/>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="n">
+        <v>12</v>
+      </c>
       <c r="L559" t="n">
         <v>256</v>
       </c>
@@ -40997,7 +41199,7 @@
         <v>1199</v>
       </c>
       <c r="E560" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -41072,7 +41274,7 @@
         <v>1499</v>
       </c>
       <c r="E561" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -41218,7 +41420,7 @@
         <v>5288</v>
       </c>
       <c r="E563" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -41239,7 +41441,9 @@
         </is>
       </c>
       <c r="J563" t="inlineStr"/>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="n">
+        <v>12</v>
+      </c>
       <c r="L563" t="n">
         <v>256</v>
       </c>
@@ -41287,7 +41491,7 @@
         <v>1799</v>
       </c>
       <c r="E564" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -41362,7 +41566,7 @@
         <v>1799</v>
       </c>
       <c r="E565" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -41444,7 +41648,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr"/>
+      <c r="G566" t="n">
+        <v>2775</v>
+      </c>
       <c r="H566" t="inlineStr">
         <is>
           <t>六核</t>
@@ -41510,7 +41716,7 @@
         <v>899</v>
       </c>
       <c r="E567" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -41585,7 +41791,7 @@
         <v>799</v>
       </c>
       <c r="E568" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -41786,7 +41992,7 @@
         <v>4499</v>
       </c>
       <c r="E571" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -41868,7 +42074,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr"/>
+      <c r="G572" t="n">
+        <v>2775</v>
+      </c>
       <c r="H572" t="inlineStr">
         <is>
           <t>六核</t>
@@ -41941,7 +42149,9 @@
           <t>2556x1179px</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
+      <c r="G573" t="n">
+        <v>2775</v>
+      </c>
       <c r="H573" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42014,7 +42224,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr"/>
+      <c r="G574" t="n">
+        <v>2775</v>
+      </c>
       <c r="H574" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42083,7 +42295,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr"/>
+      <c r="G575" t="n">
+        <v>2775</v>
+      </c>
       <c r="H575" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42152,7 +42366,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr"/>
+      <c r="G576" t="n">
+        <v>2775</v>
+      </c>
       <c r="H576" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42221,7 +42437,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G577" t="inlineStr"/>
+      <c r="G577" t="n">
+        <v>2775</v>
+      </c>
       <c r="H577" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42294,7 +42512,9 @@
           <t>2796x1290px</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr"/>
+      <c r="G578" t="n">
+        <v>2775</v>
+      </c>
       <c r="H578" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42367,7 +42587,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G579" t="inlineStr"/>
+      <c r="G579" t="n">
+        <v>2775</v>
+      </c>
       <c r="H579" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42436,7 +42658,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr"/>
+      <c r="G580" t="n">
+        <v>2775</v>
+      </c>
       <c r="H580" t="inlineStr">
         <is>
           <t>六核</t>
@@ -42561,7 +42785,7 @@
         <v>999</v>
       </c>
       <c r="E582" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -42636,7 +42860,7 @@
         <v>5299</v>
       </c>
       <c r="E583" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -42711,7 +42935,7 @@
         <v>8999</v>
       </c>
       <c r="E584" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -42786,7 +43010,7 @@
         <v>4699</v>
       </c>
       <c r="E585" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -42936,7 +43160,7 @@
         <v>4299</v>
       </c>
       <c r="E587" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -43011,7 +43235,7 @@
         <v>5299</v>
       </c>
       <c r="E588" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -43086,7 +43310,7 @@
         <v>5799</v>
       </c>
       <c r="E589" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -43161,7 +43385,7 @@
         <v>4699</v>
       </c>
       <c r="E590" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -43236,7 +43460,7 @@
         <v>4999</v>
       </c>
       <c r="E591" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -43311,7 +43535,7 @@
         <v>5499</v>
       </c>
       <c r="E592" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -43386,7 +43610,7 @@
         <v>5999</v>
       </c>
       <c r="E593" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -43461,7 +43685,7 @@
         <v>6799</v>
       </c>
       <c r="E594" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -43611,7 +43835,7 @@
         <v>1499</v>
       </c>
       <c r="E596" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -43686,7 +43910,7 @@
         <v>1099</v>
       </c>
       <c r="E597" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -43761,7 +43985,7 @@
         <v>3699</v>
       </c>
       <c r="E598" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -43782,7 +44006,9 @@
         </is>
       </c>
       <c r="J598" t="inlineStr"/>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="n">
+        <v>12</v>
+      </c>
       <c r="L598" t="n">
         <v>256</v>
       </c>
@@ -43918,7 +44144,9 @@
         </is>
       </c>
       <c r="J600" t="inlineStr"/>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="n">
+        <v>12</v>
+      </c>
       <c r="L600" t="n">
         <v>512</v>
       </c>
@@ -43966,7 +44194,7 @@
         <v>3999</v>
       </c>
       <c r="E601" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -43987,7 +44215,9 @@
         </is>
       </c>
       <c r="J601" t="inlineStr"/>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="n">
+        <v>12</v>
+      </c>
       <c r="L601" t="n">
         <v>512</v>
       </c>
@@ -44031,7 +44261,7 @@
         <v>5499</v>
       </c>
       <c r="E602" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -44181,7 +44411,7 @@
         <v>5499</v>
       </c>
       <c r="E604" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -44323,7 +44553,7 @@
         <v>3399</v>
       </c>
       <c r="E606" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -44398,7 +44628,7 @@
         <v>2299</v>
       </c>
       <c r="E607" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -44548,7 +44778,7 @@
         <v>3399</v>
       </c>
       <c r="E609" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -44623,7 +44853,7 @@
         <v>2699</v>
       </c>
       <c r="E610" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -44698,7 +44928,7 @@
         <v>13999</v>
       </c>
       <c r="E611" t="n">
-        <v>7.93</v>
+        <v>7.9</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -45210,7 +45440,7 @@
         <v>2999</v>
       </c>
       <c r="E619" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -45352,7 +45582,7 @@
         <v>14999</v>
       </c>
       <c r="E621" t="n">
-        <v>7.93</v>
+        <v>7.9</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -45415,7 +45645,7 @@
         <v>15999</v>
       </c>
       <c r="E622" t="n">
-        <v>7.93</v>
+        <v>7.9</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -45478,7 +45708,7 @@
         <v>12999</v>
       </c>
       <c r="E623" t="n">
-        <v>7.93</v>
+        <v>7.9</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -45691,7 +45921,7 @@
         <v>1399</v>
       </c>
       <c r="E626" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -45766,7 +45996,7 @@
         <v>1999</v>
       </c>
       <c r="E627" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -45916,7 +46146,7 @@
         <v>6499</v>
       </c>
       <c r="E629" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -45991,7 +46221,7 @@
         <v>1799</v>
       </c>
       <c r="E630" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -46008,7 +46238,9 @@
         </is>
       </c>
       <c r="J630" t="inlineStr"/>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="n">
+        <v>12</v>
+      </c>
       <c r="L630" t="n">
         <v>128</v>
       </c>
@@ -46056,7 +46288,7 @@
         <v>1999</v>
       </c>
       <c r="E631" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -46073,7 +46305,9 @@
         </is>
       </c>
       <c r="J631" t="inlineStr"/>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="n">
+        <v>12</v>
+      </c>
       <c r="L631" t="n">
         <v>256</v>
       </c>
@@ -46121,7 +46355,7 @@
         <v>2299</v>
       </c>
       <c r="E632" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -46138,7 +46372,9 @@
         </is>
       </c>
       <c r="J632" t="inlineStr"/>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="n">
+        <v>12</v>
+      </c>
       <c r="L632" t="n">
         <v>512</v>
       </c>
@@ -46529,7 +46765,7 @@
         <v>8999</v>
       </c>
       <c r="E638" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -46611,7 +46847,9 @@
           <t>2532x1170px</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr"/>
+      <c r="G639" t="n">
+        <v>2775</v>
+      </c>
       <c r="H639" t="inlineStr">
         <is>
           <t>六核</t>
@@ -46680,7 +46918,9 @@
           <t>2532x1170px</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr"/>
+      <c r="G640" t="n">
+        <v>2775</v>
+      </c>
       <c r="H640" t="inlineStr">
         <is>
           <t>六核</t>
@@ -46742,7 +46982,7 @@
         <v>1199</v>
       </c>
       <c r="E641" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -46958,7 +47198,9 @@
           <t>主：2120x1320px 副：980x980px</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr"/>
+      <c r="G644" t="n">
+        <v>5200</v>
+      </c>
       <c r="H644" t="inlineStr"/>
       <c r="I644" t="inlineStr">
         <is>
@@ -47209,7 +47451,7 @@
         <v>1799</v>
       </c>
       <c r="E648" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -47426,7 +47668,7 @@
         <v>4199</v>
       </c>
       <c r="E651" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -47501,7 +47743,7 @@
         <v>4699</v>
       </c>
       <c r="E652" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -47576,7 +47818,7 @@
         <v>4199</v>
       </c>
       <c r="E653" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -47651,7 +47893,7 @@
         <v>6999</v>
       </c>
       <c r="E654" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -47726,7 +47968,7 @@
         <v>7999</v>
       </c>
       <c r="E655" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -47801,7 +48043,7 @@
         <v>4199</v>
       </c>
       <c r="E656" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -47876,7 +48118,7 @@
         <v>6499</v>
       </c>
       <c r="E657" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -47951,7 +48193,7 @@
         <v>1999</v>
       </c>
       <c r="E658" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -48100,7 +48342,9 @@
           <t>2760x1256px</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr"/>
+      <c r="G660" t="n">
+        <v>5200</v>
+      </c>
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr">
         <is>
@@ -48225,7 +48469,7 @@
         <v>1199</v>
       </c>
       <c r="E662" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -48300,7 +48544,7 @@
         <v>3699</v>
       </c>
       <c r="E663" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -48375,7 +48619,7 @@
         <v>4399</v>
       </c>
       <c r="E664" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -48450,7 +48694,7 @@
         <v>4699</v>
       </c>
       <c r="E665" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -48525,7 +48769,7 @@
         <v>4999</v>
       </c>
       <c r="E666" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -48600,7 +48844,7 @@
         <v>5499</v>
       </c>
       <c r="E667" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -48675,7 +48919,7 @@
         <v>6999</v>
       </c>
       <c r="E668" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -48750,7 +48994,7 @@
         <v>7999</v>
       </c>
       <c r="E669" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -49050,7 +49294,7 @@
         <v>1199</v>
       </c>
       <c r="E673" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -49067,7 +49311,9 @@
         </is>
       </c>
       <c r="J673" t="inlineStr"/>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="n">
+        <v>12</v>
+      </c>
       <c r="L673" t="n">
         <v>128</v>
       </c>
@@ -49115,7 +49361,7 @@
         <v>1399</v>
       </c>
       <c r="E674" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -49132,7 +49378,9 @@
         </is>
       </c>
       <c r="J674" t="inlineStr"/>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="n">
+        <v>12</v>
+      </c>
       <c r="L674" t="n">
         <v>256</v>
       </c>
@@ -49180,7 +49428,7 @@
         <v>1699</v>
       </c>
       <c r="E675" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -49197,7 +49445,9 @@
         </is>
       </c>
       <c r="J675" t="inlineStr"/>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="n">
+        <v>12</v>
+      </c>
       <c r="L675" t="n">
         <v>512</v>
       </c>
@@ -49245,7 +49495,7 @@
         <v>1499</v>
       </c>
       <c r="E676" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -49262,7 +49512,9 @@
         </is>
       </c>
       <c r="J676" t="inlineStr"/>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="n">
+        <v>12</v>
+      </c>
       <c r="L676" t="n">
         <v>128</v>
       </c>
@@ -49310,7 +49562,7 @@
         <v>1499</v>
       </c>
       <c r="E677" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -49385,7 +49637,7 @@
         <v>1599</v>
       </c>
       <c r="E678" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -49460,7 +49712,7 @@
         <v>1799</v>
       </c>
       <c r="E679" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -49535,7 +49787,7 @@
         <v>1099</v>
       </c>
       <c r="E680" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -49760,7 +50012,7 @@
         <v>2799</v>
       </c>
       <c r="E683" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -49835,7 +50087,7 @@
         <v>4199</v>
       </c>
       <c r="E684" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -49852,7 +50104,9 @@
         </is>
       </c>
       <c r="J684" t="inlineStr"/>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="n">
+        <v>12</v>
+      </c>
       <c r="L684" t="n">
         <v>256</v>
       </c>
@@ -49900,7 +50154,7 @@
         <v>3499</v>
       </c>
       <c r="E685" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -49917,7 +50171,9 @@
         </is>
       </c>
       <c r="J685" t="inlineStr"/>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="n">
+        <v>12</v>
+      </c>
       <c r="L685" t="n">
         <v>256</v>
       </c>
@@ -49982,7 +50238,9 @@
         </is>
       </c>
       <c r="J686" t="inlineStr"/>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="n">
+        <v>12</v>
+      </c>
       <c r="L686" t="n">
         <v>256</v>
       </c>
@@ -50030,7 +50288,7 @@
         <v>1899</v>
       </c>
       <c r="E687" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -50105,7 +50363,7 @@
         <v>3399</v>
       </c>
       <c r="E688" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -50180,7 +50438,7 @@
         <v>3799</v>
       </c>
       <c r="E689" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -50255,7 +50513,7 @@
         <v>3999</v>
       </c>
       <c r="E690" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -50330,7 +50588,7 @@
         <v>2699</v>
       </c>
       <c r="E691" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -50405,7 +50663,7 @@
         <v>2999</v>
       </c>
       <c r="E692" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -50480,7 +50738,7 @@
         <v>3299</v>
       </c>
       <c r="E693" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -50572,7 +50830,9 @@
         </is>
       </c>
       <c r="J694" t="inlineStr"/>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="n">
+        <v>12</v>
+      </c>
       <c r="L694" t="n">
         <v>512</v>
       </c>
@@ -50620,7 +50880,7 @@
         <v>3799</v>
       </c>
       <c r="E695" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -50637,7 +50897,9 @@
         </is>
       </c>
       <c r="J695" t="inlineStr"/>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="n">
+        <v>12</v>
+      </c>
       <c r="L695" t="n">
         <v>512</v>
       </c>
@@ -50685,7 +50947,7 @@
         <v>3999</v>
       </c>
       <c r="E696" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -50702,7 +50964,9 @@
         </is>
       </c>
       <c r="J696" t="inlineStr"/>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="n">
+        <v>12</v>
+      </c>
       <c r="L696" t="n">
         <v>512</v>
       </c>
@@ -50750,7 +51014,7 @@
         <v>4499</v>
       </c>
       <c r="E697" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -50767,7 +51031,9 @@
         </is>
       </c>
       <c r="J697" t="inlineStr"/>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="n">
+        <v>12</v>
+      </c>
       <c r="L697" t="n">
         <v>512</v>
       </c>
@@ -50815,7 +51081,7 @@
         <v>4999</v>
       </c>
       <c r="E698" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -50832,7 +51098,9 @@
         </is>
       </c>
       <c r="J698" t="inlineStr"/>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="n">
+        <v>12</v>
+      </c>
       <c r="L698" t="n">
         <v>1024</v>
       </c>
@@ -50880,7 +51148,7 @@
         <v>2499</v>
       </c>
       <c r="E699" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -50955,7 +51223,7 @@
         <v>3399</v>
       </c>
       <c r="E700" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -51030,7 +51298,7 @@
         <v>3699</v>
       </c>
       <c r="E701" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -51783,7 +52051,7 @@
         <v>6999</v>
       </c>
       <c r="E712" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -51858,7 +52126,7 @@
         <v>7999</v>
       </c>
       <c r="E713" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -51933,7 +52201,7 @@
         <v>8499</v>
       </c>
       <c r="E714" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -52008,7 +52276,7 @@
         <v>8999</v>
       </c>
       <c r="E715" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -52083,7 +52351,7 @@
         <v>1399</v>
       </c>
       <c r="E716" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -52158,7 +52426,7 @@
         <v>1599</v>
       </c>
       <c r="E717" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -52233,7 +52501,7 @@
         <v>1799</v>
       </c>
       <c r="E718" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -52308,7 +52576,7 @@
         <v>1999</v>
       </c>
       <c r="E719" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -52884,7 +53152,7 @@
         <v>5499</v>
       </c>
       <c r="E727" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -52959,7 +53227,7 @@
         <v>1399</v>
       </c>
       <c r="E728" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -53034,7 +53302,7 @@
         <v>1199</v>
       </c>
       <c r="E729" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -53109,7 +53377,7 @@
         <v>2299</v>
       </c>
       <c r="E730" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -53191,7 +53459,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G731" t="inlineStr"/>
+      <c r="G731" t="n">
+        <v>2775</v>
+      </c>
       <c r="H731" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53264,7 +53534,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr"/>
+      <c r="G732" t="n">
+        <v>2775</v>
+      </c>
       <c r="H732" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53280,7 +53552,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="n">
+        <v>4</v>
+      </c>
       <c r="L732" t="n">
         <v>256</v>
       </c>
@@ -53398,7 +53672,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G734" t="inlineStr"/>
+      <c r="G734" t="n">
+        <v>2775</v>
+      </c>
       <c r="H734" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53414,7 +53690,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="n">
+        <v>4</v>
+      </c>
       <c r="L734" t="n">
         <v>256</v>
       </c>
@@ -53465,7 +53743,9 @@
           <t>2736x1260px</t>
         </is>
       </c>
-      <c r="G735" t="inlineStr"/>
+      <c r="G735" t="n">
+        <v>2775</v>
+      </c>
       <c r="H735" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53481,7 +53761,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="n">
+        <v>4</v>
+      </c>
       <c r="L735" t="n">
         <v>1024</v>
       </c>
@@ -53529,7 +53811,7 @@
         <v>1599</v>
       </c>
       <c r="E736" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -53604,7 +53886,7 @@
         <v>1799</v>
       </c>
       <c r="E737" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -53679,7 +53961,7 @@
         <v>1999</v>
       </c>
       <c r="E738" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -53821,7 +54103,7 @@
         <v>1799</v>
       </c>
       <c r="E740" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -53903,7 +54185,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr"/>
+      <c r="G741" t="n">
+        <v>2775</v>
+      </c>
       <c r="H741" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53976,7 +54260,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr"/>
+      <c r="G742" t="n">
+        <v>2775</v>
+      </c>
       <c r="H742" t="inlineStr">
         <is>
           <t>六核</t>
@@ -53992,7 +54278,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="n">
+        <v>4</v>
+      </c>
       <c r="L742" t="n">
         <v>512</v>
       </c>
@@ -54043,7 +54331,9 @@
           <t>2622x1206px</t>
         </is>
       </c>
-      <c r="G743" t="inlineStr"/>
+      <c r="G743" t="n">
+        <v>2775</v>
+      </c>
       <c r="H743" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54059,7 +54349,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="n">
+        <v>4</v>
+      </c>
       <c r="L743" t="n">
         <v>1024</v>
       </c>
@@ -54110,7 +54402,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G744" t="inlineStr"/>
+      <c r="G744" t="n">
+        <v>2775</v>
+      </c>
       <c r="H744" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54126,7 +54420,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="n">
+        <v>4</v>
+      </c>
       <c r="L744" t="n">
         <v>512</v>
       </c>
@@ -54177,7 +54473,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr"/>
+      <c r="G745" t="n">
+        <v>2775</v>
+      </c>
       <c r="H745" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54193,7 +54491,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="n">
+        <v>4</v>
+      </c>
       <c r="L745" t="n">
         <v>1024</v>
       </c>
@@ -54244,7 +54544,9 @@
           <t>2868x1320px</t>
         </is>
       </c>
-      <c r="G746" t="inlineStr"/>
+      <c r="G746" t="n">
+        <v>2775</v>
+      </c>
       <c r="H746" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54260,7 +54562,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="n">
+        <v>4</v>
+      </c>
       <c r="L746" t="n">
         <v>2048</v>
       </c>
@@ -54311,7 +54615,9 @@
           <t>2736x1260px</t>
         </is>
       </c>
-      <c r="G747" t="inlineStr"/>
+      <c r="G747" t="n">
+        <v>2775</v>
+      </c>
       <c r="H747" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54327,7 +54633,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="n">
+        <v>4</v>
+      </c>
       <c r="L747" t="n">
         <v>1024</v>
       </c>
@@ -54382,7 +54690,9 @@
           <t>2736x1260px</t>
         </is>
       </c>
-      <c r="G748" t="inlineStr"/>
+      <c r="G748" t="n">
+        <v>2775</v>
+      </c>
       <c r="H748" t="inlineStr">
         <is>
           <t>六核</t>
@@ -54398,7 +54708,9 @@
           <t>苹果 A19 Pro</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="n">
+        <v>4</v>
+      </c>
       <c r="L748" t="n">
         <v>1024</v>
       </c>
@@ -54446,7 +54758,7 @@
         <v>799</v>
       </c>
       <c r="E749" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -54521,7 +54833,7 @@
         <v>5299</v>
       </c>
       <c r="E750" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -54596,7 +54908,7 @@
         <v>4399</v>
       </c>
       <c r="E751" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -54671,7 +54983,7 @@
         <v>4399</v>
       </c>
       <c r="E752" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -54746,7 +55058,7 @@
         <v>5299</v>
       </c>
       <c r="E753" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -54821,7 +55133,7 @@
         <v>999</v>
       </c>
       <c r="E754" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -54896,7 +55208,7 @@
         <v>1099</v>
       </c>
       <c r="E755" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -54971,7 +55283,7 @@
         <v>1499</v>
       </c>
       <c r="E756" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -55046,7 +55358,7 @@
         <v>4499</v>
       </c>
       <c r="E757" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -55121,7 +55433,7 @@
         <v>4799</v>
       </c>
       <c r="E758" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -55196,7 +55508,7 @@
         <v>4999</v>
       </c>
       <c r="E759" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -55271,7 +55583,7 @@
         <v>5699</v>
       </c>
       <c r="E760" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -55346,7 +55658,7 @@
         <v>5999</v>
       </c>
       <c r="E761" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -55421,7 +55733,7 @@
         <v>6199</v>
       </c>
       <c r="E762" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -55496,7 +55808,7 @@
         <v>6699</v>
       </c>
       <c r="E763" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -55721,7 +56033,7 @@
         <v>4999</v>
       </c>
       <c r="E766" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -55796,7 +56108,7 @@
         <v>4699</v>
       </c>
       <c r="E767" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -55871,7 +56183,7 @@
         <v>4999</v>
       </c>
       <c r="E768" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -55946,7 +56258,7 @@
         <v>5299</v>
       </c>
       <c r="E769" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -56021,7 +56333,7 @@
         <v>5799</v>
       </c>
       <c r="E770" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -56096,7 +56408,7 @@
         <v>5999</v>
       </c>
       <c r="E771" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -56171,7 +56483,7 @@
         <v>6699</v>
       </c>
       <c r="E772" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -56246,7 +56558,7 @@
         <v>8299</v>
       </c>
       <c r="E773" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -56321,7 +56633,7 @@
         <v>5699</v>
       </c>
       <c r="E774" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -56396,7 +56708,7 @@
         <v>5999</v>
       </c>
       <c r="E775" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -56471,7 +56783,7 @@
         <v>6699</v>
       </c>
       <c r="E776" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -56563,7 +56875,9 @@
         </is>
       </c>
       <c r="J777" t="inlineStr"/>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="n">
+        <v>12</v>
+      </c>
       <c r="L777" t="n">
         <v>256</v>
       </c>
@@ -56628,7 +56942,9 @@
         </is>
       </c>
       <c r="J778" t="inlineStr"/>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="n">
+        <v>12</v>
+      </c>
       <c r="L778" t="n">
         <v>512</v>
       </c>
@@ -56676,7 +56992,7 @@
         <v>3488</v>
       </c>
       <c r="E779" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -56697,7 +57013,9 @@
         </is>
       </c>
       <c r="J779" t="inlineStr"/>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="n">
+        <v>12</v>
+      </c>
       <c r="L779" t="n">
         <v>256</v>
       </c>
@@ -56895,7 +57213,7 @@
         <v>4699</v>
       </c>
       <c r="E782" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -57108,7 +57426,7 @@
         <v>1799</v>
       </c>
       <c r="E785" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -57183,7 +57501,7 @@
         <v>1999</v>
       </c>
       <c r="E786" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -57258,7 +57576,7 @@
         <v>2299</v>
       </c>
       <c r="E787" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -57333,7 +57651,7 @@
         <v>2599</v>
       </c>
       <c r="E788" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -57408,7 +57726,7 @@
         <v>2999</v>
       </c>
       <c r="E789" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -57483,7 +57801,7 @@
         <v>3299</v>
       </c>
       <c r="E790" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -57558,7 +57876,7 @@
         <v>3699</v>
       </c>
       <c r="E791" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -57633,7 +57951,7 @@
         <v>3999</v>
       </c>
       <c r="E792" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -57708,7 +58026,7 @@
         <v>5999</v>
       </c>
       <c r="E793" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -57913,7 +58231,7 @@
         <v>2699</v>
       </c>
       <c r="E796" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -57988,7 +58306,7 @@
         <v>3599</v>
       </c>
       <c r="E797" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -58063,7 +58381,7 @@
         <v>3899</v>
       </c>
       <c r="E798" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -58138,7 +58456,7 @@
         <v>4199</v>
       </c>
       <c r="E799" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -58213,7 +58531,7 @@
         <v>4799</v>
       </c>
       <c r="E800" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -58355,7 +58673,7 @@
         <v>2999</v>
       </c>
       <c r="E802" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -58430,7 +58748,7 @@
         <v>3299</v>
       </c>
       <c r="E803" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -58505,7 +58823,7 @@
         <v>5199</v>
       </c>
       <c r="E804" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -58576,7 +58894,7 @@
         <v>5499</v>
       </c>
       <c r="E805" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -58647,7 +58965,7 @@
         <v>6499</v>
       </c>
       <c r="E806" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -58714,7 +59032,7 @@
         <v>6999</v>
       </c>
       <c r="E807" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -58781,7 +59099,7 @@
         <v>7999</v>
       </c>
       <c r="E808" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -59254,7 +59572,7 @@
         <v>2999</v>
       </c>
       <c r="E815" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
@@ -59325,7 +59643,7 @@
         <v>3699</v>
       </c>
       <c r="E816" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -59625,7 +59943,7 @@
         <v>3999</v>
       </c>
       <c r="E820" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -59700,7 +60018,7 @@
         <v>4299</v>
       </c>
       <c r="E821" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -59775,7 +60093,7 @@
         <v>3399</v>
       </c>
       <c r="E822" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F822" t="inlineStr"/>
       <c r="G822" t="n">
@@ -59846,7 +60164,7 @@
         <v>3299</v>
       </c>
       <c r="E823" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F823" t="inlineStr"/>
       <c r="G823" t="n">
@@ -59917,7 +60235,7 @@
         <v>3599</v>
       </c>
       <c r="E824" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F824" t="inlineStr"/>
       <c r="G824" t="n">
@@ -60009,7 +60327,9 @@
           <t>海思 麒麟 8020</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="n">
+        <v>12</v>
+      </c>
       <c r="L825" t="n">
         <v>256</v>
       </c>
@@ -60057,7 +60377,7 @@
         <v>4199</v>
       </c>
       <c r="E826" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -60078,7 +60398,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="n">
+        <v>12</v>
+      </c>
       <c r="L826" t="n">
         <v>256</v>
       </c>
@@ -60126,7 +60448,7 @@
         <v>3999</v>
       </c>
       <c r="E827" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -60201,7 +60523,7 @@
         <v>2899</v>
       </c>
       <c r="E828" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -60276,7 +60598,7 @@
         <v>1599</v>
       </c>
       <c r="E829" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -60372,7 +60694,9 @@
           <t>海思 麒麟 8020</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="n">
+        <v>12</v>
+      </c>
       <c r="L830" t="n">
         <v>512</v>
       </c>
@@ -60420,7 +60744,7 @@
         <v>3599</v>
       </c>
       <c r="E831" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -60441,7 +60765,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="n">
+        <v>12</v>
+      </c>
       <c r="L831" t="n">
         <v>256</v>
       </c>
@@ -60489,7 +60815,7 @@
         <v>3899</v>
       </c>
       <c r="E832" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -60510,7 +60836,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="n">
+        <v>12</v>
+      </c>
       <c r="L832" t="n">
         <v>512</v>
       </c>
@@ -60558,7 +60886,7 @@
         <v>4499</v>
       </c>
       <c r="E833" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -60579,7 +60907,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="n">
+        <v>12</v>
+      </c>
       <c r="L833" t="n">
         <v>512</v>
       </c>
@@ -60627,7 +60957,7 @@
         <v>4999</v>
       </c>
       <c r="E834" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -60648,7 +60978,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="n">
+        <v>12</v>
+      </c>
       <c r="L834" t="n">
         <v>1024</v>
       </c>
@@ -60696,7 +61028,7 @@
         <v>4399</v>
       </c>
       <c r="E835" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -60771,7 +61103,7 @@
         <v>4699</v>
       </c>
       <c r="E836" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -60846,7 +61178,7 @@
         <v>2599</v>
       </c>
       <c r="E837" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -60921,7 +61253,7 @@
         <v>2899</v>
       </c>
       <c r="E838" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -60996,7 +61328,7 @@
         <v>3099</v>
       </c>
       <c r="E839" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -61071,7 +61403,7 @@
         <v>3399</v>
       </c>
       <c r="E840" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -61146,7 +61478,7 @@
         <v>3999</v>
       </c>
       <c r="E841" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -61221,7 +61553,7 @@
         <v>2699</v>
       </c>
       <c r="E842" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -61296,7 +61628,7 @@
         <v>2999</v>
       </c>
       <c r="E843" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -61371,7 +61703,7 @@
         <v>4999</v>
       </c>
       <c r="E844" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -61446,7 +61778,7 @@
         <v>5299</v>
       </c>
       <c r="E845" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -61521,7 +61853,7 @@
         <v>5599</v>
       </c>
       <c r="E846" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -61596,7 +61928,7 @@
         <v>7999</v>
       </c>
       <c r="E847" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -61671,7 +62003,7 @@
         <v>8999</v>
       </c>
       <c r="E848" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -62089,7 +62421,7 @@
         <v>9999</v>
       </c>
       <c r="E854" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -62164,7 +62496,7 @@
         <v>9999</v>
       </c>
       <c r="E855" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -62239,7 +62571,7 @@
         <v>8999</v>
       </c>
       <c r="E856" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -62314,7 +62646,7 @@
         <v>9999</v>
       </c>
       <c r="E857" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -62396,7 +62728,9 @@
           <t>2532x1170px</t>
         </is>
       </c>
-      <c r="G858" t="inlineStr"/>
+      <c r="G858" t="n">
+        <v>2775</v>
+      </c>
       <c r="H858" t="inlineStr">
         <is>
           <t>六核</t>
@@ -62412,7 +62746,9 @@
           <t>苹果 A19</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="n">
+        <v>4</v>
+      </c>
       <c r="L858" t="n">
         <v>256</v>
       </c>
@@ -62467,7 +62803,9 @@
           <t>2532x1170px</t>
         </is>
       </c>
-      <c r="G859" t="inlineStr"/>
+      <c r="G859" t="n">
+        <v>2775</v>
+      </c>
       <c r="H859" t="inlineStr">
         <is>
           <t>六核</t>
@@ -62483,7 +62821,9 @@
           <t>苹果 A19</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="n">
+        <v>4</v>
+      </c>
       <c r="L859" t="n">
         <v>512</v>
       </c>
@@ -62531,7 +62871,7 @@
         <v>1499</v>
       </c>
       <c r="E860" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -62552,7 +62892,9 @@
           <t>海思 麒麟8000</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="n">
+        <v>12</v>
+      </c>
       <c r="L860" t="n">
         <v>128</v>
       </c>
@@ -62600,7 +62942,7 @@
         <v>1699</v>
       </c>
       <c r="E861" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -62621,7 +62963,9 @@
           <t>海思 麒麟8000</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="n">
+        <v>12</v>
+      </c>
       <c r="L861" t="n">
         <v>128</v>
       </c>
@@ -62669,7 +63013,7 @@
         <v>10999</v>
       </c>
       <c r="E862" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -62744,7 +63088,7 @@
         <v>6999</v>
       </c>
       <c r="E863" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -62953,7 +63297,7 @@
         <v>1999</v>
       </c>
       <c r="E866" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -62974,7 +63318,9 @@
           <t>海思 麒麟8000</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="n">
+        <v>12</v>
+      </c>
       <c r="L866" t="n">
         <v>256</v>
       </c>
@@ -63022,7 +63368,7 @@
         <v>2399</v>
       </c>
       <c r="E867" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -63043,7 +63389,9 @@
           <t>海思 麒麟8000</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="n">
+        <v>12</v>
+      </c>
       <c r="L867" t="n">
         <v>512</v>
       </c>
@@ -63091,7 +63439,7 @@
         <v>1799</v>
       </c>
       <c r="E868" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -63112,7 +63460,9 @@
           <t>海思 麒麟8000</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="n">
+        <v>12</v>
+      </c>
       <c r="L868" t="n">
         <v>256</v>
       </c>
@@ -63160,7 +63510,7 @@
         <v>1299</v>
       </c>
       <c r="E869" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -63181,7 +63531,9 @@
           <t>海思 麒麟 8000A</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="n">
+        <v>12</v>
+      </c>
       <c r="L869" t="n">
         <v>128</v>
       </c>
@@ -63229,7 +63581,7 @@
         <v>1599</v>
       </c>
       <c r="E870" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -63250,7 +63602,9 @@
           <t>海思 麒麟 8000A</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="n">
+        <v>12</v>
+      </c>
       <c r="L870" t="n">
         <v>128</v>
       </c>
@@ -63298,7 +63652,7 @@
         <v>3199</v>
       </c>
       <c r="E871" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -63373,7 +63727,7 @@
         <v>3499</v>
       </c>
       <c r="E872" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -63448,7 +63802,7 @@
         <v>4999</v>
       </c>
       <c r="E873" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -63523,7 +63877,7 @@
         <v>8999</v>
       </c>
       <c r="E874" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -63598,7 +63952,7 @@
         <v>7499</v>
       </c>
       <c r="E875" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -63673,7 +64027,7 @@
         <v>7999</v>
       </c>
       <c r="E876" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -63748,7 +64102,7 @@
         <v>11999</v>
       </c>
       <c r="E877" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -63823,7 +64177,7 @@
         <v>6999</v>
       </c>
       <c r="E878" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -63898,7 +64252,7 @@
         <v>5499</v>
       </c>
       <c r="E879" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -63973,7 +64327,7 @@
         <v>5999</v>
       </c>
       <c r="E880" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -64048,7 +64402,7 @@
         <v>7999</v>
       </c>
       <c r="E881" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -64691,7 +65045,7 @@
         <v>5299</v>
       </c>
       <c r="E890" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -64837,7 +65191,7 @@
         <v>7499</v>
       </c>
       <c r="E892" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -64912,7 +65266,7 @@
         <v>2399</v>
       </c>
       <c r="E893" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -65349,7 +65703,9 @@
           <t>2856x1320px</t>
         </is>
       </c>
-      <c r="G899" t="inlineStr"/>
+      <c r="G899" t="n">
+        <v>5200</v>
+      </c>
       <c r="H899" t="inlineStr"/>
       <c r="I899" t="inlineStr">
         <is>
@@ -65411,7 +65767,7 @@
         <v>7999</v>
       </c>
       <c r="E900" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -65486,7 +65842,7 @@
         <v>8499</v>
       </c>
       <c r="E901" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -65561,7 +65917,7 @@
         <v>9499</v>
       </c>
       <c r="E902" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -65636,7 +65992,7 @@
         <v>5699</v>
       </c>
       <c r="E903" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -65711,7 +66067,7 @@
         <v>5999</v>
       </c>
       <c r="E904" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -65786,7 +66142,7 @@
         <v>1999</v>
       </c>
       <c r="E905" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -65861,7 +66217,7 @@
         <v>1799</v>
       </c>
       <c r="E906" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -65936,7 +66292,7 @@
         <v>1169</v>
       </c>
       <c r="E907" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -66011,7 +66367,7 @@
         <v>1349</v>
       </c>
       <c r="E908" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -66086,7 +66442,7 @@
         <v>1799</v>
       </c>
       <c r="E909" t="n">
-        <v>6.74</v>
+        <v>6.7</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -66161,7 +66517,7 @@
         <v>2299</v>
       </c>
       <c r="E910" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -66236,7 +66592,7 @@
         <v>2599</v>
       </c>
       <c r="E911" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -66311,7 +66667,7 @@
         <v>2599</v>
       </c>
       <c r="E912" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -66386,7 +66742,7 @@
         <v>2899</v>
       </c>
       <c r="E913" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -66461,7 +66817,7 @@
         <v>3499</v>
       </c>
       <c r="E914" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -66536,7 +66892,7 @@
         <v>4499</v>
       </c>
       <c r="E915" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -66611,7 +66967,7 @@
         <v>698</v>
       </c>
       <c r="E916" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -66686,7 +67042,7 @@
         <v>598</v>
       </c>
       <c r="E917" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -66836,7 +67192,7 @@
         <v>3899</v>
       </c>
       <c r="E919" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -66911,7 +67267,7 @@
         <v>4299</v>
       </c>
       <c r="E920" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -66986,7 +67342,7 @@
         <v>4699</v>
       </c>
       <c r="E921" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -67061,7 +67417,7 @@
         <v>3299</v>
       </c>
       <c r="E922" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -67136,7 +67492,7 @@
         <v>3699</v>
       </c>
       <c r="E923" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -67211,7 +67567,7 @@
         <v>2399</v>
       </c>
       <c r="E924" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -67286,7 +67642,7 @@
         <v>2099</v>
       </c>
       <c r="E925" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -67361,7 +67717,7 @@
         <v>2699</v>
       </c>
       <c r="E926" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -67436,7 +67792,7 @@
         <v>3899</v>
       </c>
       <c r="E927" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -67511,7 +67867,7 @@
         <v>3999</v>
       </c>
       <c r="E928" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -67586,7 +67942,7 @@
         <v>4299</v>
       </c>
       <c r="E929" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -67661,7 +68017,7 @@
         <v>4899</v>
       </c>
       <c r="E930" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -67736,7 +68092,7 @@
         <v>4899</v>
       </c>
       <c r="E931" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -67811,7 +68167,7 @@
         <v>2699</v>
       </c>
       <c r="E932" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -67886,7 +68242,7 @@
         <v>2999</v>
       </c>
       <c r="E933" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -67961,7 +68317,7 @@
         <v>3399</v>
       </c>
       <c r="E934" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -68036,7 +68392,7 @@
         <v>3599</v>
       </c>
       <c r="E935" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -68111,7 +68467,7 @@
         <v>3299</v>
       </c>
       <c r="E936" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -68182,7 +68538,7 @@
         <v>2999</v>
       </c>
       <c r="E937" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -68203,7 +68559,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="n">
+        <v>12</v>
+      </c>
       <c r="L937" t="n">
         <v>256</v>
       </c>
@@ -68322,7 +68680,7 @@
         <v>3899</v>
       </c>
       <c r="E939" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -68343,7 +68701,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="n">
+        <v>12</v>
+      </c>
       <c r="L939" t="n">
         <v>256</v>
       </c>
@@ -68391,7 +68751,7 @@
         <v>5799</v>
       </c>
       <c r="E940" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -68462,7 +68822,7 @@
         <v>3599</v>
       </c>
       <c r="E941" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -68533,7 +68893,7 @@
         <v>4199</v>
       </c>
       <c r="E942" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -68604,7 +68964,7 @@
         <v>3999</v>
       </c>
       <c r="E943" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -68679,7 +69039,7 @@
         <v>4399</v>
       </c>
       <c r="E944" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -68754,7 +69114,7 @@
         <v>3699</v>
       </c>
       <c r="E945" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -68829,7 +69189,7 @@
         <v>3999</v>
       </c>
       <c r="E946" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -68904,7 +69264,7 @@
         <v>2899</v>
       </c>
       <c r="E947" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -68979,7 +69339,7 @@
         <v>3199</v>
       </c>
       <c r="E948" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -69054,7 +69414,7 @@
         <v>3499</v>
       </c>
       <c r="E949" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -69129,7 +69489,7 @@
         <v>4699</v>
       </c>
       <c r="E950" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -69200,7 +69560,7 @@
         <v>5199</v>
       </c>
       <c r="E951" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -69271,7 +69631,7 @@
         <v>3499</v>
       </c>
       <c r="E952" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -69292,7 +69652,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="n">
+        <v>12</v>
+      </c>
       <c r="L952" t="n">
         <v>512</v>
       </c>
@@ -69411,7 +69773,7 @@
         <v>4399</v>
       </c>
       <c r="E954" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -69432,7 +69794,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="n">
+        <v>12</v>
+      </c>
       <c r="L954" t="n">
         <v>512</v>
       </c>
@@ -69480,7 +69844,7 @@
         <v>4999</v>
       </c>
       <c r="E955" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -69501,7 +69865,9 @@
           <t>海思 麒麟 9010S</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="n">
+        <v>12</v>
+      </c>
       <c r="L955" t="n">
         <v>1024</v>
       </c>
@@ -69549,7 +69915,7 @@
         <v>7999</v>
       </c>
       <c r="E956" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -69924,7 +70290,7 @@
         <v>8999</v>
       </c>
       <c r="E961" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -69999,7 +70365,7 @@
         <v>9999</v>
       </c>
       <c r="E962" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -70074,7 +70440,7 @@
         <v>10999</v>
       </c>
       <c r="E963" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -70149,7 +70515,7 @@
         <v>11299</v>
       </c>
       <c r="E964" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -70224,7 +70590,7 @@
         <v>2199</v>
       </c>
       <c r="E965" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -70764,7 +71130,7 @@
         <v>2299</v>
       </c>
       <c r="E973" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -70839,7 +71205,7 @@
         <v>2699</v>
       </c>
       <c r="E974" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -70914,7 +71280,7 @@
         <v>2999</v>
       </c>
       <c r="E975" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -70989,7 +71355,7 @@
         <v>2499</v>
       </c>
       <c r="E976" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -71014,7 +71380,9 @@
           <t>海思 麒麟 8020</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="n">
+        <v>12</v>
+      </c>
       <c r="L976" t="n">
         <v>128</v>
       </c>
@@ -71062,7 +71430,7 @@
         <v>2599</v>
       </c>
       <c r="E977" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -71137,7 +71505,7 @@
         <v>2699</v>
       </c>
       <c r="E978" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -71162,7 +71530,9 @@
           <t>海思 麒麟 8020</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
+      <c r="K978" t="n">
+        <v>12</v>
+      </c>
       <c r="L978" t="n">
         <v>256</v>
       </c>
@@ -71210,7 +71580,7 @@
         <v>3199</v>
       </c>
       <c r="E979" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -71235,7 +71605,9 @@
           <t>海思 麒麟 8020</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="n">
+        <v>12</v>
+      </c>
       <c r="L979" t="n">
         <v>512</v>
       </c>
@@ -71283,7 +71655,7 @@
         <v>12999</v>
       </c>
       <c r="E980" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -71358,7 +71730,7 @@
         <v>5999</v>
       </c>
       <c r="E981" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -71429,7 +71801,7 @@
         <v>6999</v>
       </c>
       <c r="E982" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -71500,7 +71872,7 @@
         <v>8499</v>
       </c>
       <c r="E983" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -71570,7 +71942,9 @@
       <c r="D984" t="n">
         <v>21999</v>
       </c>
-      <c r="E984" t="inlineStr"/>
+      <c r="E984" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F984" t="inlineStr"/>
       <c r="G984" t="n">
         <v>5600</v>
@@ -71627,7 +72001,9 @@
       <c r="D985" t="n">
         <v>23999</v>
       </c>
-      <c r="E985" t="inlineStr"/>
+      <c r="E985" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F985" t="inlineStr"/>
       <c r="G985" t="n">
         <v>5600</v>
@@ -71684,7 +72060,9 @@
       <c r="D986" t="n">
         <v>24999</v>
       </c>
-      <c r="E986" t="inlineStr"/>
+      <c r="E986" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F986" t="inlineStr"/>
       <c r="G986" t="n">
         <v>5600</v>
@@ -71741,7 +72119,9 @@
       <c r="D987" t="n">
         <v>29999</v>
       </c>
-      <c r="E987" t="inlineStr"/>
+      <c r="E987" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F987" t="inlineStr"/>
       <c r="G987" t="n">
         <v>5600</v>
@@ -71798,7 +72178,9 @@
       <c r="D988" t="n">
         <v>19999</v>
       </c>
-      <c r="E988" t="inlineStr"/>
+      <c r="E988" t="n">
+        <v>6.8</v>
+      </c>
       <c r="F988" t="inlineStr"/>
       <c r="G988" t="n">
         <v>5600</v>
@@ -71855,9 +72237,13 @@
       <c r="D989" t="n">
         <v>9999</v>
       </c>
-      <c r="E989" t="inlineStr"/>
+      <c r="E989" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F989" t="inlineStr"/>
-      <c r="G989" t="inlineStr"/>
+      <c r="G989" t="n">
+        <v>2775</v>
+      </c>
       <c r="H989" t="inlineStr">
         <is>
           <t>六核</t>
@@ -71869,7 +72255,9 @@
           <t>苹果 A20 Pro</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="n">
+        <v>4</v>
+      </c>
       <c r="L989" t="n">
         <v>256</v>
       </c>
@@ -71912,9 +72300,13 @@
       <c r="D990" t="n">
         <v>15999</v>
       </c>
-      <c r="E990" t="inlineStr"/>
+      <c r="E990" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F990" t="inlineStr"/>
-      <c r="G990" t="inlineStr"/>
+      <c r="G990" t="n">
+        <v>2775</v>
+      </c>
       <c r="H990" t="inlineStr">
         <is>
           <t>六核</t>
@@ -71926,7 +72318,9 @@
           <t>苹果 A20 Pro</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr"/>
+      <c r="K990" t="n">
+        <v>4</v>
+      </c>
       <c r="L990" t="n">
         <v>256</v>
       </c>
@@ -71965,9 +72359,13 @@
       <c r="D991" t="n">
         <v>10999</v>
       </c>
-      <c r="E991" t="inlineStr"/>
+      <c r="E991" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F991" t="inlineStr"/>
-      <c r="G991" t="inlineStr"/>
+      <c r="G991" t="n">
+        <v>2775</v>
+      </c>
       <c r="H991" t="inlineStr">
         <is>
           <t>六核</t>
@@ -71979,7 +72377,9 @@
           <t>苹果 A20 Pro</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="n">
+        <v>4</v>
+      </c>
       <c r="L991" t="n">
         <v>256</v>
       </c>
@@ -72022,9 +72422,13 @@
       <c r="D992" t="n">
         <v>11999</v>
       </c>
-      <c r="E992" t="inlineStr"/>
+      <c r="E992" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F992" t="inlineStr"/>
-      <c r="G992" t="inlineStr"/>
+      <c r="G992" t="n">
+        <v>2775</v>
+      </c>
       <c r="H992" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72032,7 +72436,9 @@
       </c>
       <c r="I992" t="inlineStr"/>
       <c r="J992" t="inlineStr"/>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="n">
+        <v>4</v>
+      </c>
       <c r="L992" t="n">
         <v>256</v>
       </c>
@@ -72071,9 +72477,13 @@
       <c r="D993" t="n">
         <v>15499</v>
       </c>
-      <c r="E993" t="inlineStr"/>
+      <c r="E993" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F993" t="inlineStr"/>
-      <c r="G993" t="inlineStr"/>
+      <c r="G993" t="n">
+        <v>2775</v>
+      </c>
       <c r="H993" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72081,7 +72491,9 @@
       </c>
       <c r="I993" t="inlineStr"/>
       <c r="J993" t="inlineStr"/>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="n">
+        <v>4</v>
+      </c>
       <c r="L993" t="n">
         <v>256</v>
       </c>
@@ -72120,9 +72532,13 @@
       <c r="D994" t="n">
         <v>20499</v>
       </c>
-      <c r="E994" t="inlineStr"/>
+      <c r="E994" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F994" t="inlineStr"/>
-      <c r="G994" t="inlineStr"/>
+      <c r="G994" t="n">
+        <v>2775</v>
+      </c>
       <c r="H994" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72130,7 +72546,9 @@
       </c>
       <c r="I994" t="inlineStr"/>
       <c r="J994" t="inlineStr"/>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="n">
+        <v>4</v>
+      </c>
       <c r="L994" t="n">
         <v>256</v>
       </c>
@@ -72169,9 +72587,13 @@
       <c r="D995" t="n">
         <v>17999</v>
       </c>
-      <c r="E995" t="inlineStr"/>
+      <c r="E995" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F995" t="inlineStr"/>
-      <c r="G995" t="inlineStr"/>
+      <c r="G995" t="n">
+        <v>2775</v>
+      </c>
       <c r="H995" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72179,7 +72601,9 @@
       </c>
       <c r="I995" t="inlineStr"/>
       <c r="J995" t="inlineStr"/>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="n">
+        <v>4</v>
+      </c>
       <c r="L995" t="n">
         <v>512</v>
       </c>
@@ -72222,9 +72646,13 @@
       <c r="D996" t="n">
         <v>21499</v>
       </c>
-      <c r="E996" t="inlineStr"/>
+      <c r="E996" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F996" t="inlineStr"/>
-      <c r="G996" t="inlineStr"/>
+      <c r="G996" t="n">
+        <v>2775</v>
+      </c>
       <c r="H996" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72232,7 +72660,9 @@
       </c>
       <c r="I996" t="inlineStr"/>
       <c r="J996" t="inlineStr"/>
-      <c r="K996" t="inlineStr"/>
+      <c r="K996" t="n">
+        <v>4</v>
+      </c>
       <c r="L996" t="n">
         <v>1024</v>
       </c>
@@ -72275,9 +72705,13 @@
       <c r="D997" t="n">
         <v>26499</v>
       </c>
-      <c r="E997" t="inlineStr"/>
+      <c r="E997" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F997" t="inlineStr"/>
-      <c r="G997" t="inlineStr"/>
+      <c r="G997" t="n">
+        <v>2775</v>
+      </c>
       <c r="H997" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72285,7 +72719,9 @@
       </c>
       <c r="I997" t="inlineStr"/>
       <c r="J997" t="inlineStr"/>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="n">
+        <v>4</v>
+      </c>
       <c r="L997" t="n">
         <v>2048</v>
       </c>
@@ -72328,9 +72764,13 @@
       <c r="D998" t="n">
         <v>12999</v>
       </c>
-      <c r="E998" t="inlineStr"/>
+      <c r="E998" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F998" t="inlineStr"/>
-      <c r="G998" t="inlineStr"/>
+      <c r="G998" t="n">
+        <v>2775</v>
+      </c>
       <c r="H998" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72338,7 +72778,9 @@
       </c>
       <c r="I998" t="inlineStr"/>
       <c r="J998" t="inlineStr"/>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="n">
+        <v>4</v>
+      </c>
       <c r="L998" t="n">
         <v>256</v>
       </c>
@@ -72377,9 +72819,13 @@
       <c r="D999" t="n">
         <v>16499</v>
       </c>
-      <c r="E999" t="inlineStr"/>
+      <c r="E999" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F999" t="inlineStr"/>
-      <c r="G999" t="inlineStr"/>
+      <c r="G999" t="n">
+        <v>2775</v>
+      </c>
       <c r="H999" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72387,7 +72833,9 @@
       </c>
       <c r="I999" t="inlineStr"/>
       <c r="J999" t="inlineStr"/>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="n">
+        <v>4</v>
+      </c>
       <c r="L999" t="n">
         <v>256</v>
       </c>
@@ -72426,9 +72874,13 @@
       <c r="D1000" t="n">
         <v>21499</v>
       </c>
-      <c r="E1000" t="inlineStr"/>
+      <c r="E1000" t="n">
+        <v>6.1</v>
+      </c>
       <c r="F1000" t="inlineStr"/>
-      <c r="G1000" t="inlineStr"/>
+      <c r="G1000" t="n">
+        <v>2775</v>
+      </c>
       <c r="H1000" t="inlineStr">
         <is>
           <t>六核</t>
@@ -72436,7 +72888,9 @@
       </c>
       <c r="I1000" t="inlineStr"/>
       <c r="J1000" t="inlineStr"/>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="n">
+        <v>4</v>
+      </c>
       <c r="L1000" t="n">
         <v>256</v>
       </c>
@@ -72476,7 +72930,7 @@
         <v>6999</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
